--- a/public/shopping_decision_diary_extended.xlsx
+++ b/public/shopping_decision_diary_extended.xlsx
@@ -15,7 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -6357,7 +6359,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Tonya</t>
+          <t>Christine</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -6366,48 +6368,48 @@
         </is>
       </c>
       <c r="C119" s="1" t="n">
-        <v>40219</v>
+        <v>40211</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>cold medicine, Valentine card</t>
+          <t>boys clothes</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>ebay</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Walgreens, Nyquil, Dayquil, card for my mom, bread</t>
+          <t>lot of 12 boys size 10 clothes on ebay, $26 with shipping</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Snow day, Tyler's school was closed and I called in since the roads were bad.  Walked to the Walgreens on Grand because Tyler has a cold and we were out of everything.  Got the Walgreens brand Nyquil and Dayquil, a loaf of bread and a Valentine card for my mom.  The Dayquil had a $3 register reward so I will use that next time.</t>
+          <t>Jake is growing out of everything and I am not paying $20 a pair for jeans at Kohls. I had been watching a few ebay lots for boys size 10 all week. Won one tonight for $18.50 plus $7.50 shipping, 12 pieces, mostly Gap and Children's Place, a couple Old Navy. Pictures looked ok. I lost the first one I bid on because somebody came in at the last 10 seconds, that always drives me nuts.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Didn't have to drive in the snow, store brand medicine is half the price and I got $3 back for next time.</t>
+          <t>Good price if everything fits and isn't stained. Won't really know until it gets here.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Tonya</t>
+          <t>Christine</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -6416,43 +6418,48 @@
         </is>
       </c>
       <c r="C120" s="1" t="n">
-        <v>40211</v>
+        <v>40219</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>graphing calculator</t>
+          <t>cold medicine, Valentine card</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>walmart.com</t>
+          <t>Walgreens</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Walgreens, Nyquil, Dayquil, card for my mom, bread</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Tyler's algebra teacher sent home a note that they need a TI-83 or TI-84 calculator.  Looked on walmart.com, the TI-83 Plus is $89 and the 84 is over a hundred.  Not this paycheck.  I'm going to ask the teacher if the school has ones to borrow, a girl at work said her daughter's school did that.</t>
+          <t>Snow day, Tyler's school was closed and I called in since the roads were bad.  Walked to the Walgreens on Route 83 because Tyler has a cold and we were out of everything.  Got the Walgreens brand Nyquil and Dayquil, a loaf of bread and a Valentine card for my mom.  The Dayquil had a $3 register reward so I will use that next time.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>At least now I know what it costs and I can plan for it.  Didnt have to drive anywhere to find out.</t>
+          <t>Didn't have to drive in the snow, store brand medicine is half the price and I got $3 back for next time.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Tonya</t>
+          <t>Christine</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -6461,48 +6468,43 @@
         </is>
       </c>
       <c r="C121" s="1" t="n">
-        <v>40215</v>
+        <v>40211</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>gym shoes for Tyler</t>
+          <t>graphing calculator</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Payless</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Payless, gym shoes and a pair of flats for me</t>
+          <t>walmart.com</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Payless had the buy one get one half off going on so we went Saturday.  Tyler needed gym shoes, his old ones have a hole in the side.  He wanted Nikes from somewhere else but I told him it was Payless or nothing this month.  He found a pair of black Champion ones he was ok with, $24.99, and I got black flats for work for half off.  Came to $37 and change with tax.</t>
+          <t>Tyler's algebra teacher sent home a note that they need a TI-83 or TI-84 calculator.  Looked on walmart.com, the TI-83 Plus is $89 and the 84 is over a hundred.  Not this paycheck.  I'm going to ask the teacher if the school has ones to borrow, a girl at work said her daughter's school did that.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Two pairs of shoes for under $40.  He got over the Nike thing pretty fast once he saw the Champions.</t>
+          <t>At least now I know what it costs and I can plan for it.  Didnt have to drive anywhere to find out.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Tonya</t>
+          <t>Christine</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -6511,31 +6513,31 @@
         </is>
       </c>
       <c r="C122" s="1" t="n">
-        <v>40217</v>
+        <v>40210</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>phone minutes</t>
+          <t>groceries</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>tracfone.com</t>
+          <t>Aldi</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>120 minute card from tracfone.com</t>
+          <t>Aldi - groceries for the week</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>My Tracfone was down to 11 minutes.  I usually get the card at Walgreens but my sister told me if you buy on the tracfone website and put in a bonus code you get extra minutes.  Found a code on a website that gave 40 extra, so I paid $29.99 for the 120 minute card and got 160 minutes plus 90 more days.  It added to the phone right away.</t>
+          <t>Aldi on Monday like always. $87 for the week, including the stuff for Jake's lunches and a bag of apples for 2.49. I bring my own bags and a quarter for the cart. Mike's hours got cut again in January so Aldi is pretty much it for groceries now unless Jewel has something really good on sale. The only thing I couldnt get was the Eggo waffles Emma likes. They have a store brand but she knows the difference.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6545,14 +6547,14 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Same price as the store but 40 extra minutes.  Why didnt I know about this before.</t>
+          <t>Cheapest groceries around and I was done in 30 minutes. $87 for a family of 5 is hard to beat.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Elaine</t>
+          <t>Christine</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -6561,48 +6563,48 @@
         </is>
       </c>
       <c r="C123" s="1" t="n">
-        <v>40212</v>
+        <v>40215</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Le Creuset braiser</t>
+          <t>gym shoes for Tyler</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>williams-sonoma.com, Williams-Sonoma at Northbrook Court</t>
+          <t>Payless</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Le Creuset braiser, Williams-Sonoma</t>
+          <t>Payless, gym shoes and a pair of flats for me</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>I have been looking at the 3.5 quart Le Creuset braiser on the Williams-Sonoma site for about a month. At $229 I wanted to see the colors in person before committing, so I drove to Northbrook Court on Wednesday afternoon thinking it would be quiet. It was quiet. The store had the braiser in Flame and Cherry but not the Caribbean blue I had my heart set on. The saleswoman, when I finally got her attention, told me I could "just order that online" and went back to folding napkins. I asked whether they could ship it from another store and she said she didn't think so. I bought the Flame one because I wanted to use it this weekend, and because I was a little annoyed and wanted to be done. Mark's position is that it is a pot and it will braise the same in any color. He is right, which does not help.</t>
+          <t>Payless had the buy one get one half off going on so we went Saturday.  Tyler needed gym shoes, his old ones have a hole in the side.  He wanted Nikes from somewhere else but I told him it was Payless or nothing this month.  He found a pair of black Champion ones he was ok with, $24.99, and I got black flats for work for half off.  Came to $37 and change with tax.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Not satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>I got a very good pot, but not the one I wanted, and I was made to feel like a nuisance for asking. For what Williams-Sonoma charges, I expect someone to at least look it up.</t>
+          <t>Two pairs of shoes for under $40.  He got over the Nike thing pretty fast once he saw the Champions.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Elaine</t>
+          <t>Christine</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -6611,48 +6613,43 @@
         </is>
       </c>
       <c r="C124" s="1" t="n">
-        <v>40210</v>
+        <v>40218</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>SAT study guide</t>
+          <t>Netflix</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>The Official SAT Study Guide, Amazon</t>
+          <t>netflix.com</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Will's tutor sent an email last week recommending the College Board's Official SAT Study Guide, the blue one, and said not to bother with anything else until he has worked through it. Barnes &amp; Noble in Deerfield had it for $21.99 when I was there in January. On Amazon it was $13.57, and since that was under the free shipping threshold I added a package of the mechanical pencils he likes and a Barron's vocabulary book I suspect will go unopened. The order is due Thursday, which is before his next session, so that was the deciding factor as much as the price.</t>
+          <t>Snow day, kids home, bored out of their minds by 10am. I looked at signing up for Netflix, the $8.99 one disc at a time plan with the free trial. Looked at what they have on the watch instantly thing and it's mostly old stuff. Decided no. Between Redbox and the library DVDs we're fine and another $9 a month is another $9 a month. Put on Wii Sports instead.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>It was eight dollars less than the bookstore and I didn't have to drive anywhere. The tutor was specific about the edition, so there was no decision to agonize over.</t>
+          <t>Talked myself out of it, which was the right call. The free trial is tempting but I know we'd forget to cancel.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Elaine</t>
+          <t>Christine</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -6661,31 +6658,31 @@
         </is>
       </c>
       <c r="C125" s="1" t="n">
-        <v>40215</v>
+        <v>40217</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Super Bowl party food</t>
+          <t>phone minutes</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Whole Foods</t>
+          <t>tracfone.com</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Whole Foods in Deerfield, salmon, cheese, prepared foods, wine</t>
+          <t>120 minute card from tracfone.com</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>We are having three other families over for the game tomorrow, so I went to Whole Foods in Deerfield on Saturday morning before it got crazy. I had a list: a side of salmon, two cheeses, the spinach artichoke dip from the prepared foods case, baguettes, a case of Pellegrino and the Spanish red Mark likes. The man at the cheese counter let me taste three things and talked me into a Manchego that was not on the list, and the fish was gorgeous. The checkout line was long but it moved. I spent $214, which is more than I meant to, but with four families that is not outrageous and I do not have to cook anything but the salmon.</t>
+          <t>My Tracfone was down to 11 minutes.  I usually get the card at Walgreens but my sister told me if you buy on the tracfone website and put in a bonus code you get extra minutes.  Found a code on a website that gave 40 extra, so I paid $29.99 for the 120 minute card and got 160 minutes plus 90 more days.  It added to the phone right away.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6695,14 +6692,14 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Everything was fresh, the staff knew what they were talking about and I was in and out in forty minutes with the party essentially done.</t>
+          <t>Same price as the store but 40 extra minutes.  Why didnt I know about this before.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Elaine</t>
+          <t>Christine</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -6711,26 +6708,31 @@
         </is>
       </c>
       <c r="C126" s="1" t="n">
-        <v>40216</v>
+        <v>40219</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Turnabout dress for Charlotte</t>
+          <t>poster board, valentines</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>nordstrom.com</t>
+          <t>Walmart</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Walmart - poster board, glue sticks, valentines for Jake, milk</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Charlotte's turnabout dance is the first weekend in March and she wanted to look at dresses, so we sat on the couch with the laptop during the pregame and went through nordstrom.com. She filtered by juniors and under $200, which I appreciated. She has narrowed it to three: a navy BCBG one-shoulder, a Jessica McClintock in dark green, and something strapless I have reservations about. We did not order anything because she wants to try them on and I want to see the strapless one on her before I have an opinion. We will go to Old Orchard next Saturday, assuming the roads are clear.</t>
+          <t>Jake's report turned into a poster (of course) and it's due Friday now because of the snow days. Walmart in Mundelein for poster board, glue sticks and the valentines for his class. He wanted the Star Wars ones and they were sold out so he settled for Transformers. Store was packed, everyone digging out and restocking after the storm. 20 minutes in line with the 20 items or less lane closed. Grabbed milk since I was there.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6740,14 +6742,14 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>The site is easy to narrow down and she did most of the work. Nothing purchased yet, but we know what we are looking for, which is more than I could say an hour earlier.</t>
+          <t>Got what we needed but the line was ridiculous and they were out of the valentines he wanted. Walmart is always like that lately.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Elaine</t>
+          <t>Christine</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -6756,48 +6758,48 @@
         </is>
       </c>
       <c r="C127" s="1" t="n">
-        <v>40217</v>
+        <v>40216</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Valentine's dinner reservation</t>
+          <t>printer ink</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>OpenTable, Froggy's, Gabriel's</t>
+          <t>amazon, walmart.com, staples.com</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>reservation at Froggy's in Highwood for Sunday the 14th</t>
+          <t>nothing yet</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Mark and I do not exchange gifts for Valentine's Day, we go to dinner, and I am the one who remembers to book it. I looked at the menus for Froggy's and Gabriel's in Highwood and one place in Lake Forest, then checked OpenTable for Sunday night. Gabriel's had nothing between 5:00 and 9:30, and the Lake Forest place had a prix fixe for $85 a person that felt like a lot for a Sunday. Froggy's had 7:00 and the regular menu, so I took it. The whole thing took about ten minutes and I got an email confirmation, which is the part I like, since I have called restaurants before and found no record of us at the door.</t>
+          <t>Our printer is out of black ink again and Jake has a report due. HP 60 cartridge. Walmart.com is $14.97, Staples $15.99, amazon has off brand ones for $6 but the reviews say they don't always work with the printer. I'm sick of paying $15 for ink every two months, the printer only cost $39. Looked at the refill kits too. Didn't buy anything, going to see if Mike can print it at work.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Not satisfied</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Reservation made in ten minutes, at the place we actually prefer, with a confirmation in writing. The hard part was remembering to do it before the week got away from me.</t>
+          <t>Still have no ink and the report is due Tuesday. Everything is either expensive or iffy.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Vicki</t>
+          <t>Christine</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -6806,48 +6808,48 @@
         </is>
       </c>
       <c r="C128" s="1" t="n">
-        <v>40213</v>
+        <v>40220</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>basketball shoes for my daughter</t>
+          <t>restaurant deal</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dick's Sporting Goods</t>
+          <t>Groupon</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Nike basketball shoes at Dick's, $54.99</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>My daughter plays on the 7th grade team at school (she's 13) and her shoes were coming apart at the toe. Took her to Dick's in Vernon Hills after practice. They have a whole wall of basketball shoes and she went straight for the $110 Kobe ones, which I said no to. Found a pair of Nikes on the sale rack for 54.99 that she liked fine once she tried them on. The kid working the shoe department actually knew what he was talking about and brought out a half size up, which was the right call. Also grabbed a new water bottle since hers is somewhere in the school gym.</t>
+          <t>My sister keeps telling me about Groupon so I finally signed up for the emails. Today's deal was $20 for $40 at some Italian place in Lake Forest. Mike and I haven't been out since our anniversary, and I thought maybe for Valentines. Then I thought about it, $20 plus the tip plus a sitter is $50 we don't have for one dinner. Closed it. Also half the deals are for spas and yoga, not really my life right now.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Not satisfied</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>She got shoes she likes, I paid half of what she wanted me to pay, and the salesperson was helpful. In and out in 30 minutes.</t>
+          <t>It's a good deal for someone else. Just made me a little depressed honestly.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Vicki</t>
+          <t>Christine</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6856,31 +6858,31 @@
         </is>
       </c>
       <c r="C129" s="1" t="n">
-        <v>40220</v>
+        <v>40213</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>car emergency kit</t>
+          <t>snow boots</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>target.com, Amazon</t>
+          <t>Once Upon a Child</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>roadside emergency kit at Target, $29.99</t>
+          <t>Sorel boots size 3 at Once Upon a Child, $12</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>After the storm I decided my son is not driving around without jumper cables and a blanket in the trunk. Looked on Amazon and target.com Wednesday night. Amazon had a kit for 24.99 but shipping made it the same as Target's. Target.com said the Mundelein store had it in stock so I picked it up on the way home from work Thursday. Threw in an ice scraper and a jug of washer fluid while I was there.</t>
+          <t>Jakes boots from last year are too small and the ones at Walmart are junk, they leak after a month. Took both kids to Once Upon a Child in Vernon Hills after school. They had a pair of Sorels in a 3 that looked barely worn for $12. New those are like $60. Also found a Columbia fleece for Emma for $6. The kids were climbing on the toy shelf the whole time and I had to put back a Leapster Emma found, but we got out of there in 20 minutes.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6890,14 +6892,14 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Checking the website first saved me a wasted trip. $29.99 for cables, flares, a flashlight and a poncho is fine with me if it means I worry a little less.</t>
+          <t>$12 for good boots that will actually last the rest of the winter. I love that store.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Vicki</t>
+          <t>Christine</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6906,11 +6908,11 @@
         </is>
       </c>
       <c r="C130" s="1" t="n">
-        <v>40211</v>
+        <v>40215</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>groceries</t>
+          <t>Super Bowl food</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -6925,12 +6927,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Jewel - milk, cereal, chicken, lunch stuff, frozen pizzas</t>
+          <t>Jewel - chips, salsa, ground beef, pop, buns</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Tuesday is my grocery day. I had my list and the Jewel ad and went after work. With a 16 year old in the house we go through milk and cereal like crazy, so I got 3 gallons and whatever cereal was on the 10 for $10. Boneless chicken breasts were 1.99 a pound so I got two family packs for the freezer.  Line was long at 5:30 and only two lanes open, which is typical for that store.</t>
+          <t>Mike's brother and his family are coming over for the Super Bowl so I needed more than Aldi had. Jewel had Tostitos buy one get one, Pepsi 12 packs 4 for $11 and ground beef for 1.99 a pound. I had a coupon for the salsa from the Sunday paper too. $43 total and the receipt said I saved $22 so I actually read it twice. It was a zoo in there on a Saturday afternoon though. Emma knocked over a display of Valentine M&amp;Ms, so that was fun.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6940,14 +6942,14 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Got everything on the list and the chicken was a good price. I would have said extremely but the checkout took 15 minutes.</t>
+          <t>Saved almost as much as I spent, which is the only reason I shop at Jewel anymore. Would of been better without the crowds.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Vicki</t>
+          <t>Christine</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6956,31 +6958,31 @@
         </is>
       </c>
       <c r="C131" s="1" t="n">
-        <v>40215</v>
+        <v>40221</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>jeans and a hoodie for the kids</t>
+          <t>Valentine's gift for my husband</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Hollister, American Eagle at Hawthorn Mall</t>
+          <t>Walgreens photo</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2 pair of jeans and a hoodie at American Eagle</t>
+          <t>8x10 collage print of the kids, Walgreens photo, $3.99</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Saturday at Hawthorn with both kids, which is not my favorite way to spend a Saturday. My daughter wanted Hollister. We went in, it is dark and the music is so loud you can't think, and a plain hoodie was $49.50. I told her we would look at American Eagle first. AE had jeans buy one get one 50% off so my son got two pair (he's outgrown everything again, 16 and still growing) and my daughter found a hoodie on the clearance rack for $19.99. She was a little sulky about not getting the Hollister one but got over it by the food court. Total was about $95 for the three things.</t>
+          <t>Didn't want to spend money on Mike for Valentines but didn't want to do nothing either. The Walgreens website lets you make a collage from your pictures, so I did one with the kids from the sledding pictures the day of the storm. 8x10 was 3.99 and I had a 20% off code from an email. Ordered it online and picked it up at the Walgreens on Route 83 an hour later, paid at the counter. Grabbed a frame at Dollar Tree on the way home. Jake signed the back.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6990,14 +6992,14 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Half the price of Hollister for basically the same stuff. My son could care less what brand it is as long as it fits, so he was easy.</t>
+          <t>Under $5 for something he'll actually like better than a tie. Ready in an hour, no waiting.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Vicki</t>
+          <t>Christine</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -7006,31 +7008,31 @@
         </is>
       </c>
       <c r="C132" s="1" t="n">
-        <v>40210</v>
+        <v>40212</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>SAT prep book</t>
+          <t>Valentine's party supplies</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Amazon, borders.com</t>
+          <t>Dollar Tree</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>The Official SAT Study Guide from Amazon</t>
+          <t>Dollar Tree - valentines, heart stickers, plates, napkins, 2 bags of candy</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>My son is taking the SAT in May so I told him we were getting a prep book now, not in April. I looked at the Kaplan and Princeton Review ones and the College Board book that has the actual old tests in it. The reviews on Amazon said to use the College Board one for the practice tests so that is what I went with. It was $13.59 on Amazon and $21.99 at Borders, and with a couple of other things I was over the $25 for free shipping. Ordered it from the kitchen table in about ten minutes.</t>
+          <t>I got stuck being the room mom for Emma's kindergarten Valentine party. Went to the Dollar Tree in Mundelein with the list from the teacher. Got paper plates and napkins with hearts, foam heart stickers for the craft, 2 bags of conversation hearts and a box of valentines for Emma to fill out (she wanted the Hannah Montana ones, fine). 9 things, $9 and some tax. I looked at the same stickers at Target last week and they were 3.99 a pack.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -7040,14 +7042,14 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Eight dollars cheaper than the store, no driving, and it should be here by Thursday. Now whether he opens it is a different story.</t>
+          <t>Everything on the list for under 10 bucks. The other moms can chip in for the juice boxes.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Vicki</t>
+          <t>Christine</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -7056,48 +7058,48 @@
         </is>
       </c>
       <c r="C133" s="1" t="n">
-        <v>40221</v>
+        <v>40214</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>snow boots for my daughter</t>
+          <t>Wimpy Kid book</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped offline and didn't purchase</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lands End, Zappos</t>
+          <t>Borders</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lands End snow boots</t>
+          <t>nothing - put it on hold at the library instead</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Her boots from last year don't fit, so my daughter has been wearing gym shoes in the snow all week. I looked at Zappos first since shipping is free both ways but the Sorels were $90. Lands End had their snow boots marked down to 34.99 and I had a free shipping code from an email, so I ordered a size 7. She wanted the pink ones. If they don't fit I can return them at Sears, which is easier than mailing them back.</t>
+          <t>Jake wanted the new Diary of a Wimpy Kid book (Dog Days) so we stopped at Borders in Vernon Hills on the way home. $13.95. I let him read a few pages in the store and then told him no, we'd get it from the library. He pouted. We went to the Fremont library and they have 4 copies but all were checked out, so I put a hold on it, he's 6th in line. Figure 3 weeks. I'm not spending $14 on a book he'll finish in 2 days.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>$35 with free shipping for boots that will probably only fit her one winter anyway. Can't complain.</t>
+          <t>Didn't spend the money. He'll live. The library hold system works fine, it's just slow.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Vicki</t>
+          <t>Christine</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -7106,48 +7108,48 @@
         </is>
       </c>
       <c r="C134" s="1" t="n">
-        <v>40216</v>
+        <v>40217</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Super Bowl food</t>
+          <t>winter jacket for Jake</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Costco</t>
+          <t>ebay</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Costco - wings, chips, salsa, pop, water, paper plates</t>
+          <t>boys Columbia jacket on ebay, $22</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>We had my brother's family and a couple of my son's friends coming over for the Super Bowl. Went to Costco Sunday morning right when they opened at 10 to beat the crowd. Got the big bag of frozen wings, two things of tortilla chips, the salsa, a case of pop, a case of water and paper plates. Also a rotisserie chicken for Monday because they are $4.99 and I was not going to want to cook. Was out of there by 10:40 and the lines were already getting long behind me.</t>
+          <t>Won a Columbia winter jacket for Jake on ebay, size 10/12, $15 plus $7 shipping. Listing said "excellent used condition." It came Thursday and the zipper is seperated at the bottom and won't zip up past halfway, which is the whole point of a winter coat. There's also a stain on the sleeve that wasn't in the pictures. I emailed the seller twice, nothing. Opened a case with ebay but I'm not holding my breath over $22. Should have just gone to Once Upon a Child where I can look at it first.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Not at all satisfied</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Everything in one trip, the wings fed 6 teenagers, and I think I spent about $85 which is less than it would of been at Jewel.</t>
+          <t>Wasted $22 we don't have on a coat he can't wear. The seller won't answer and now I have to deal with ebay's dispute thing.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Vicki</t>
+          <t>Elaine</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -7156,48 +7158,48 @@
         </is>
       </c>
       <c r="C135" s="1" t="n">
-        <v>40218</v>
+        <v>40211</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>used car for my son</t>
+          <t>driving school</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>cars.com, autotrader, craigslist</t>
+          <t>topdriver.com</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>behind the wheel lessons, Top Driver</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Snow day, everything was cancelled, so my son and I sat down at the computer and looked at used cars. He got his license in January and has been driving my car, which is getting old fast. We are thinking a 2002-2004 Civic or Corolla, under $6,000, and nothing with a sunroof or anything he can show off with. Looked at cars.com and autotrader and craigslist. Anything decent under 6,000 has 130,000 miles on it or is in the city. The ones on craigslist I dont trust. We bookmarked a couple from dealers in Waukegan and Libertyville but I am not calling anybody until the roads are clear.</t>
+          <t>Charlotte turned 16 in January and the State of Illinois would like her to have six hours of behind the wheel instruction from a professional before she is allowed to terrify the rest of us. The high school program has a waiting list until summer, so I signed her up with Top Driver online. $395 for the classroom and driving package. The school newsletter had a $25 off code which I found after I'd already typed my credit card in, so I backed up and did it again. I'd like to say I shopped around but there are two driving schools within a reasonable distance and the other one's website looked like it was built in 1997.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Not satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Not satisfied because there was nothing in our price range that I would actually put my kid in. We may have to go up to $7,000 or wait until spring.</t>
+          <t>It's a lot of money to pay someone to sit in a car with my daughter, but it's required and the signup took five minutes. The $25 off made me feel slightly less held up.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Wendy</t>
+          <t>Elaine</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -7206,31 +7208,31 @@
         </is>
       </c>
       <c r="C136" s="1" t="n">
-        <v>40215</v>
+        <v>40218</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ceiling tiles and grid</t>
+          <t>floor mats for the Camry</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Menards</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Menards, 11 cases of ceiling tiles, hanger wire, grid clips, shop light</t>
+          <t>rubber all weather floor mats, Amazon</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Went to Menards in Gurnee Saturday morning after the Home Depot trip was a bust. They had the same Armstrong tiles, 14 cases on the shelf, so we took 11 plus the hanger wire and a box of the grid clips. Paid about $22 more total than Home Depot would have been but the 11% rebate was going on so it comes out ahead if I remember to mail in the form. A kid from the lumber yard helped Rick load the truck. Also picked up a shop light for the furnace room since we were there.</t>
+          <t>Charlotte is inheriting the 2002 Camry when she gets her license, and between a teenager and a Chicago winter the carpet mats have no chance. I looked at the WeatherTech ones first since everybody raves about them, but they were $90 and this is a car with 140,000 miles on it. Amazon had a set of rubber all weather mats for $34.95 with free shipping and about 200 reviews, most of them from people in states with actual weather. Ordered them from the couch Tuesday night while the snow came down and Mark shoveled. It seemed like the right division of labor.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -7240,14 +7242,14 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Had everything we needed in one trip, loaded it for us, and the rebate will cover the price difference. Basement ceiling goes in next weekend.</t>
+          <t>A third of the price of the fancy ones, free shipping, and I didn't have to leave the house in a blizzard. If they curl up in the sun I'll report back.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Wendy</t>
+          <t>Elaine</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -7256,48 +7258,48 @@
         </is>
       </c>
       <c r="C137" s="1" t="n">
-        <v>40214</v>
+        <v>40213</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ceiling tiles for the basement</t>
+          <t>groceries</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Shopped offline and didn't purchase</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Home Depot</t>
+          <t>Trader Joe's</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Did not purchase</t>
+          <t>Trader Joe's, snacks, frozen stuff, wine</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>We are putting a drop ceiling in the basement. I priced the Armstrong 2x4 tiles on menards.com and homedepot.com Thursday night and Home Depot was about $2 a case cheaper, and their site showed them in stock at the Gurnee store. Drove over after work Friday with the truck. They had 3 cases on the shelf and we need 11. The guy in the department checked the computer and said Vernon Hills had 4. So the website was wrong or somebody bought 8 cases that afternoon. Either way I drove home with nothing.</t>
+          <t>Thursday Trader Joe's run in Northbrook. I go for the frozen orange chicken, the pita chips and the two dollar wine (two ninety nine here, Illinois gets everything last), and I come out with $78 of things I didn't know I needed. This week it was a bag of dark chocolate peanut butter cups that did not make it to the car intact. Jack has decided he only eats their mini pizzas, which is fine, they're cheap. The lot was its usual demolition derby but the checkout guy was cheerful and bagged everything so the eggs were on top for once.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Not satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>An hour and the gas wasted because the website said in stock and it wasn't. I would of just gone to Menards if I had known.</t>
+          <t>Cheap, quick, nobody in my family complains about anything from there. The peanut butter cups alone were worth the trip.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Wendy</t>
+          <t>Elaine</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -7306,48 +7308,48 @@
         </is>
       </c>
       <c r="C138" s="1" t="n">
-        <v>40218</v>
+        <v>40212</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>groceries before the snow</t>
+          <t>Le Creuset braiser</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Jewel</t>
+          <t>williams-sonoma.com, Williams-Sonoma at Northbrook Court</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Jewel, milk, bread, eggs, chili stuff, dog food, driveway salt</t>
+          <t>Le Creuset braiser, Williams-Sonoma</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>The news said 8 to 12 inches starting Tuesday afternoon so I went to Jewel at 7 Tuesday morning before work. Milk, bread, eggs, the stuff for a pot of chili, dog food, and a bag of salt for the driveway. It was already busier than a normal Tuesday morning but the shelves were full and I was out in 25 minutes. By the time I drove past on the way home at 5 the lot was packed.</t>
+          <t>I have been looking at the 3.5 quart Le Creuset braiser on the Williams-Sonoma site for about a month. At $229 I wanted to see the colors in person before committing, so I drove to Northbrook Court on Wednesday afternoon thinking it would be quiet. It was quiet. The store had the braiser in Flame and Cherry but not the Caribbean blue I had my heart set on. The saleswoman, when I finally got her attention, told me I could "just order that online" and went back to folding napkins. I asked whether they could ship it from another store and she said she didn't think so. I bought the Flame one because I wanted to use it this weekend, and because I was a little annoyed and wanted to be done. Mark's position is that it is a pot and it will braise the same in any color. He is right, which does not help.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Not satisfied</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Beat the rush and had everything I needed when school got cancelled Wednesday. Didn't have to leave the house for two days.</t>
+          <t>I got a very good pot, but not the one I wanted, and I was made to feel like a nuisance for asking. For what Williams-Sonoma charges, I expect someone to at least look it up.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Elaine</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -7356,48 +7358,48 @@
         </is>
       </c>
       <c r="C139" s="1" t="n">
-        <v>40215</v>
+        <v>40210</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>American Girl doll clothes</t>
+          <t>SAT study guide</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>ebay</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>The Official SAT Study Guide, Amazon</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Emma wants an outfit for her American Girl doll and they are $28 in the catalog which is insane for doll clothes.  Saturday night I looked on ebay and there are tons of homemade ones for $8 to $12.  I put a couple on my watch list, one auction ends Tuesday.  Didn't bid yet, I want to see how high they go first.</t>
+          <t>Will's tutor sent an email last week recommending the College Board's Official SAT Study Guide, the blue one, and said not to bother with anything else until he has worked through it. Barnes &amp; Noble in Deerfield had it for $21.99 when I was there in January. On Amazon it was $13.57, and since that was under the free shipping threshold I added a package of the mechanical pencils he likes and a Barron's vocabulary book I suspect will go unopened. The order is due Thursday, which is before his next session, so that was the deciding factor as much as the price.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Should be able to get her something cute for a third of the catalog price.  We'll see Tuesday.</t>
+          <t>It was eight dollars less than the bookstore and I didn't have to drive anywhere. The tutor was specific about the edition, so there was no decision to agonize over.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Elaine</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -7406,31 +7408,31 @@
         </is>
       </c>
       <c r="C140" s="1" t="n">
-        <v>40214</v>
+        <v>40215</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>birthday present for my nephew</t>
+          <t>Super Bowl party food</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>amazon.com</t>
+          <t>Whole Foods</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lego City fire truck set, amazon.com</t>
+          <t>Whole Foods in Deerfield, salmon, cheese, prepared foods, wine</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>My nephew Connor turns 6 next weekend and my sister said he is into Legos.  Got on Amazon Friday morning before work and found a Lego City fire truck set for $34.99 with free super saver shipping, and I had it sent straight to her house in Naperville so I don't have to haul it to the party.  Took me 10 minutes.  Read a couple reviews to make sure it wasn't too hard for a 6 year old.  Amazon says it will be there by Thursday.</t>
+          <t>We are having three other families over for the game tomorrow, so I went to Whole Foods in Deerfield on Saturday morning before it got crazy. I had a list: a side of salmon, two cheeses, the spinach artichoke dip from the prepared foods case, baguettes, a case of Pellegrino and the Spanish red Mark likes. The man at the cheese counter let me taste three things and talked me into a Manchego that was not on the list, and the fish was gorgeous. The checkout line was long but it moved. I spent $214, which is more than I meant to, but with four families that is not outrageous and I do not have to cook anything but the salmon.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7440,14 +7442,14 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Fast, free shipping, and one less thing to carry.  Amazon spoils me.</t>
+          <t>Everything was fresh, the staff knew what they were talking about and I was in and out in forty minutes with the party essentially done.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Elaine</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -7456,43 +7458,48 @@
         </is>
       </c>
       <c r="C141" s="1" t="n">
-        <v>40214</v>
+        <v>40220</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Blackhawks tickets</t>
+          <t>towels and a shower caddy</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>ticketmaster, stubhub</t>
+          <t>bedbathandbeyond.com, Bed Bath &amp; Beyond in Vernon Hills</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>4 bath towels and a shower caddy at Bed Bath &amp; Beyond</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Tyler's birthday is in March and all he wants is to go to a Blackhawks game.  I looked on ticketmaster at lunch and everything was gone except the 300 level at $65 each, then I looked on stubhub and it was worse, $90 and up for the same seats plus fees.  For 2 tickets we're talking $150+ to sit in the rafters.  Didn't buy.  Mark thinks his buddy at work has season tickets and might sell him a pair so we'll try that first.</t>
+          <t>The kids' bathroom towels have reached the texture of cardboard and the shower caddy rusted through, which I discovered when it fell on Jack. I checked the Bed Bath &amp; Beyond site Wednesday night to see what they had and what it cost, then went to the Vernon Hills store Thursday after the roads were plowed because I had two of the 20% off coupons in the kitchen drawer and they are only good in the store. Got four bath towels in a gray that will hide everything and a stainless caddy that hangs from the shower head. One coupon per item in theory, but the cashier took both without blinking. $64 before coupons, $51 after.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Not thrilled with the prices but at least I know what we're dealing with.  Hockey is expensive this year with the team doing so well.</t>
+          <t>Knew what I wanted before I walked in, coupons worked, in and out in 20 minutes. The towels are already softer than the old ones and they've only been washed once.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Elaine</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -7501,48 +7508,43 @@
         </is>
       </c>
       <c r="C142" s="1" t="n">
-        <v>40219</v>
+        <v>40216</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>books and printer ink</t>
+          <t>Turnabout dress for Charlotte</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>amazon.com</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>Diary of a Wimpy Kid, Percy Jackson book, HP ink - amazon</t>
+          <t>nordstrom.com</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>SNOW DAY.  All three kids home, Mark worked from home, and by 10 am everyone was allready bored and fighting.  Emma has been begging for the newest Diary of a Wimpy Kid (Dog Days) and Ryan wants the last Percy Jackson book since the movie comes out Friday, so I got on Amazon and ordered both, $8.99 and $7.99, and threw in the black ink cartridge for the printer since Tyler has a paper due and we were almost out.  Total was over $25 so free shipping.  I told the kids the books are their reward for not killing each other.  Amazon says 5 to 9 days with the free shipping but it's usually faster than that.</t>
+          <t>Charlotte's turnabout dance is the first weekend in March and she wanted to look at dresses, so we sat on the couch with the laptop during the pregame and went through nordstrom.com. She filtered by juniors and under $200, which I appreciated. She has narrowed it to three: a navy BCBG one-shoulder, a Jessica McClintock in dark green, and something strapless I have reservations about. We did not order anything because she wants to try them on and I want to see the strapless one on her before I have an opinion. We will go to Old Orchard next Saturday, assuming the roads are clear.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Didn't have to go out in a foot of snow, free shipping, and the kids had something to look forward to.  Amazon in a blizzard is a wonderful thing.</t>
+          <t>The site is easy to narrow down and she did most of the work. Nothing purchased yet, but we know what we are looking for, which is more than I could say an hour earlier.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Elaine</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -7551,31 +7553,31 @@
         </is>
       </c>
       <c r="C143" s="1" t="n">
-        <v>40210</v>
+        <v>40217</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>coffee</t>
+          <t>Valentine's dinner reservation</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dunkin Donuts</t>
+          <t>OpenTable, Froggy's, Gabriel's</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>medium coffee, Dunkin Donuts</t>
+          <t>reservation at Froggy's in Highwood for Sunday the 14th</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Quick stop at the Dunkin on Rt. 83 on my way in to the office.  Medium coffee with cream, $1.89.  Drive thru line was 6 cars but it moved fast.</t>
+          <t>Mark and I do not exchange gifts for Valentine's Day, we go to dinner, and I am the one who remembers to book it. I looked at the menus for Froggy's and Gabriel's in Highwood and one place in Lake Forest, then checked OpenTable for Sunday night. Gabriel's had nothing between 5:00 and 9:30, and the Lake Forest place had a prix fixe for $85 a person that felt like a lot for a Sunday. Froggy's had 7:00 and the regular menu, so I took it. The whole thing took about ten minutes and I got an email confirmation, which is the part I like, since I have called restaurants before and found no record of us at the door.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7585,7 +7587,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Hot, fast, and they got it right.  That's all I ask at 7:15 in the morning.</t>
+          <t>Reservation made in ten minutes, at the place we actually prefer, with a confirmation in writing. The hard part was remembering to do it before the week got away from me.</t>
         </is>
       </c>
     </row>
@@ -7601,41 +7603,41 @@
         </is>
       </c>
       <c r="C144" s="1" t="n">
-        <v>40212</v>
+        <v>40215</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>American Girl doll clothes</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Jewel gas station</t>
+          <t>ebay</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>fill up, Jewel</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Filled up the minivan at the Jewel gas station because I had 20 cents off a gallon from my grocery points.  $2.69 instead of $2.89, which on 18 gallons is almost $4.  Mark laughs at me but it adds up!!</t>
+          <t>Emma wants an outfit for her American Girl doll and they are $28 in the catalog which is insane for doll clothes.  Saturday night I looked on ebay and there are tons of homemade ones for $8 to $12.  I put a couple on my watch list, one auction ends Tuesday.  Didn't bid yet, I want to see how high they go first.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Free money basically.  I was buying the groceries anyway.</t>
+          <t>Should be able to get her something cute for a third of the catalog price.  We'll see Tuesday.</t>
         </is>
       </c>
     </row>
@@ -7651,31 +7653,31 @@
         </is>
       </c>
       <c r="C145" s="1" t="n">
-        <v>40210</v>
+        <v>40214</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>groceries</t>
+          <t>birthday present for my nephew</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Jewel</t>
+          <t>amazon.com</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Jewel, groceries for the week</t>
+          <t>Lego City fire truck set, amazon.com</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Went to Jewel after my shift ended at 1:00.  I had the ad from Sunday's paper and my list and I stuck to it for the most part.  Boneless chicken was $1.79 a pound so I bought three packs and froze two, and the Jewel brand cereal was buy one get one so the boys are set for the week.  Used my Preferred card and the $3 off coupon they printed on my receipt last time.  The store is nice and quiet at 1:30 on a Monday, after 4:00 it's a zoo.  $112 total which is about normal for us with three kids who eat like linebackers.</t>
+          <t>My nephew Connor turns 6 next weekend and my sister said he is into Legos.  Got on Amazon Friday morning before work and found a Lego City fire truck set for $34.99 with free super saver shipping, and I had it sent straight to her house in Naperville so I don't have to haul it to the party.  Took me 10 minutes.  Read a couple reviews to make sure it wasn't too hard for a 6 year old.  Amazon says it will be there by Thursday.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7685,7 +7687,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Got everything on my list, most of it on sale, and in and out in 40 minutes.  Can't complain about that!</t>
+          <t>Fast, free shipping, and one less thing to carry.  Amazon spoils me.</t>
         </is>
       </c>
     </row>
@@ -7701,41 +7703,36 @@
         </is>
       </c>
       <c r="C146" s="1" t="n">
-        <v>40211</v>
+        <v>40214</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>hockey skates for Ryan</t>
+          <t>Blackhawks tickets</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>hockeygiant.com, hockeymonkey.com, Dick's Sporting Goods</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>Bauer skates at Dick's</t>
+          <t>ticketmaster, stubhub</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Ryan's skates are two sizes too small (he grew again) and his coach said he really needs new ones before playoffs.  I looked at hockeygiant.com and hockeymonkey.com Monday night to figure out what a decent pair costs and honestly the prices made me a little sick, $150 and up for the Bauer ones he wanted.  I also checked the Play It Again Sports website for used but you really need to try skates on.  Tuesday after school we went to Dick's and the kid there was great, he had Ryan try on 4 pairs and we ended up with Bauer Supreme One05 marked down to $99.99 from $139.99.  Mark had printed a $10 off $50 coupon from thier email too.  Ryan skated in them Tuesday night and said they felt "awesome" so I guess we did ok.</t>
+          <t>Tyler's birthday is in March and all he wants is to go to a Blackhawks game.  I looked on ticketmaster at lunch and everything was gone except the 300 level at $65 each, then I looked on stubhub and it was worse, $90 and up for the same seats plus fees.  For 2 tickets we're talking $150+ to sit in the rafters.  Didn't buy.  Mark thinks his buddy at work has season tickets and might sell him a pair so we'll try that first.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>I did my homework online so I knew what a fair price was, then got a better one in the store with the coupon.  Plus someone who knew what they were doing fit him.  Worth the trip.</t>
+          <t>Not thrilled with the prices but at least I know what we're dealing with.  Hockey is expensive this year with the team doing so well.</t>
         </is>
       </c>
     </row>
@@ -7751,41 +7748,41 @@
         </is>
       </c>
       <c r="C147" s="1" t="n">
-        <v>40215</v>
+        <v>40212</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>jeans for Tyler, a sweater for me</t>
+          <t>book for school</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kohls</t>
+          <t>borders.com, amazon</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Kohls - 2 pr Levis for Tyler, a sweater for me, socks</t>
+          <t>nothing yet</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>I had $20 in Kohl's cash from the stuff I bought the kids after Christmas that expired Sunday, plus a 15% off coupon from the mailer, so Saturday morning Tyler and I went to the Kohl's in Gurnee.  He needed jeans, he is 15 and 6 feet tall and all of his are floods.  Levi's 514 were on sale for $29.99 from $44 so we got two pair.  I found a Croft &amp; Barrow sweater on the clearance rack for $11.20 and a 6 pack of socks for the boys.  With the Kohl's cash and the 15% I paid $62 for everything and the receipt said I saved $87.  I love it when the receipt says you saved more than you spent!!  The line was long like it always is on a Saturday, maybe 10 minutes, but they had alot of registers open.</t>
+          <t>Ryan's 7th grade English class is starting The Outsiders and he needs his own copy by the 10th. I checked borders.com first since I had a 33% off coupon in my email, but it turned out the coupon was in store only and the book was $9.99 with shipping on top of that. Amazon had it for $6.99 but you need $25 for free shipping and I didn't want to add stuff just to get there. I'm going to stop at the Borders in Deerfield on the way home Friday and use the coupon, which gets it under $7 anyway. If they are out I'll have Ryan check the school library.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Saved more than I spent and Tyler has pants that fit.  Kohl's cash is the best thing they ever did, it gets me back in the store every time but I don't mind.</t>
+          <t>Didn't buy anything yet but I figured out the cheapest way to get it in about 10 minutes. A little annoyed the coupon was store only, that wasnt obvious in the email.</t>
         </is>
       </c>
     </row>
@@ -7801,36 +7798,41 @@
         </is>
       </c>
       <c r="C148" s="1" t="n">
-        <v>40220</v>
+        <v>40219</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>lacrosse stick for Tyler</t>
+          <t>books and printer ink</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Shopped offline and didn't purchase</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Sports Authority</t>
+          <t>amazon.com</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Diary of a Wimpy Kid, Percy Jackson book, HP ink - amazon</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Tyler's lacrosse season starts in March and his stick cracked.  Thursday after work I drove to the Sports Authority in Gurnee since I was over there anyway.  They had moved the lacrosse stuff to a tiny corner in the back and there were exactly 3 sticks, all $90 and up, and nobody around to ask.  I stood there for 15 minutes and finally found a kid stocking shelves who said that was all they had and the ridiculus price is the price.  Left with nothing.  I'll look at lacrossemonkey.com or ask the coach where the other parents go.</t>
+          <t>SNOW DAY.  All three kids home, Mark worked from home, and by 10 am everyone was allready bored and fighting.  Emma has been begging for the newest Diary of a Wimpy Kid (Dog Days) and Ryan wants the last Percy Jackson book since the movie comes out Friday, so I got on Amazon and ordered both, $8.99 and $7.99, and threw in the black ink cartridge for the printer since Tyler has a paper due and we were almost out.  Total was over $25 so free shipping.  I told the kids the books are their reward for not killing each other.  Amazon says 5 to 9 days with the free shipping but it's usually faster than that.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Not at all satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Total waste of 45 minutes and the gas to get there.  Nobody to help, no selection, and when I did find someone he could not have cared less.  I'll order online next time and skip that store.</t>
+          <t>Didn't have to go out in a foot of snow, free shipping, and the kids had something to look forward to.  Amazon in a blizzard is a wonderful thing.</t>
         </is>
       </c>
     </row>
@@ -7846,11 +7848,11 @@
         </is>
       </c>
       <c r="C149" s="1" t="n">
-        <v>40218</v>
+        <v>40210</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>milk, bread, batteries before the storm</t>
+          <t>coffee</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -7860,27 +7862,27 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Jewel</t>
+          <t>Dunkin Donuts</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Jewel - milk, bread, eggs, D batteries, hot chocolate</t>
+          <t>medium coffee, Dunkin Donuts</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>They were saying 12 inches or more starting Tuesday afternoon so I ran to Jewel at 11 in the morning and so did everyone else in Grayslake.  Got 2 gallons of milk, bread, eggs, D batteries for the flashlights and hot chocolate for the kids.  The bread aisle was picked over already and the lines were 6 deep at every register.  Took 35 minutes for 8 things.</t>
+          <t>Quick stop at the Dunkin on Rt. 83 on my way in to the office.  Medium coffee with cream, $1.89.  Drive thru line was 6 cars but it moved fast.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>I got what we needed before the storm but it was a madhouse.  Not Jewel's fault really, it's the weather people who get everybody worked up.</t>
+          <t>Hot, fast, and they got it right.  That's all I ask at 7:15 in the morning.</t>
         </is>
       </c>
     </row>
@@ -7896,11 +7898,11 @@
         </is>
       </c>
       <c r="C150" s="1" t="n">
-        <v>40218</v>
+        <v>40213</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>photo book for my mom</t>
+          <t>comforter set for Emma's room</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -7910,17 +7912,17 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Shutterfly</t>
+          <t>target.com</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>8x8 photo book, Shutterfly</t>
+          <t>Xhilaration comforter set and a desk lamp from target.com</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>I've been meaning to make my mom a photo book of the kids from Christmas and I had a 20% off code from Shutterfly that expired the 10th.  Did it Tuesday night while the snow came down.  Took me almost 2 hours to lay it out, the site kept freezing with that many pictures loaded, but I got it done.  The 8x8 book was $29.99 minus the 20% plus $5 shipping.  It will be late for Valentine's but she won't mind.</t>
+          <t>Emma is 10 and has decided the Disney princess bedding is for babies. We looked at the Target in Vernon Hills a couple of weeks ago and she liked a purple and teal Xhilaration set that was $59.99 in the store. I checked target.com Thursday and the same set was $49.99 online, plus free shipping on orders over $50, so I added a $12 desk lamp she needed anyway. Ordered it on my lunch break. It is supposed to come in 5 to 7 days which is fine, she can live with the princesses another week.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7930,7 +7932,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>The book came out really cute and I beat the coupon deadline.  The site was slow but I was watching the snow anyway so I wasn't in a hurry.</t>
+          <t>Ten dollars cheaper than the store for the exact same thing, and I didn't have to drag it through the parking lot. The lamp was basically free with the shipping math.</t>
         </is>
       </c>
     </row>
@@ -7946,41 +7948,41 @@
         </is>
       </c>
       <c r="C151" s="1" t="n">
-        <v>40216</v>
+        <v>40212</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>pizza for the Super Bowl</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>papajohns.com</t>
+          <t>Jewel gas station</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>3 large pizzas and breadsticks, Papa Johns</t>
+          <t>fill up, Jewel</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>We had Mark's brother's family over for the Super Bowl so that was 9 people.  I ordered online from Papa John's for the first time because they had a special on the website, 3 large one toppings for $30, and you could pick the delivery time.  I set it for 5:15 so it would come before kickoff.  It came at 5:40 and one was supposed to be sausage and was pepperoni, but nobody really cared, the kids ate it anyway.  The online ordering was easy and I didn't have to sit on hold which on Super Bowl Sunday is a big deal.</t>
+          <t>Filled up the minivan at the Jewel gas station because I had 20 cents off a gallon from my grocery points.  $2.69 instead of $2.89, which on 18 gallons is almost $4.  Mark laughs at me but it adds up!!</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Good deal and I liked ordering online, but it was late and one pizza was wrong.  Not the end of the world but not perfect either.</t>
+          <t>Free money basically.  I was buying the groceries anyway.</t>
         </is>
       </c>
     </row>
@@ -7996,11 +7998,11 @@
         </is>
       </c>
       <c r="C152" s="1" t="n">
-        <v>40211</v>
+        <v>40210</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>groceries</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -8010,17 +8012,17 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Jewel</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>amoxicillin for Emma, Walgreens</t>
+          <t>Jewel, groceries for the week</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Emma woke up with an earache and the pediatrician called in amoxicillin to the Walgreens on Washington St.  I don't work Tuesdays so I took her in and then picked it up through the drive thru after her appointment.  They had it ready in 20 minutes like they said and it was a $10 copay.  Also grabbed a box of kleenex and some Gatorade for her since she wasn't eating anything.</t>
+          <t>Went to Jewel after my shift ended at 1:00.  I had the ad from Sunday's paper and my list and I stuck to it for the most part.  Boneless chicken was $1.79 a pound so I bought three packs and froze two, and the Jewel brand cereal was buy one get one so the boys are set for the week.  Used my Preferred card and the $3 off coupon they printed on my receipt last time.  The store is nice and quiet at 1:30 on a Monday, after 4:00 it's a zoo.  $112 total which is about normal for us with three kids who eat like linebackers.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -8030,7 +8032,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>The drive thru is a life saver with a sick kid in the back seat.  Fast, and the pharmacist came to the window herself to tell me to give it with food.</t>
+          <t>Got everything on my list, most of it on sale, and in and out in 40 minutes.  Can't complain about that!</t>
         </is>
       </c>
     </row>
@@ -8046,31 +8048,31 @@
         </is>
       </c>
       <c r="C153" s="1" t="n">
-        <v>40217</v>
+        <v>40211</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>science fair supplies</t>
+          <t>hockey skates for Ryan</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Michaels</t>
+          <t>hockeygiant.com, hockeymonkey.com, Dick's Sporting Goods</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Michaels - tri-fold board, stick on letters, glue sticks</t>
+          <t>Bauer skates at Dick's</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Ryan's science fair project is due the 19th and of course we had nothing.  Went to the Michaels in Gurnee after his hockey practice and got the tri-fold poster board, a pack of stick on letters and glue sticks.  I had a 40% off one item coupon from the Sunday paper and used it on the board.  Ryan wanted the fancy black board and I said white is fine, it's a project about which paper towel is most absorbent, not the Nobel prize.</t>
+          <t>Ryan's skates are two sizes too small (he grew again) and his coach said he really needs new ones before playoffs.  I looked at hockeygiant.com and hockeymonkey.com Monday night to figure out what a decent pair costs and honestly the prices made me a little sick, $150 and up for the Bauer ones he wanted.  I also checked the Play It Again Sports website for used but you really need to try skates on.  Tuesday after school we went to Dick's and the kid there was great, he had Ryan try on 4 pairs and we ended up with Bauer Supreme One05 marked down to $99.99 from $139.99.  Mark had printed a $10 off $50 coupon from thier email too.  Ryan skated in them Tuesday night and said they felt "awesome" so I guess we did ok.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -8080,7 +8082,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>40% coupon, in and out in 15 minutes, and Ryan has no excuses now.</t>
+          <t>I did my homework online so I knew what a fair price was, then got a better one in the store with the coupon.  Plus someone who knew what they were doing fit him.  Worth the trip.</t>
         </is>
       </c>
     </row>
@@ -8096,31 +8098,31 @@
         </is>
       </c>
       <c r="C154" s="1" t="n">
-        <v>40221</v>
+        <v>40215</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>songs for Emma's iPod</t>
+          <t>jeans for Tyler, a sweater for me</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>iTunes</t>
+          <t>Kohls</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>4 songs, iTunes</t>
+          <t>Kohls - 2 pr Levis for Tyler, a sweater for me, socks</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Emma got an iPod shuffle for Christmas and had a $10 iTunes card left from her birthday.  Friday night we sat down together and she picked 4 songs (Taylor Swift mostly) at 99 cents or $1.29.  iTunes is easy enough that she can almost do it herself now, I just have to put in the password.</t>
+          <t>I had $20 in Kohl's cash from the stuff I bought the kids after Christmas that expired Sunday, plus a 15% off coupon from the mailer, so Saturday morning Tyler and I went to the Kohl's in Gurnee.  He needed jeans, he is 15 and 6 feet tall and all of his are floods.  Levi's 514 were on sale for $29.99 from $44 so we got two pair.  I found a Croft &amp; Barrow sweater on the clearance rack for $11.20 and a 6 pack of socks for the boys.  With the Kohl's cash and the 15% I paid $62 for everything and the receipt said I saved $87.  I love it when the receipt says you saved more than you spent!!  The line was long like it always is on a Saturday, maybe 10 minutes, but they had alot of registers open.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -8130,7 +8132,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Used up a gift card, took 10 minutes, and she was dancing around the kitchen.  Easy.</t>
+          <t>Saved more than I spent and Tyler has pants that fit.  Kohl's cash is the best thing they ever did, it gets me back in the store every time but I don't mind.</t>
         </is>
       </c>
     </row>
@@ -8146,41 +8148,36 @@
         </is>
       </c>
       <c r="C155" s="1" t="n">
-        <v>40221</v>
+        <v>40220</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>spring break flights</t>
+          <t>lacrosse stick for Tyler</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped offline and didn't purchase</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>southwest.com, Expedia</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>nothing</t>
+          <t>Sports Authority</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Spring break is the last week of March and my parents want us to come down to Fort Myers.  I looked on southwest.com and Expedia Friday at lunch.  Southwest out of Midway was $159 each way per person which times 5 is over $1,500.  Driving is 20 hours but we've done it before.  Didn't book anything, Mark and I need to talk about it this weekend.  Southwest's site is easy to use at least, you can see the whole month of fares at once.</t>
+          <t>Tyler's lacrosse season starts in March and his stick cracked.  Thursday after work I drove to the Sports Authority in Gurnee since I was over there anyway.  They had moved the lacrosse stuff to a tiny corner in the back and there were exactly 3 sticks, all $90 and up, and nobody around to ask.  I stood there for 15 minutes and finally found a kid stocking shelves who said that was all they had and the ridiculus price is the price.  Left with nothing.  I'll look at lacrossemonkey.com or ask the coach where the other parents go.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Not at all satisfied</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>No decision yet but I have the numbers to show Mark.  If the fares drop a little I'll jump on it.</t>
+          <t>Total waste of 45 minutes and the gas to get there.  Nobody to help, no selection, and when I did find someone he could not have cared less.  I'll order online next time and skip that store.</t>
         </is>
       </c>
     </row>
@@ -8196,31 +8193,31 @@
         </is>
       </c>
       <c r="C156" s="1" t="n">
-        <v>40213</v>
+        <v>40218</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>used treadmill</t>
+          <t>milk, bread, batteries before the storm</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>craigslist</t>
+          <t>Jewel</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>nothing yet, still looking</t>
+          <t>Jewel - milk, bread, eggs, D batteries, hot chocolate</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Mark and I keep saying we're going to start walking in the mornings but it's 10 degrees out.  Looked on craigslist for a used treadmill in the Lake County listings.  There were a bunch, $100 to $600, but the cheap ones looked beat up in the pictures and the nice ones were in Schaumburg or the city and we don't have a truck.  I emailed one person in Round Lake about a ProForm for $175 and haven't heard back.  Still looking.</t>
+          <t>They were saying 12 inches or more starting Tuesday afternoon so I ran to Jewel at 11 in the morning and so did everyone else in Grayslake.  Got 2 gallons of milk, bread, eggs, D batteries for the flashlights and hot chocolate for the kids.  The bread aisle was picked over already and the lines were 6 deep at every register.  Took 35 minutes for 8 things.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -8230,7 +8227,7 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Craigslist is hit or miss but it's free to look.  I'd rather pay $175 than $800 at Sears for something we may not use after March, lets be honest.</t>
+          <t>I got what we needed before the storm but it was a madhouse.  Not Jewel's fault really, it's the weather people who get everybody worked up.</t>
         </is>
       </c>
     </row>
@@ -8246,41 +8243,41 @@
         </is>
       </c>
       <c r="C157" s="1" t="n">
-        <v>40221</v>
+        <v>40218</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Valentine candy for the kids</t>
+          <t>photo book for my mom</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Shutterfly</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Walgreens - 3 heart boxes, cards for the kids, bag of Hershey kisses</t>
+          <t>8x8 photo book, Shutterfly</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Friday morning before work I ran into Walgreens for the kids' Valentine candy and a card for each from Mark and me.  The Valentine aisle was pretty picked over already, half the shelves empty, but I found the little heart boxes for $2.49 and the Kisses were 2 for $5.  The cards were $3.99 each which seems like alot for something a 12 year old is going to look at for 4 seconds.  One register open and 5 people in line.</t>
+          <t>I've been meaning to make my mom a photo book of the kids from Christmas and I had a 20% off code from Shutterfly that expired the 10th.  Did it Tuesday night while the snow came down.  Took me almost 2 hours to lay it out, the site kept freezing with that many pictures loaded, but I got it done.  The 8x8 book was $29.99 minus the 20% plus $5 shipping.  It will be late for Valentine's but she won't mind.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Got it done but I should have gone last week, the good stuff was gone and the line was slow.  Lesson learned for next year.</t>
+          <t>The book came out really cute and I beat the coupon deadline.  The site was slow but I was watching the snow anyway so I wasn't in a hurry.</t>
         </is>
       </c>
     </row>
@@ -8296,11 +8293,11 @@
         </is>
       </c>
       <c r="C158" s="1" t="n">
-        <v>40219</v>
+        <v>40216</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Valentine's dinner deal</t>
+          <t>pizza for the Super Bowl</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -8310,27 +8307,27 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Groupon</t>
+          <t>papajohns.com</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Groupon for a restaurant in Libertyville</t>
+          <t>3 large pizzas and breadsticks, Papa Johns</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>My coworker Dana told me about Groupon, you get an email every day with one deal for the Chicago area.  Wednesday's deal (while we were snowed in) was $20 for $40 at a restaurant in Libertyville that Mark and I have wanted to try.  I signed up and bought it, really easy, and you just print it out.  It's good for 6 months so we'll use it for a Valentine's dinner once we can get a sitter, or more likely once the roads clear.  I never would have gone there at full price.</t>
+          <t>We had Mark's brother's family over for the Super Bowl so that was 9 people.  I ordered online from Papa John's for the first time because they had a special on the website, 3 large one toppings for $30, and you could pick the delivery time.  I set it for 5:15 so it would come before kickoff.  It came at 5:40 and one was supposed to be sausage and was pepperoni, but nobody really cared, the kids ate it anyway.  The online ordering was easy and I didn't have to sit on hold which on Super Bowl Sunday is a big deal.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Half price dinner at a nice place and I didn't even have to leave the couch.  I'm definately watching these emails now.</t>
+          <t>Good deal and I liked ordering online, but it was late and one pizza was wrong.  Not the end of the world but not perfect either.</t>
         </is>
       </c>
     </row>
@@ -8346,31 +8343,31 @@
         </is>
       </c>
       <c r="C159" s="1" t="n">
-        <v>40220</v>
+        <v>40211</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Valentine's gift for Mark</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>carsons.com, Carson Pirie Scott</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Carsons - Blackhawks fleece and a Timex watch for Mark</t>
+          <t>amoxicillin for Emma, Walgreens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>I knew Mark wanted the Blackhawks fleece pullover he saw at Carson's at Hawthorn but he wouldn't pay $60 for it.  I looked on carsons.com Wednesday night and they had a one day sale Thursday with an extra 20% coupon you print, so after work I went to the store, found the fleece on sale for $44.99, used the coupon and it came to $36.  Then I walked past the watches and they had Timex 50% off so I got him one of those too since his band broke at Christmas.  Both wrapped for free at the counter.  Spent $58 for both which is less than the fleece alone would have been last week.</t>
+          <t>Emma woke up with an earache and the pediatrician called in amoxicillin to the Walgreens on Washington St.  I don't work Tuesdays so I took her in and then picked it up through the drive thru after her appointment.  They had it ready in 20 minutes like they said and it was a $10 copay.  Also grabbed a box of kleenex and some Gatorade for her since she wasn't eating anything.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -8380,7 +8377,7 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Got him exactly what he wanted plus a bonus gift for less than I planned to spend.  Checking the website first saved me $25 easy.</t>
+          <t>The drive thru is a life saver with a sick kid in the back seat.  Fast, and the pharmacist came to the window herself to tell me to give it with food.</t>
         </is>
       </c>
     </row>
@@ -8396,11 +8393,11 @@
         </is>
       </c>
       <c r="C160" s="1" t="n">
-        <v>40213</v>
+        <v>40217</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>valentines for Emma's class, paper towels, shampoo</t>
+          <t>science fair supplies</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -8410,17 +8407,17 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Michaels</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Target - valentines, Bounty, shampoo, 2 picture frames</t>
+          <t>Michaels - tri-fold board, stick on letters, glue sticks</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Emma needs 24 valentines for her class party on the 12th so we went to the Target in Gurnee after school.  She picked the Hannah Montana ones with the little tattoos (2 boxes, $2.99 each) and I did my usual loop for the stuff we were out of, Bounty paper towels and Suave shampoo for the boys.  Target had the Bounty on sale and I printed a $1 off coupon from their website before we left.  Also found two picture frames on the clearance endcap for $3.48 that I'll use for the Shutterfly pictures for my mom.  Got out for $41 and change which for Target is a victory, I usually can't get out of there under $75.  Emma wanted a seperate box of candy to go with the cards and I said we'll get that closer to the party.</t>
+          <t>Ryan's science fair project is due the 19th and of course we had nothing.  Went to the Michaels in Gurnee after his hockey practice and got the tri-fold poster board, a pack of stick on letters and glue sticks.  I had a 40% off one item coupon from the Sunday paper and used it on the board.  Ryan wanted the fancy black board and I said white is fine, it's a project about which paper towel is most absorbent, not the Nobel prize.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -8430,7 +8427,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Got what we came for plus a couple clearance finds, and Emma was thrilled with her valentines.  Target late afternoon on a weekday is nice and empty.</t>
+          <t>40% coupon, in and out in 15 minutes, and Ryan has no excuses now.</t>
         </is>
       </c>
     </row>
@@ -8446,36 +8443,41 @@
         </is>
       </c>
       <c r="C161" s="1" t="n">
-        <v>40212</v>
+        <v>40221</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Wii Fit</t>
+          <t>songs for Emma's iPod</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>amazon.com, target.com, walmart.com, bestbuy.com</t>
+          <t>iTunes</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>4 songs, iTunes</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Tyler and Emma have been begging for the Wii Fit Plus since Christmas and I keep saying we'll see.  Spent my lunch looking at it on Amazon, target.com, walmart.com and Best Buy's site and it is $99 everywhere, nobody is discounting it.  Read some of the Amazon reviews and most people like it.  I'm going to wait, I have a feeling it goes on sale around spring break or I'll see a Target coupon.  Didn't buy anything.</t>
+          <t>Emma got an iPod shuffle for Christmas and had a $10 iTunes card left from her birthday.  Friday night we sat down together and she picked 4 songs (Taylor Swift mostly) at 99 cents or $1.29.  iTunes is easy enough that she can almost do it herself now, I just have to put in the password.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>I know what it costs now so I'll know a good deal when I see one.  No rush.</t>
+          <t>Used up a gift card, took 10 minutes, and she was dancing around the kitchen.  Easy.</t>
         </is>
       </c>
     </row>
@@ -8491,11 +8493,11 @@
         </is>
       </c>
       <c r="C162" s="1" t="n">
-        <v>40217</v>
+        <v>40221</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>work shoes</t>
+          <t>spring break flights</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -8505,34 +8507,34 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Zappos, amazon.com</t>
+          <t>southwest.com, Expedia</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Did not purchase</t>
+          <t>nothing</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>My Danskos are shot, I'm on my feet all day at the dental office and these are 4 years old.  Looked at Zappos Monday night and they have every color but they're $120 to $130 and nothing on sale.  Amazon was the same price.  I was really hoping to find last year's color on clearance somewhere.  I'll keep looking, maybe 6pm.com or the outlet at Gurnee Mills.</t>
+          <t>Spring break is the last week of March and my parents want us to come down to Fort Myers.  I looked on southwest.com and Expedia Friday at lunch.  Southwest out of Midway was $159 each way per person which times 5 is over $1,500.  Driving is 20 hours but we've done it before.  Didn't book anything, Mark and I need to talk about it this weekend.  Southwest's site is easy to use at least, you can see the whole month of fares at once.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Not satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>$125 for shoes I wear to work is hard to swallow right now, even if they do last 4 years.  Didn't find a deal so I'm still wearing the old ones.</t>
+          <t>No decision yet but I have the numbers to show Mark.  If the fares drop a little I'll jump on it.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -8541,31 +8543,31 @@
         </is>
       </c>
       <c r="C163" s="1" t="n">
-        <v>40210</v>
+        <v>40213</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>groceries</t>
+          <t>used treadmill</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Jewel</t>
+          <t>craigslist</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Jewel, groceries for the week</t>
+          <t>nothing yet, still looking</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Monday grocery run at Jewel after dropping the kids off. Had my list and the Preferred Card, used a couple of coupons from the Sunday paper. $142, about what it always is.</t>
+          <t>Mark and I keep saying we're going to start walking in the mornings but it's 10 degrees out.  Looked on craigslist for a used treadmill in the Lake County listings.  There were a bunch, $100 to $600, but the cheap ones looked beat up in the pictures and the nice ones were in Schaumburg or the city and we don't have a truck.  I emailed one person in Round Lake about a ProForm for $175 and haven't heard back.  Still looking.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8575,14 +8577,14 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Got what we needed. Chicken was on sale, which helped. Nothing special.</t>
+          <t>Craigslist is hit or miss but it's free to look.  I'd rather pay $175 than $800 at Sears for something we may not use after March, lets be honest.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -8595,22 +8597,27 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Valentine's gift for my husband</t>
+          <t>Valentine candy for the kids</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>kohls.com</t>
+          <t>Walgreens</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Walgreens - 3 heart boxes, cards for the kids, bag of Hershey kisses</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Looked on kohls.com Friday night for something for Rob for Valentine's Day.  He needs a new fleece so I was looking at the Columbia ones, $45 to $60 and nothing on sale that I could see. I have $10 in Kohl's Cash that expires Sunday, so I'll run to the store tomorrow and look at them in person instead.</t>
+          <t>Friday morning before work I ran into Walgreens for the kids' Valentine candy and a card for each from Mark and me.  The Valentine aisle was pretty picked over already, half the shelves empty, but I found the little heart boxes for $2.49 and the Kisses were 2 for $5.  The cards were $3.99 each which seems like alot for something a 12 year old is going to look at for 4 seconds.  One register open and 5 people in line.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8620,14 +8627,14 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>I have an idea of what I'm getting and I'll use the Kohl's Cash. Would have liked to see a sale.</t>
+          <t>Got it done but I should have gone last week, the good stuff was gone and the line was slow.  Lesson learned for next year.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Robin</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -8636,11 +8643,11 @@
         </is>
       </c>
       <c r="C165" s="1" t="n">
-        <v>40211</v>
+        <v>40219</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>basketball shoes</t>
+          <t>Valentine's dinner deal</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -8650,17 +8657,17 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>dickssportinggoods.com, eastbay.com, zappos</t>
+          <t>Groupon</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2 pair Nike basketball shoes, dickssportinggoods.com</t>
+          <t>Groupon for a restaurant in Libertyville</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Both boys needed new basketball shoes before the Vernon Hills tournament. Ryan's have a hole, Tyler's are too small. Checked Eastbay, Zappos and Dick's online. Dick's had the Nike Hyperdunks on sale, $54.99 from $70, and free shipping over $50. Ordered a size 6 and a 6.5, same shoe, so they stop fighting over whose is whose. Should be here Friday.</t>
+          <t>My coworker Dana told me about Groupon, you get an email every day with one deal for the Chicago area.  Wednesday's deal (while we were snowed in) was $20 for $40 at a restaurant in Libertyville that Mark and I have wanted to try.  I signed up and bought it, really easy, and you just print it out.  It's good for 6 months so we'll use it for a Valentine's dinner once we can get a sitter, or more likely once the roads clear.  I never would have gone there at full price.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8670,14 +8677,14 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Two pair for about the price of one at full price, and I didn't have to drag them to the store on a school night.</t>
+          <t>Half price dinner at a nice place and I didn't even have to leave the couch.  I'm definately watching these emails now.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Robin</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -8686,43 +8693,48 @@
         </is>
       </c>
       <c r="C166" s="1" t="n">
-        <v>40212</v>
+        <v>40220</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>indoor soccer shoes</t>
+          <t>Valentine's gift for Mark</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>sportsauthority.com, soccer.com</t>
+          <t>carsons.com, Carson Pirie Scott</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Carsons - Blackhawks fleece and a Timex watch for Mark</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Indoor soccer starts in March and the boys' shoes from last year are shot. Looked on Sports Authority and soccer.com during lunch. Adidas Sambas are $55 each at both. Didn't order. Sports Authority usually sends a 20% coupon by the end of the month and I'd rather have them try them on anyway. Made a note on the calendar.</t>
+          <t>I knew Mark wanted the Blackhawks fleece pullover he saw at Carson's at Hawthorn but he wouldn't pay $60 for it.  I looked on carsons.com Wednesday night and they had a one day sale Thursday with an extra 20% coupon you print, so after work I went to the store, found the fleece on sale for $44.99, used the coupon and it came to $36.  Then I walked past the watches and they had Timex 50% off so I got him one of those too since his band broke at Christmas.  Both wrapped for free at the counter.  Spent $58 for both which is less than the fleece alone would have been last week.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Know what they cost and have a plan. No reason to pay full price three weeks early.</t>
+          <t>Got him exactly what he wanted plus a bonus gift for less than I planned to spend.  Checking the website first saved me $25 easy.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Robin</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -8731,11 +8743,11 @@
         </is>
       </c>
       <c r="C167" s="1" t="n">
-        <v>40215</v>
+        <v>40213</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>lunch</t>
+          <t>valentines for Emma's class, paper towels, shampoo</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -8745,17 +8757,17 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Panera</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Panera - 2 kids meals, 2 soups, coffee</t>
+          <t>Target - valentines, Bounty, shampoo, 2 picture frames</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Saturday: basketball game at 9, soccer scrimmage at 1. Took the boys and Dave to Panera in Vernon Hills in between. Two kids meals, two bowls of broccoli cheddar and a coffee, about $26. Line was out the door but it moved. They ate fast and were back on the field by 12:45. Beats McDonalds.</t>
+          <t>Emma needs 24 valentines for her class party on the 12th so we went to the Target in Gurnee after school.  She picked the Hannah Montana ones with the little tattoos (2 boxes, $2.99 each) and I did my usual loop for the stuff we were out of, Bounty paper towels and Suave shampoo for the boys.  Target had the Bounty on sale and I printed a $1 off coupon from their website before we left.  Also found two picture frames on the clearance endcap for $3.48 that I'll use for the Shutterfly pictures for my mom.  Got out for $41 and change which for Target is a victory, I usually can't get out of there under $75.  Emma wanted a seperate box of candy to go with the cards and I said we'll get that closer to the party.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8765,14 +8777,14 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Fast, decent food, close to both gyms. Exactly what Saturday needed.</t>
+          <t>Got what we came for plus a couple clearance finds, and Emma was thrilled with her valentines.  Target late afternoon on a weekday is nice and empty.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Robin</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -8781,48 +8793,43 @@
         </is>
       </c>
       <c r="C168" s="1" t="n">
-        <v>40219</v>
+        <v>40212</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>photo books for the coaches</t>
+          <t>Wii Fit</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Costco photo center</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>2 photo books from costco.com</t>
+          <t>amazon.com, target.com, walmart.com, bestbuy.com</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Snow day so I finally did the basketball team photo book for the coaches' end of season gift. Uploaded about 60 pictures from the season to the Costco photo site and used the 8x8 hardcover template. $19.99 each, ordered two, one for each coach. Shutterfly was running a sale too but Costco was still cheaper and I can pick them up when I'm there for groceries anyway. Took about two hours total, mostly picking pictures.</t>
+          <t>Tyler and Emma have been begging for the Wii Fit Plus since Christmas and I keep saying we'll see.  Spent my lunch looking at it on Amazon, target.com, walmart.com and Best Buy's site and it is $99 everywhere, nobody is discounting it.  Read some of the Amazon reviews and most people like it.  I'm going to wait, I have a feeling it goes on sale around spring break or I'll see a Target coupon.  Didn't buy anything.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Half the price of Shutterfly for the same book, and the other parents already paid me back. Pickup at the store, no shipping.</t>
+          <t>I know what it costs now so I'll know a good deal when I see one.  No rush.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Robin</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -8835,44 +8842,44 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>soccer gear</t>
+          <t>work shoes</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>soccer.com</t>
+          <t>Zappos, amazon.com</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>shin guards, 4 pr socks, goalie gloves at soccer.com</t>
+          <t>Did not purchase</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Travel soccer sent the equipment list for spring. Both boys need new shin guards (lost one each, naturally), socks, and Tyler needs goalie gloves this year. Went straight to soccer.com since the club uses them and the sizing chart matches. Ordered 2 pair of Adidas shin guards at $12.99, 4 pair of socks, and the Reusch gloves at $24.99. Free shipping with the club code. Twenty minutes, done.</t>
+          <t>My Danskos are shot, I'm on my feet all day at the dental office and these are 4 years old.  Looked at Zappos Monday night and they have every color but they're $120 to $130 and nothing on sale.  Amazon was the same price.  I was really hoping to find last year's color on clearance somewhere.  I'll keep looking, maybe 6pm.com or the outlet at Gurnee Mills.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Not satisfied</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>One site, one order, club discount. Everything was in stock.</t>
+          <t>$125 for shoes I wear to work is hard to swallow right now, even if they do last 4 years.  Didn't find a deal so I'm still wearing the old ones.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Robin</t>
+          <t>Margaret</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -8881,31 +8888,31 @@
         </is>
       </c>
       <c r="C170" s="1" t="n">
-        <v>40220</v>
+        <v>40221</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Valentine's cards and teacher gifts</t>
+          <t>ACT prep book</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Hallmark</t>
+          <t>amazon.com</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hallmark - 4 cards, 2 teacher mugs, candy</t>
+          <t>ACT prep book and a calculator from amazon.com</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Hit Hallmark in Vernon Hills after work for Valentine's. Cards for Dave and the boys, a mug and a bag of candy for each of the twins' teachers, and a bag of the little foil hearts for the team snack bags. The teacher mugs were $9.95 each, a little steep, but it was one stop instead of three. Cashier put the mugs in gift bags for free. In and out in 15 minutes.</t>
+          <t>Michael takes the ACT in April and his counselor recommended the Princeton Review book.  Barnes &amp; Noble had it for $21.99; Amazon had it for $14.95 with free shipping once I added the TI-30 calculator he also needs, which was less than Target's price as well.  I ordered both Friday morning before work.  I also looked at the Kaplan book, but the reviews on Amazon were better for the Princeton Review.  Katie used the same book two years ago and did well, so I did not deliberate long.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8915,14 +8922,14 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>One stop, everything done, free gift bags. Worth the few extra dollars not to run around.</t>
+          <t>The lower price and free shipping made the decision easy, and it will be here before his first practice test.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Christine</t>
+          <t>Margaret</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -8931,48 +8938,48 @@
         </is>
       </c>
       <c r="C171" s="1" t="n">
-        <v>40211</v>
+        <v>40217</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>boys clothes</t>
+          <t>black pumps</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>ebay</t>
+          <t>Nordstrom, Old Orchard</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>lot of 12 boys size 10 clothes on ebay, $26 with shipping</t>
+          <t>Cole Haan pumps at Nordstrom</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Jake is growing out of everything and I am not paying $20 a pair for jeans at Kohls. I had been watching a few ebay lots for boys size 10 all week. Won one tonight for $18.50 plus $7.50 shipping, 12 pieces, mostly Gap and Children's Place, a couple Old Navy. Pictures looked ok. I lost the first one I bid on because somebody came in at the last 10 seconds, that always drives me nuts.</t>
+          <t>I needed a pair of black pumps for a dinner Tom and I are attending next week, and the pair I have are shabby. Rather than go to Hawthorn, I drove down to Nordstrom at Old Orchard on my day off, since their shoe department is so much larger. The salesman measured my foot, which no one has done in years, and brought out five pairs in my size, including a Cole Haan with the Nike Air sole that I had not considered. They were $138, more than I had planned, but I tried on several and kept coming back to them. I also looked at the Carson's shoe sale on the way home, but nothing there was as comfortable.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Good price if everything fits and isn't stained. Won't really know until it gets here.</t>
+          <t>Real service, a good selection and a shoe I can actually walk in. I paid more than I intended, but I will wear them for years.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Christine</t>
+          <t>Margaret</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -8981,11 +8988,11 @@
         </is>
       </c>
       <c r="C172" s="1" t="n">
-        <v>40210</v>
+        <v>40213</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>groceries</t>
+          <t>cardigan</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -8995,17 +9002,17 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Aldi</t>
+          <t>Talbots</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Aldi - groceries for the week</t>
+          <t>Talbots, a cardigan and a shell</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Aldi on Monday like always. $87 for the week, including the stuff for Jake's lunches and a bag of apples for 2.49. I bring my own bags and a quarter for the cart. Mike's hours got cut again in January so Aldi is pretty much it for groceries now unless Jewel has something really good on sale. The only thing I couldnt get was the Eggo waffles Emma likes. They have a store brand but she knows the difference.</t>
+          <t>Talbots at Hawthorn had their red-line clearance going, an additional 40% off the already marked-down winter things. I went in looking for a cardigan to wear to work and found a navy one in my size that had been $89 and came to $32. The saleswoman brought me a matching shell without my asking, which I also bought. There were only two other customers in the store, so I had the fitting room to myself. I did have to dig through the racks, as the clearance was not sorted by size.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -9015,14 +9022,14 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Cheapest groceries around and I was done in 30 minutes. $87 for a family of 4 is hard to beat.</t>
+          <t>A classic cardigan at about a third of the original price, with pleasant and attentive service. I will get years out of it.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Christine</t>
+          <t>Margaret</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -9031,26 +9038,31 @@
         </is>
       </c>
       <c r="C173" s="1" t="n">
-        <v>40218</v>
+        <v>40210</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Netflix</t>
+          <t>care package for Katie</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>netflix.com</t>
+          <t>amazon.com</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>amazon.com - snacks, a book and a phone charger, shipped to Katie's dorm</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Snow day, kids home, bored out of their minds by 10am. I looked at signing up for Netflix, the $8.99 one disc at a time plan with the free trial. Looked at what they have on the watch instantly thing and it's mostly old stuff. Decided no. Between Redbox and the library DVDs we're fine and another $9 a month is another $9 a month. Put on Wii Sports instead.</t>
+          <t>Katie has midterms coming up at the U of I and I like to send a little something to her dorm.  I put together an order on Amazon with a box of Clif bars, microwave popcorn, the Jodi Picoult paperback she mentioned and a replacement charger for her phone, which she has lost for the second time.  I kept the order over $25 so the shipping was free, though that meant the slower shipping, so it will not arrive until the end of the week.  I considered packing a box myself and taking it to the post office, but by the time I bought the items and paid the postage, this was simpler.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -9060,14 +9072,14 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Talked myself out of it, which was the right call. The free trial is tempting but I know we'd forget to cancel.</t>
+          <t>It was convenient and the free shipping helped, but I would have liked it to arrive sooner. I also could not tuck in a note the way I can when I pack the box myself.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Christine</t>
+          <t>Margaret</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -9076,48 +9088,48 @@
         </is>
       </c>
       <c r="C174" s="1" t="n">
-        <v>40219</v>
+        <v>40220</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>poster board, valentines</t>
+          <t>dress shirts for my husband</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Carson's</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Walmart - poster board, glue sticks, valentines for Jake, milk</t>
+          <t>3 dress shirts at Carson's, Hawthorn</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Jake's report turned into a poster (of course) and it's due Friday now because of the snow days. Walmart in Mundelein for poster board, glue sticks and the valentines for his class. He wanted the Star Wars ones and they were sold out so he settled for Transformers. Store was packed, everyone digging out and restocking after the storm. 20 minutes in line with the 20 items or less lane closed. Grabbed milk since I was there.</t>
+          <t>Carson's sent an email about their Presidents' Day sale with a printable coupon for an extra 20% off, and I saw that the Van Heusen dress shirts Tom wears were marked down to $19.99 from $45. I checked the sizes online, then went to the store at Hawthorn rather than order, because I know how those shirts can run and I wanted to see the colors. I bought three, a white, a blue and a stripe, for about $48 after the coupon. The line at the register was the longest I have seen in months, with all the Valentine's shoppers.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Got what we needed but the line was ridiculous and they were out of the valentines he wanted. Walmart is always like that lately.</t>
+          <t>Three good shirts for roughly the price of one, and Tom will not have to go to the store himself, which he would never do.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Christine</t>
+          <t>Margaret</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -9126,48 +9138,48 @@
         </is>
       </c>
       <c r="C175" s="1" t="n">
-        <v>40216</v>
+        <v>40214</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>printer ink</t>
+          <t>Dutch oven</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>amazon, walmart.com, staples.com</t>
+          <t>Williams-Sonoma</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>nothing yet</t>
+          <t>Le Creuset Dutch oven at Williams-Sonoma, Deer Park</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Our printer is out of black ink again and Jake has a report due. HP 60 cartridge. Walmart.com is $14.97, Staples $15.99, amazon has off brand ones for $6 but the reviews say they don't always work with the printer. I'm sick of paying $15 for ink every two months, the printer only cost $39. Looked at the refill kits too. Didn't buy anything, going to see if Mike can print it at work.</t>
+          <t>I have wanted a Le Creuset Dutch oven for years and finally decided to buy one with some of my Christmas money. I compared prices on the Williams-Sonoma site, Sur La Table and Amazon, and they were essentially identical, which I gather is how that company operates. Williams-Sonoma had the 5 1/2 quart in the cherry red on sale for $199 instead of $265, and the website showed it in stock at Deer Park Town Center. I drove over Friday afternoon rather than pay to ship something that heavy. The clerk carried it out to the car for me. I made a pot roast in it that night.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Not satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Still have no ink and the report is due Tuesday. Everything is either expensive or iffy.</t>
+          <t>Checking the website first meant I knew the price and that they had it before I drove over. The sale price made it feel justified, and the pot roast was wonderful.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Christine</t>
+          <t>Margaret</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -9176,48 +9188,48 @@
         </is>
       </c>
       <c r="C176" s="1" t="n">
-        <v>40220</v>
+        <v>40219</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>restaurant deal</t>
+          <t>flowers for my mother</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Groupon</t>
+          <t>proflowers</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>tulips from proflowers for my mother</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>My sister keeps telling me about Groupon so I finally signed up for the emails. Today's deal was $20 for $40 at some Italian place in Lake Forest. Mike and I haven't been out since our anniversary, and I thought maybe for Valentines. Then I thought about it, $20 plus the tip plus a sitter is $50 we don't have for one dinner. Closed it. Also half the deals are for spas and yoga, not really my life right now.</t>
+          <t>My mother is 78 and lives alone in Rockford, and I always send her flowers for Valentine's Day since my father passed. I used ProFlowers, as I have for the last few years. I chose the pink tulips with the glass vase, $39.99, and paid a little extra to have them delivered on Friday the 12th so they would not come on the weekend, when the rates are higher. The site remembered her address and my card. It took perhaps five minutes, which was welcome on a day when the roads were a mess from the storm.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Not satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>It's a good deal for someone else. Just made me a little depressed honestly.</t>
+          <t>Simple, dependable, and the flowers have always arrived looking fresh. She called in tears last year, so I know it means a great deal to her.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Christine</t>
+          <t>Margaret</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -9226,11 +9238,11 @@
         </is>
       </c>
       <c r="C177" s="1" t="n">
-        <v>40213</v>
+        <v>40210</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>snow boots</t>
+          <t>groceries</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -9240,17 +9252,17 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Once Upon a Child</t>
+          <t>Jewel</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Sorel boots size 3 at Once Upon a Child, $12</t>
+          <t>Jewel, groceries for the week</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Jakes boots from last year are too small and the ones at Walmart are junk, they leak after a month. Took both kids to Once Upon a Child in Vernon Hills after school. They had a pair of Sorels in a 3 that looked barely worn for $12. New those are like $60. Also found a Columbia fleece for Emma for $6. The kids were climbing on the toy shelf the whole time and I had to put back a Leapster Emma found, but we got out of there in 20 minutes.</t>
+          <t>Monday is my grocery day, so I went to the Jewel on Milwaukee Avenue after my morning walk. I had gone through the Sunday ad and made my list around what was on sale, which this week was chicken breasts, strawberries and the Tropicana orange juice that Michael goes through by the gallon. I also used three of the coupons I had clipped. The store was quiet at that hour and I was in and out in about forty minutes.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -9260,14 +9272,14 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>$12 for good boots that will actually last the rest of the winter. I love that store.</t>
+          <t>I stayed on my list, saved about $18 with the sale items and coupons, and did not have to wait at the register.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Christine</t>
+          <t>Margaret</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -9276,48 +9288,48 @@
         </is>
       </c>
       <c r="C178" s="1" t="n">
-        <v>40215</v>
+        <v>40219</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Super Bowl food</t>
+          <t>guest room bedding</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Jewel</t>
+          <t>overstock.com, Bed Bath &amp; Beyond</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Jewel - chips, salsa, ground beef, pop, buns</t>
+          <t>quilt set from overstock.com</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Mike's brother and his family are coming over for the Super Bowl so I needed more than Aldi had. Jewel had Tostitos buy one get one, Pepsi 12 packs 4 for $11 and ground beef for 1.99 a pound. I had a coupon for the salsa from the Sunday paper too. $43 total and the receipt said I saved $22 so I actually read it twice. It was a zoo in there on a Saturday afternoon though. Emma knocked over a display of Valentine M&amp;Ms, so that was fun.</t>
+          <t>Katie is bringing her roommate home for spring break and the guest room comforter has seen better days.  Being snowed in, I compared quilts on the Bed Bath &amp; Beyond website and on Overstock.  Overstock had a cotton quilt set in a blue and white pattern for $64.99 with $2.95 shipping, where the comparable set at Bed Bath &amp; Beyond was $99 before my 20% coupon.  I read through the reviews, which were mostly favorable aside from a few about the colors being lighter than pictured, and ordered the Overstock set.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Saved almost as much as I spent, which is the only reason I shop at Jewel anymore. Would of been better without the crowds.</t>
+          <t>A good price, nearly free shipping and the reviews gave me confidence. I will definately know when it arrives, but I expect to be pleased.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Christine</t>
+          <t>Margaret</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -9326,48 +9338,43 @@
         </is>
       </c>
       <c r="C179" s="1" t="n">
-        <v>40221</v>
+        <v>40215</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Valentine's gift for my husband</t>
+          <t>Kindle or nook</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Walgreens photo</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>8x10 collage print of the kids, Walgreens photo, $3.99</t>
+          <t>amazon.com, barnesandnoble.com</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Didn't want to spend money on Mike for Valentines but didn't want to do nothing either. The Walgreens website lets you make a collage from your pictures, so I did one with the kids from the sledding pictures the day of the storm. 8x10 was 3.99 and I had a 20% off code from an email. Ordered it online and picked it up at the Walgreens on Route 83 an hour later, paid at the counter. Grabbed a frame at Dollar Tree on the way home. Jake signed the back.</t>
+          <t>Tom's sister has a Kindle and raves about it, so I spent some time Saturday morning reading about the Kindle on Amazon and the new nook on the Barnes &amp; Noble site. They are both $259, which seems like a great deal of money for something to read a book on. The reviews for the nook mentioned it being slow to turn pages. I did not order one. I will keep it in mind for Tom's birthday in April, when perhaps the prices will have come down.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Under $5 for something he'll actually like better than a tie. Ready in an hour, no waiting.</t>
+          <t>I learned what I wanted to know. There is no hurry, and I would rather wait and see whether the price drops.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Christine</t>
+          <t>Margaret</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -9376,48 +9383,48 @@
         </is>
       </c>
       <c r="C180" s="1" t="n">
-        <v>40212</v>
+        <v>40218</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Valentine's party supplies</t>
+          <t>spring tops</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Dollar Tree</t>
+          <t>chicos.com</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Dollar Tree - valentines, heart stickers, plates, napkins, 2 bags of candy</t>
+          <t>nothing yet</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>I got stuck being the room mom for Emma's kindergarten Valentine party. Went to the Dollar Tree in Mundelein with the list from the teacher. Got paper plates and napkins with hearts, foam heart stickers for the craft, 2 bags of conversation hearts and a box of valentines for Emma to fill out (she wanted the Hannah Montana ones, fine). 9 things, $9 and some tax. I looked at the same stickers at Target last week and they were 3.99 a pack.</t>
+          <t>With the snow coming down all day and school already called off for tomorrow, I spent an hour on the Chico's website with a glass of wine. They had sent an email about their new spring arrivals and a 20% off coupon for Passport members. I put two tops and a pair of their Travelers pants in my cart, nearly $160 with the discount, and then closed the browser. I have enough clothes, and I would rather see the colors in person at the store in Deer Park. Michael and Tom were watching the hockey game and did not notice I was shopping, which is probably for the best.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Everything on the list for under 10 bucks. The other moms can chip in for the juice boxes.</t>
+          <t>A pleasant way to pass a snowy evening, and I did not spend any money. The coupon is good through the end of the month.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Christine</t>
+          <t>Margaret</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -9426,48 +9433,48 @@
         </is>
       </c>
       <c r="C181" s="1" t="n">
-        <v>40214</v>
+        <v>40216</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Wimpy Kid book</t>
+          <t>statistics textbook</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Shopped offline and didn't purchase</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Borders</t>
+          <t>half.com, Chegg, amazon.com</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>nothing - put it on hold at the library instead</t>
+          <t>used textbook from half.com</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Jake wanted the new Diary of a Wimpy Kid book (Dog Days) so we stopped at Borders in Vernon Hills on the way home. $13.95. I let him read a few pages in the store and then told him no, we'd get it from the library. He pouted. We went to the Fremont library and they have 4 copies but all were checked out, so I put a hold on it, he's 6th in line. Figure 3 weeks. I'm not spending $14 on a book he'll finish in 2 days.</t>
+          <t>Katie called in a bit of a panic because she needs a statistics textbook for a class she added late, and the campus bookstore wants $148 for it. I had her read me the ISBN and I looked it up on half.com, Chegg and Amazon. Chegg would rent it for $52 for the semester; half.com had a used copy in "good" condition for $41 plus $3.99 shipping. I bought the used one, since she can sell it back in May. It will ship directly to her dorm.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Didn't spend the money. He'll live. The library hold system works fine, it's just slow.</t>
+          <t>Less than a third of the bookstore price, and it took ten minutes on a Sunday morning. Katie was relieved.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Christine</t>
+          <t>Margaret</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -9476,48 +9483,48 @@
         </is>
       </c>
       <c r="C182" s="1" t="n">
-        <v>40217</v>
+        <v>40220</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>winter jacket for Jake</t>
+          <t>Valentine's cards and candy</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>ebay</t>
+          <t>Hallmark, Fannie May</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>boys Columbia jacket on ebay, $22</t>
+          <t>cards at Hallmark; Pixies, Mint Meltaways and Trinidads at Fannie May</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Won a Columbia winter jacket for Jake on ebay, size 10/12, $15 plus $7 shipping. Listing said "excellent used condition." It came Thursday and the zipper is seperated at the bottom and won't zip up past halfway, which is the whole point of a winter coat. There's also a stain on the sleeve that wasn't in the pictures. I emailed the seller twice, nothing. Opened a case with ebay but I'm not holding my breath over $22. Should have just gone to Once Upon a Child where I can look at it first.</t>
+          <t>Valentine's errands. I stopped at the Hallmark in the Libertyville shopping center for cards for Tom, Michael, Katie and my mother, and then went next door to Fannie May. Tom gets a box of Pixies every year and Michael gets the Mint Meltaways, and Katie's box of Trinidads will go in the mail tomorrow. The Hallmark cards were $4 and $5 apiece, which always surprises me, but I like to take my time choosing them. The young woman at Fannie May wrapped Katie's box in tissue for shipping without my asking.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Not at all satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>Wasted $22 we don't have on a coat he can't wear. The seller won't answer and now I have to deal with ebay's dispute thing.</t>
+          <t>Both stores had exactly what I came for, I was done in half an hour and the people at Fannie May are always lovely.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Gail</t>
+          <t>Margaret</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -9526,48 +9533,48 @@
         </is>
       </c>
       <c r="C183" s="1" t="n">
-        <v>40211</v>
+        <v>40212</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>driving school</t>
+          <t>Valentine's gift for Tom</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>topdriver.com</t>
+          <t>Orvis, LL Bean, Brookstone</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>behind the wheel lessons, Top Driver</t>
+          <t>Did not purchase</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Megan turned 16 in January and the State of Illinois would like her to have six hours of behind the wheel instruction from a professional before she is allowed to terrify the rest of us. The high school program has a waiting list until summer, so I signed her up with Top Driver online. $395 for the classroom and driving package. The school newsletter had a $25 off code which I found after I'd already typed my credit card in, so I backed up and did it again. I'd like to say I shopped around but there are two driving schools within a reasonable distance and the other one's website looked like it was built in 1997.</t>
+          <t>Tom is impossible to shop for. I looked through the Orvis and L.L. Bean sites for a nice flannel shirt or a fleece vest, and then at Brookstone for one of those gadgets he would never buy himself. Everything was either $90 for a shirt or something he does not need. I had a cup of tea and gave up for the night. He will probably end up with a card and dinner at Tavern in Libertyville, which, to be fair, is what he would choose anyway.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Not satisfied</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>It's a lot of money to pay someone to sit in a car with my daughter, but it's required and the signup took five minutes. The $25 off made me feel slightly less held up.</t>
+          <t>Over an hour on three websites and nothing to show for it. The prices on the clothing were more than I want to spend on a Valentine's gift.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Gail</t>
+          <t>Margaret</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -9576,48 +9583,43 @@
         </is>
       </c>
       <c r="C184" s="1" t="n">
-        <v>40218</v>
+        <v>40211</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>floor mats for the Camry</t>
+          <t>winter coat for my son</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>rubber all weather floor mats, Amazon</t>
+          <t>nordstrom.com, macys.com, landsend.com</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Megan is inheriting the 2002 Camry when she gets her license, and between a teenager and a Chicago winter the carpet mats have no chance. I looked at the WeatherTech ones first since everybody raves about them, but they were $90 and this is a car with 140,000 miles on it. Amazon had a set of rubber all weather mats for $34.95 with free shipping and about 200 reviews, most of them from people in states with actual weather. Ordered them from the couch Tuesday night while the snow came down and Dave shoveled. It seemed like the right division of labor.</t>
+          <t>Michael has outgrown his winter coat, again, and refuses to wear the one Tom offered him. I spent part of the evening looking at the North Face jackets on Nordstrom's site and at Macy's, and then at the Lands' End squall parka, which is less expensive and would probably last longer. The North Face is what he wants, of course, at $199. I did not order anything. I want him to try one on, and I suspect Nordstrom will mark the winter coats down further by the end of the month.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>A third of the price of the fancy ones, free shipping, and I didn't have to leave the house in a blizzard. If they curl up in the sun I'll report back.</t>
+          <t>I did not buy anything, but I now know the prices and what the choices are, so a trip to the store will be quicker.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Gail</t>
+          <t>Maureen</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -9626,11 +9628,11 @@
         </is>
       </c>
       <c r="C185" s="1" t="n">
-        <v>40213</v>
+        <v>40210</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>groceries</t>
+          <t>care package for my daughter at college</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -9640,17 +9642,17 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Trader Joe's</t>
+          <t>Target, the post office</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Trader Joe's, snacks, frozen stuff, wine</t>
+          <t>Target - cold medicine, Easy Mac, popcorn, Dove hearts, socks; flat rate box at the post office</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Thursday Trader Joe's run in Northbrook. I go for the frozen orange chicken, the pita chips and the two dollar wine (two ninety nine here, Illinois gets everything last), and I come out with $78 of things I didn't know I needed. This week it was a bag of dark chocolate peanut butter cups that did not make it to the car intact. Jack has decided he only eats their mini pizzas, which is fine, they're cheap. The lot was its usual demolition derby but the checkout guy was cheerful and bagged everything so the eggs were on top for once.</t>
+          <t>My oldest is a sophomore at Iowa and she has had a cold for two weeks (she says it's a cold, I say go to student health). So Monday I did a care package. Went to Target in Vernon Hills and bought DayQuil, NyQuil, Ricola, a box of the Easy Mac she likes, microwave popcorn, a bag of Dove hearts for Valentine's, and a 6-pack of socks because for some reason she can never find socks. I wanted to throw in Girl Scout cookies but those don't come till March. Then over to the post office for a medium flat rate box -- $10.70 to ship no matter how much I cram in, and believe me I crammed. Her roommate will probably eat half of it but that's fine.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -9660,14 +9662,14 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Cheap, quick, nobody in my family complains about anything from there. The peanut butter cups alone were worth the trip.</t>
+          <t>Two stops and it went out the same day. For about $45 total I get to feel like I'm doing something for her from 250 miles away, which is really what a care package is for.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Gail</t>
+          <t>Maureen</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -9676,11 +9678,11 @@
         </is>
       </c>
       <c r="C186" s="1" t="n">
-        <v>40220</v>
+        <v>40215</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>towels and a shower caddy</t>
+          <t>laptop for my college daughter</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -9690,17 +9692,17 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>bedbathandbeyond.com, Bed Bath &amp; Beyond in Vernon Hills</t>
+          <t>bestbuy.com, dell.com, cnet</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>4 bath towels and a shower caddy at Bed Bath &amp; Beyond</t>
+          <t>Toshiba Satellite laptop and a case at Best Buy</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>The kids' bathroom towels have reached the texture of cardboard and the shower caddy rusted through, which I discovered when it fell on Jack. I checked the Bed Bath &amp; Beyond site Wednesday night to see what they had and what it cost, then went to the Vernon Hills store Thursday after the roads were plowed because I had two of the 20% off coupons in the kitchen drawer and they are only good in the store. Got four bath towels in a gray that will hide everything and a stainless caddy that hangs from the shower head. One coupon per item in theory, but the cashier took both without blinking. $64 before coupons, $51 after.</t>
+          <t>The laptop my sophomore took to college finally died (it was four years old and had been dropped more than once). I spent a couple evenings this week on bestbuy.com and dell.com and reading the cnet reviews. I know just enough about computers to be dangerous, so I had my husband look too. We narrowed it down to a Toshiba Satellite with Windows 7 for $549 that was in the Best Buy ad this week, and a Dell that was about the same but would take two weeks to ship. Saturday we drove to Best Buy in Vernon Hills, the kid in the computer department was fine, didn't push the extended warranty too hard when I said no, and we were out in 30 minutes. My daughter will pick it up when she's home for Presidents Day. I did buy a case for it, $29.99, which I probably could have gotten cheaper online but at that point I just wanted to be done.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -9710,14 +9712,14 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Knew what I wanted before I walked in, coupons worked, in and out in 20 minutes. The towels are already softer than the old ones and they've only been washed once.</t>
+          <t>Doing the homework online first meant I walked in knowing exactly what I wanted and what it should cost, and that is the only way I can stand Best Buy. She gets a decent computer and we stayed under $600 with the case.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Tracy</t>
+          <t>Maureen</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -9726,48 +9728,43 @@
         </is>
       </c>
       <c r="C187" s="1" t="n">
-        <v>40215</v>
+        <v>40212</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>bulk groceries, paper goods</t>
+          <t>prom dress (just looking)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Costco</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>Costco - paper towels, chicken, cheese, cereal, milk, dishwasher tabs, Gatorade</t>
+          <t>promgirl.com, davidsbridal.com, nordstrom.com, macys.com</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Saturday morning Costco in Mettawa, we go every other weekend.  My husband takes the kids to the samples and I do the actual shopping.  Usual list: paper towels, toilet paper, the big pack of chicken breasts, string cheese, milk, cereal and dishwasher tablets.  Also a case of Gatorade for Jack's basketball.  $218.  Checkout is always fast there, I don't know how they do it with those lines.</t>
+          <t>Prom is not until May but my senior has informed me that all her friends are already looking, so Wednesday night the two of us sat on the couch with the laptop. (I should say she sat with the laptop and I was allowed to watch.) We looked at promgirl.com, David's Bridal, Nordstrom and Macy's. Her taste runs to long, strapless, and about $300 more than I had in mind. Nordstrom had a couple of BCBG ones she liked around $250. Macy's had similar for $150 but she says those are the ones everyone will have. I said nobody is buying anything online without trying it on first, so this was strictly research. She has a list going on a sticky note on her mirror. We'll hit Hawthorn or Old Orchard in March when there is more in the stores.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>One trip covers two weeks of the boring stuff and the per unit prices beat Jewel by a lot.  In and out in 45 minutes including samples.</t>
+          <t>Nothing bought, nothing lost. It was nice to do it together without arguing, and now I know what the prices look like so I'm not shocked in March.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Tracy</t>
+          <t>Maureen</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -9776,26 +9773,31 @@
         </is>
       </c>
       <c r="C188" s="1" t="n">
-        <v>40217</v>
+        <v>40214</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>flat iron</t>
+          <t>Sam's Club run</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>amazon.com, folica.com</t>
+          <t>Sam's Club</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Sam's - paper towels, toilet paper, chicken, cereal, Tide, Gatorade</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>My flat iron died.  Looked at Amazon and folica.com during lunch.  The one everyone recommends (CHI) is $90 to $100 and the reviews are all over the place, half say it's great and half say it broke after six months.  The cheaper ones have the same problem.  I closed the browser.  I'll ask my stylist what she uses and come back to it.</t>
+          <t>Friday afternoon Sam's Club trip. I go about every three weeks and buy the things we go through at a ridiculous rate with three kids (well, two at home now, but the 8th grader eats like three). The 30-roll paper towels, the big Tide, two of the double boxes of Cheerios, the 10 pound bag of chicken breasts, and a case of Gatorade for my son's basketball. I had my list but still came out at $212, there is always something -- this time it was a 3-pack of Crest and a book for me. The lines were long, only three registers open on a Friday afternoon, and the cart was so heavy I needed my son to unload it.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -9805,14 +9807,14 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Didn't waste money on something with 2 star reviews.  I'll get a real recommendation first.</t>
+          <t>The prices are good and I know they are good, that's why I go. But 25 minutes in line and a $200 bill never feels great, even when it's all stuff we need.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Tracy</t>
+          <t>Maureen</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -9821,48 +9823,48 @@
         </is>
       </c>
       <c r="C189" s="1" t="n">
-        <v>40220</v>
+        <v>40219</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Flip video camera</t>
+          <t>science fair supplies</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>bestbuy.com, amazon.com</t>
+          <t>Michaels, Walgreens</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Flip Ultra camcorder, Best Buy in Vernon Hills</t>
+          <t>Walgreens - 2 sheets of poster board (not the tri-fold), glue stick, markers</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Sophie's class play is next week and our camcorder is from 2003 and takes tapes.  Compared the Flip Ultra on bestbuy.com and Amazon at lunch, same price, $149.  Best Buy had it in stock at the Vernon Hills store for in-store pickup, so I reserved it online and grabbed it on the way home.  Took 4 minutes at the pickup counter.  I would have ordered from Amazon but I wanted it in hand before the weekend so Jack could figure it out for me.</t>
+          <t>The science fair is Friday and my 8th grader announced Wednesday morning, with school cancelled for the snow, that he needs a tri-fold display board. Of course he does. I drove to Michaels in Mundelein on roads that were honestly not good and they were out of the tri-fold boards. Completely out. The girl at the register said they "might get some Friday" and went back to her conversation. So I went over to Walgreens, which had regular poster board but not the tri-fold, and bought two sheets and told him he'd be taping them together. He was not thrilled. Neither was I. I know, I know, I should have asked him about this a week ago, but he definately should have told me too.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Not at all satisfied</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Same price as online, no shipping, and it was waiting for me.  In-store pickup is the only reason I still go into a Best Buy.</t>
+          <t>Risked the roads for nothing, the Michaels clerk could not have cared less, and the project is going to look like two pieces of poster board taped together because that's what it is.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Tracy</t>
+          <t>Maureen</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -9871,11 +9873,11 @@
         </is>
       </c>
       <c r="C190" s="1" t="n">
-        <v>40219</v>
+        <v>40217</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>groceries delivered</t>
+          <t>Valentine's dinner</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -9885,34 +9887,34 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Peapod</t>
+          <t>Groupon</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Peapod - groceries</t>
+          <t>Groupon - $50 at an Italian restaurant in Lake Forest for $25</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>With the storm I worked from home Wednesday and the kids were off school.  I had placed a Peapod order Tuesday night for Wednesday morning delivery, the usual week's groceries, about $140 plus the $7.95 delivery fee.  Wednesday morning I recieved an email that my delivery was moved to Thursday afternoon because of the roads.  Fine, except we were out of milk and bread and I ordered Tuesday specifically because I knew the storm was coming.  My husband ended up digging the car out and going to Sunset Foods anyway.  The order did show up Thursday and everything was there.</t>
+          <t>A friend from church has been going on about Groupon so I finally signed up for the emails a couple weeks ago. Monday's deal was $25 for $50 at an Italian place in Lake Forest we've been meaning to try. My husband and I haven't done a real Valentine's dinner in probably three years (with three kids something always comes up -- last year it was a stomach bug). So I bought it. It took about two minutes, you print the certificate and bring it in. I called the restaurant after to make sure they would take it on the 14th since the fine print said something about holidays, and the woman said yes but make a reservation now, so I did -- 7:30 Sunday. My 8th grader will be at a friend's. Now I just have to remember to print the thing.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Not satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>I paid for delivery so I wouldn't have to go out in the snow, and then we went out in the snow.  I get that the roads were bad, but a 24 hour delay with no option to cancel is not great.</t>
+          <t>Half off dinner at a place we wanted to try anyway, and it forced us to actually make a plan instead of saying we should go out and then not going.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Tracy</t>
+          <t>Maureen</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -9921,31 +9923,31 @@
         </is>
       </c>
       <c r="C191" s="1" t="n">
-        <v>40212</v>
+        <v>40221</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>printer toner, book club book</t>
+          <t>Valentine's gift for my husband</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>amazon.com</t>
+          <t>amazon.com, brookstone.com, bestbuy.com</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>toner cartridge and The Help, amazon</t>
+          <t>Did not purchase</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>The printer at home ran out of toner and I needed the book for book club on the 18th (The Help).  Both from Amazon, both at lunch.  Toner was $58 which is still less than Office Depot, and the book was $9.50 in hardcover.  Free shipping over $25.  I have the login saved so it's three clicks.</t>
+          <t>I'd been going back and forth about what to get my husband. He's impossible, he buys what he wants when he wants it. Friday at lunch I looked on Amazon and Brookstone for a few things -- a new wallet (his is held together with hope), a book about the Cubs he mentioned, and those noise cancelling headphones for his flights. The headphones are $99 and up and I am not spending that for Valentine's. Amazon had the Cubs book but with it being Friday there was no way it would get here by Sunday without paying $15 for overnight. So I didn't buy anything online. I'll run to Borders tomorrow for the book and get a wallet at Carson's, and honestly he'll be happy with the dinner and a card. Took me 20 minutes to figure out what I already knew.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -9955,14 +9957,14 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Two errands I didn't have to run.  Amazon is faster than driving to the store and cheaper for anything with a part number.</t>
+          <t>I didn't buy anything but I finally made up my mind, and looking online meant I knew the Cubs book existed and what it should cost before I walk into Borders.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Tracy</t>
+          <t>Robin</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -9971,11 +9973,11 @@
         </is>
       </c>
       <c r="C192" s="1" t="n">
-        <v>40213</v>
+        <v>40211</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>snow boots for Sophie</t>
+          <t>basketball shoes</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -9985,34 +9987,34 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>LL Bean</t>
+          <t>dickssportinggoods.com, eastbay.com, zappos</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>kids snow boots, llbean.com (backordered)</t>
+          <t>2 pair Nike basketball shoes, dickssportinggoods.com</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Sophie's boots leak.  Went to llbean.com at lunch because their kids' boots are the only ones that have ever actually kept her feet dry.  Her size was backordered until March 5 in the color she wanted and until mid March in the other color.  I ordered the first one anyway because the alternative is Target boots that fall apart in a month.  Free shipping, $39.  So she'll have new boots in time for the last snow of the year, probably.</t>
+          <t>Both boys needed new basketball shoes before the Vernon Hills tournament. Ryan's have a hole, Tyler's are too small. Checked Eastbay, Zappos and Dick's online. Dick's had the Nike Hyperdunks on sale, $54.99 from $70, and free shipping over $50. Ordered a size 6 and a 6.5, same shoe, so they stop fighting over whose is whose. Should be here Friday.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Not satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>I'm paying now for boots I won't see for a month.  I understand it's February but they should have stock in February, that is when people buy boots.</t>
+          <t>Two pair for about the price of one at full price, and I didn't have to drag them to the store on a school night.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Tracy</t>
+          <t>Robin</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -10021,48 +10023,48 @@
         </is>
       </c>
       <c r="C193" s="1" t="n">
-        <v>40218</v>
+        <v>40215</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>teacher Valentine gifts</t>
+          <t>ceiling tiles and grid</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>starbucks.com, amazon.com</t>
+          <t>Menards</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Did not purchase</t>
+          <t>Menards, 11 cases of ceiling tiles, hanger wire, grid clips, shop light</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Both kids' teachers get something for Valentine's Day, it's expected at their school.  Looked at Starbucks gift cards online and at Amazon gift cards during lunch, then realized it's easier to pick up the Starbucks cards at Jewel when I'm there anyway and skip the shipping.  Spent 10 minutes on it and bought nothing.</t>
+          <t>Went to Menards in Gurnee Saturday after the boys' games, since the Home Depot trip was a bust. They had the same Armstrong tiles, 14 cases on the shelf, so we took 11 plus the hanger wire and a box of the grid clips. Paid about $22 more total than Home Depot would have been but the 11% rebate was going on so it comes out ahead if I remember to mail in the form. A kid from the lumber yard helped Dave load the truck. Also picked up a shop light for the furnace room since we were there.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Nothing wrong with the sites, I just caught myself about to pay shipping on a gift card.</t>
+          <t>Had everything we needed in one trip, loaded it for us, and the rebate will cover the price difference. Basement ceiling goes in next weekend.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Tracy</t>
+          <t>Robin</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -10071,48 +10073,48 @@
         </is>
       </c>
       <c r="C194" s="1" t="n">
-        <v>40221</v>
+        <v>40214</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>valentines for the kids' classes</t>
+          <t>ceiling tiles for the basement</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped offline and didn't purchase</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Home Depot</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Walgreens - 2 boxes of valentines, 2 Starbucks cards, milk</t>
+          <t>Did not purchase</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Friday after work, the Walgreens on Deerfield Rd before I got on the Tollway.  Two boxes of valentines (Sophie picked Disney princesses, Jack took whatever had Star Wars on it), two $15 Starbucks cards for the teachers since I never made it to Jewel, and a gallon of milk because we were out again.  No line.  $44.</t>
+          <t>We are putting a drop ceiling in the basement. I priced the Armstrong 2x4 tiles on menards.com and homedepot.com Thursday night and Home Depot was about $2 a case cheaper, and their site showed them in stock at the Gurnee store. Drove over after work Friday with the truck. They had 3 cases on the shelf and we need 11. The guy in the department checked the computer and said Vernon Hills had 4. So the website was wrong or somebody bought 8 cases that afternoon. Either way I drove home with nothing.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Not satisfied</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Three errands in one 10 minute stop on the way home.  Walgreens exists for exactly this.</t>
+          <t>An hour and the gas wasted because the website said in stock and it wasn't. I would of just gone to Menards if I had known.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Tracy</t>
+          <t>Robin</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -10121,48 +10123,48 @@
         </is>
       </c>
       <c r="C195" s="1" t="n">
-        <v>40211</v>
+        <v>40210</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>winter coat for Jack</t>
+          <t>groceries</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Lands End</t>
+          <t>Jewel</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Squall parka, landsend.com</t>
+          <t>Jewel, groceries for the week</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Jack's zipper broke on his coat for the second time and he's 10, he needs something that survives recess.  Ordered the Lands' End Squall parka at lunch.  I've bought their coats for both kids for years, they hold up and the sizing is predictable.  It was marked down to $49.50 from $79 and I had a free shipping code from an email.  Done in 5 minutes.</t>
+          <t>Monday grocery run at Jewel after dropping the kids off. Had my list and the Preferred Card, used a couple of coupons from the Sunday paper. $142, about what it always is.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Known quantity, good price, no thinking required.  That's what I need in February.</t>
+          <t>Got what we needed. Chicken was on sale, which helped. Nothing special.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Maureen</t>
+          <t>Robin</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -10171,11 +10173,11 @@
         </is>
       </c>
       <c r="C196" s="1" t="n">
-        <v>40210</v>
+        <v>40218</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>care package for my daughter at college</t>
+          <t>groceries before the snow</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -10185,17 +10187,17 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Target, the post office</t>
+          <t>Jewel</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Target - cold medicine, Easy Mac, popcorn, Dove hearts, socks; flat rate box at the post office</t>
+          <t>Jewel, milk, bread, eggs, chili stuff, dog food, driveway salt</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>My oldest is a sophomore at Iowa and she has had a cold for two weeks (she says it's a cold, I say go to student health). So Monday I did a care package. Went to Target in Vernon Hills and bought DayQuil, NyQuil, Ricola, a box of the Easy Mac she likes, microwave popcorn, a bag of Dove hearts for Valentine's, and a 6-pack of socks because for some reason she can never find socks. I wanted to throw in Girl Scout cookies but those don't come till March. Then over to the post office for a medium flat rate box -- $10.70 to ship no matter how much I cram in, and believe me I crammed. Her roommate will probably eat half of it but that's fine.</t>
+          <t>The news said 8 to 12 inches starting Tuesday afternoon so I went to Jewel at 7 Tuesday morning before work. Milk, bread, eggs, the stuff for a pot of chili, dog food, and a bag of salt for the driveway. It was already busier than a normal Tuesday morning but the shelves were full and I was out in 25 minutes. By the time I drove past on the way home at 5 the lot was packed.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -10205,14 +10207,14 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Two stops and it went out the same day. For about $45 total I get to feel like I'm doing something for her from 250 miles away, which is really what a care package is for.</t>
+          <t>Beat the rush and had everything I needed when school got cancelled Wednesday. Didn't have to leave the house for two days.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Maureen</t>
+          <t>Robin</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -10221,48 +10223,43 @@
         </is>
       </c>
       <c r="C197" s="1" t="n">
-        <v>40215</v>
+        <v>40212</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>laptop for my college daughter</t>
+          <t>indoor soccer shoes</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>bestbuy.com, dell.com, cnet</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>Toshiba Satellite laptop and a case at Best Buy</t>
+          <t>sportsauthority.com, soccer.com</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>The laptop my sophomore took to college finally died (it was four years old and had been dropped more than once). I spent a couple evenings this week on bestbuy.com and dell.com and reading the cnet reviews. I know just enough about computers to be dangerous, so I had my husband look too. We narrowed it down to a Toshiba Satellite with Windows 7 for $549 that was in the Best Buy ad this week, and a Dell that was about the same but would take two weeks to ship. Saturday we drove to Best Buy in Vernon Hills, the kid in the computer department was fine, didn't push the extended warranty too hard when I said no, and we were out in 30 minutes. My daughter will pick it up when she's home for Presidents Day. I did buy a case for it, $29.99, which I probably could have gotten cheaper online but at that point I just wanted to be done.</t>
+          <t>Indoor soccer starts in March and the boys' shoes from last year are shot. Looked on Sports Authority and soccer.com during lunch. Adidas Sambas are $55 each at both. Didn't order. Sports Authority usually sends a 20% coupon by the end of the month and I'd rather have them try them on anyway. Made a note on the calendar.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Doing the homework online first meant I walked in knowing exactly what I wanted and what it should cost, and that is the only way I can stand Best Buy. She gets a decent computer and we stayed under $600 with the case.</t>
+          <t>Know what they cost and have a plan. No reason to pay full price three weeks early.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Maureen</t>
+          <t>Robin</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -10271,43 +10268,48 @@
         </is>
       </c>
       <c r="C198" s="1" t="n">
-        <v>40212</v>
+        <v>40215</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>prom dress (just looking)</t>
+          <t>lunch</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>promgirl.com, davidsbridal.com, nordstrom.com, macys.com</t>
+          <t>Panera</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Panera - 2 kids meals, 2 soups, coffee</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Prom is not until May but my senior has informed me that all her friends are already looking, so Wednesday night the two of us sat on the couch with the laptop. (I should say she sat with the laptop and I was allowed to watch.) We looked at promgirl.com, David's Bridal, Nordstrom and Macy's. Her taste runs to long, strapless, and about $300 more than I had in mind. Nordstrom had a couple of BCBG ones she liked around $250. Macy's had similar for $150 but she says those are the ones everyone will have. I said nobody is buying anything online without trying it on first, so this was strictly research. She has a list going on a sticky note on her mirror. We'll hit Hawthorn or Old Orchard in March when there is more in the stores.</t>
+          <t>Saturday: basketball game at 9, soccer scrimmage at 1. Took the boys and Dave to Panera in Vernon Hills in between. Two kids meals, two bowls of broccoli cheddar and a coffee, about $26. Line was out the door but it moved. They ate fast and were back on the field by 12:45. Beats McDonalds.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Nothing bought, nothing lost. It was nice to do it together without arguing, and now I know what the prices look like so I'm not shocked in March.</t>
+          <t>Fast, decent food, close to both gyms. Exactly what Saturday needed.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Maureen</t>
+          <t>Robin</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -10316,48 +10318,48 @@
         </is>
       </c>
       <c r="C199" s="1" t="n">
-        <v>40214</v>
+        <v>40219</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Sam's Club run</t>
+          <t>photo books for the coaches</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Costco photo center</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Sam's - paper towels, toilet paper, chicken, cereal, Tide, Gatorade</t>
+          <t>2 photo books from costco.com</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Friday afternoon Sam's Club trip. I go about every three weeks and buy the things we go through at a ridiculous rate with three kids (well, two at home now, but the 8th grader eats like three). The 30-roll paper towels, the big Tide, two of the double boxes of Cheerios, the 10 pound bag of chicken breasts, and a case of Gatorade for my son's basketball. I had my list but still came out at $212, there is always something -- this time it was a 3-pack of Crest and a book for me. The lines were long, only three registers open on a Friday afternoon, and the cart was so heavy I needed my son to unload it.</t>
+          <t>Snow day so I finally did the basketball team photo book for the coaches' end of season gift. Uploaded about 60 pictures from the season to the Costco photo site and used the 8x8 hardcover template. $19.99 each, ordered two, one for each coach. Shutterfly was running a sale too but Costco was still cheaper and I can pick them up when I'm there for groceries anyway. Took about two hours total, mostly picking pictures.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>The prices are good and I know they are good, that's why I go. But 25 minutes in line and a $200 bill never feels great, even when it's all stuff we need.</t>
+          <t>Half the price of Shutterfly for the same book, and the other parents already paid me back. Pickup at the store, no shipping.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Maureen</t>
+          <t>Robin</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -10366,48 +10368,48 @@
         </is>
       </c>
       <c r="C200" s="1" t="n">
-        <v>40219</v>
+        <v>40217</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>science fair supplies</t>
+          <t>soccer gear</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Michaels, Walgreens</t>
+          <t>soccer.com</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Walgreens - 2 sheets of poster board (not the tri-fold), glue stick, markers</t>
+          <t>shin guards, 4 pr socks, goalie gloves at soccer.com</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>The science fair is Friday and my 8th grader announced Wednesday morning, with school cancelled for the snow, that he needs a tri-fold display board. Of course he does. I drove to Michaels in Mundelein on roads that were honestly not good and they were out of the tri-fold boards. Completely out. The girl at the register said they "might get some Friday" and went back to her conversation. So I went over to Walgreens, which had regular poster board but not the tri-fold, and bought two sheets and told him he'd be taping them together. He was not thrilled. Neither was I. I know, I know, I should have asked him about this a week ago, but he definately should have told me too.</t>
+          <t>Travel soccer sent the equipment list for spring. Both boys need new shin guards (lost one each, naturally), socks, and Tyler needs goalie gloves this year. Went straight to soccer.com since the club uses them and the sizing chart matches. Ordered 2 pair of Adidas shin guards at $12.99, 4 pair of socks, and the Reusch gloves at $24.99. Free shipping with the club code. Twenty minutes, done.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Not at all satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Risked the roads for nothing, the Michaels clerk could not have cared less, and the project is going to look like two pieces of poster board taped together because that's what it is.</t>
+          <t>One site, one order, club discount. Everything was in stock.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Maureen</t>
+          <t>Robin</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -10416,31 +10418,31 @@
         </is>
       </c>
       <c r="C201" s="1" t="n">
-        <v>40217</v>
+        <v>40220</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Valentine's dinner</t>
+          <t>Valentine's cards and teacher gifts</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Groupon</t>
+          <t>Hallmark</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Groupon - $50 at an Italian restaurant in Lake Forest for $25</t>
+          <t>Hallmark - 4 cards, 2 teacher mugs, candy</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>A friend from church has been going on about Groupon so I finally signed up for the emails a couple weeks ago. Monday's deal was $25 for $50 at an Italian place in Lake Forest we've been meaning to try. My husband and I haven't done a real Valentine's dinner in probably three years (with three kids something always comes up -- last year it was a stomach bug). So I bought it. It took about two minutes, you print the certificate and bring it in. I called the restaurant after to make sure they would take it on the 14th since the fine print said something about holidays, and the woman said yes but make a reservation now, so I did -- 7:30 Sunday. My 8th grader will be at a friend's. Now I just have to remember to print the thing.</t>
+          <t>Hit Hallmark in Vernon Hills after work for Valentine's. Cards for Dave and the boys, a mug and a bag of candy for each of the twins' teachers, and a bag of the little foil hearts for the team snack bags. The teacher mugs were $9.95 each, a little steep, but it was one stop instead of three. Cashier put the mugs in gift bags for free. In and out in 15 minutes.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -10450,14 +10452,14 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Half off dinner at a place we wanted to try anyway, and it forced us to actually make a plan instead of saying we should go out and then not going.</t>
+          <t>One stop, everything done, free gift bags. Worth the few extra dollars not to run around.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Maureen</t>
+          <t>Robin</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -10480,34 +10482,29 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>amazon.com, brookstone.com, bestbuy.com</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>Did not purchase</t>
+          <t>kohls.com</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>I'd been going back and forth about what to get my husband. He's impossible, he buys what he wants when he wants it. Friday at lunch I looked on Amazon and Brookstone for a few things -- a new wallet (his is held together with hope), a book about the Cubs he mentioned, and those noise cancelling headphones for his flights. The headphones are $99 and up and I am not spending that for Valentine's. Amazon had the Cubs book but with it being Friday there was no way it would get here by Sunday without paying $15 for overnight. So I didn't buy anything online. I'll run to Borders tomorrow for the book and get a wallet at Carson's, and honestly he'll be happy with the dinner and a card. Took me 20 minutes to figure out what I already knew.</t>
+          <t>Looked on kohls.com Friday night for something for Dave for Valentine's Day.  He needs a new fleece so I was looking at the Columbia ones, $45 to $60 and nothing on sale that I could see. I have $10 in Kohl's Cash that expires Sunday, so I'll run to the store tomorrow and look at them in person instead.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>I didn't buy anything but I finally made up my mind, and looking online meant I knew the Cubs book existed and what it should cost before I walk into Borders.</t>
+          <t>I have an idea of what I'm getting and I'll use the Kohl's Cash. Would have liked to see a sale.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Connie</t>
+          <t>Tracy</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -10516,48 +10513,48 @@
         </is>
       </c>
       <c r="C203" s="1" t="n">
-        <v>40212</v>
+        <v>40215</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>book for school</t>
+          <t>bulk groceries, paper goods</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>borders.com, amazon</t>
+          <t>Costco</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>nothing yet</t>
+          <t>Costco - paper towels, chicken, cheese, cereal, milk, dishwasher tabs, Gatorade</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Ryan's 7th grade English class is starting The Outsiders and he needs his own copy by the 10th. I checked borders.com first since I had a 33% off coupon in my email, but it turned out the coupon was in store only and the book was $9.99 with shipping on top of that. Amazon had it for $6.99 but you need $25 for free shipping and I didn't want to add stuff just to get there. I'm going to stop at the Borders in Deerfield on the way home Friday and use the coupon, which gets it under $7 anyway. If they are out I'll have Ryan check the school library.</t>
+          <t>Saturday morning Costco in Mettawa, we go every other weekend.  My husband takes the kids to the samples and I do the actual shopping.  Usual list: paper towels, toilet paper, the big pack of chicken breasts, string cheese, milk, cereal and dishwasher tablets.  Also a case of Gatorade for Jack's basketball.  $218.  Checkout is always fast there, I don't know how they do it with those lines.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>Didn't buy anything yet but I figured out the cheapest way to get it in about 10 minutes. A little annoyed the coupon was store only, that wasnt obvious in the email.</t>
+          <t>One trip covers two weeks of the boring stuff and the per unit prices beat Jewel by a lot.  In and out in 45 minutes including samples.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Connie</t>
+          <t>Tracy</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -10566,48 +10563,43 @@
         </is>
       </c>
       <c r="C204" s="1" t="n">
-        <v>40213</v>
+        <v>40217</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>comforter set for Emma's room</t>
+          <t>flat iron</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>target.com</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>Xhilaration comforter set and a desk lamp from target.com</t>
+          <t>amazon.com, folica.com</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Emma is 10 and has decided the Disney princess bedding is for babies. We looked at the Target in Vernon Hills a couple of weeks ago and she liked a purple and teal Xhilaration set that was $59.99 in the store. I checked target.com Thursday and the same set was $49.99 online, plus free shipping on orders over $50, so I added a $12 desk lamp she needed anyway. Ordered it on my lunch break. It is supposed to come in 5 to 7 days which is fine, she can live with the princesses another week.</t>
+          <t>My flat iron died.  Looked at Amazon and folica.com during lunch.  The one everyone recommends (CHI) is $90 to $100 and the reviews are all over the place, half say it's great and half say it broke after six months.  The cheaper ones have the same problem.  I closed the browser.  I'll ask my stylist what she uses and come back to it.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>Ten dollars cheaper than the store for the exact same thing, and I didn't have to drag it through the parking lot. The lamp was basically free with the shipping math.</t>
+          <t>Didn't waste money on something with 2 star reviews.  I'll get a real recommendation first.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Margaret</t>
+          <t>Tracy</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -10616,31 +10608,31 @@
         </is>
       </c>
       <c r="C205" s="1" t="n">
-        <v>40221</v>
+        <v>40220</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>ACT prep book</t>
+          <t>Flip video camera</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>amazon.com</t>
+          <t>bestbuy.com, amazon.com</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>ACT prep book and a calculator from amazon.com</t>
+          <t>Flip Ultra camcorder, Best Buy in Vernon Hills</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Michael takes the ACT in April and his counselor recommended the Princeton Review book.  Barnes &amp; Noble had it for $21.99; Amazon had it for $14.95 with free shipping once I added the TI-30 calculator he also needs, which was less than Target's price as well.  I ordered both Friday morning before work.  I also looked at the Kaplan book, but the reviews on Amazon were better for the Princeton Review.  Katie used the same book two years ago and did well, so I did not deliberate long.</t>
+          <t>Sophie's class play is next week and our camcorder is from 2003 and takes tapes.  Compared the Flip Ultra on bestbuy.com and Amazon at lunch, same price, $149.  Best Buy had it in stock at the Vernon Hills store for in-store pickup, so I reserved it online and grabbed it on the way home.  Took 4 minutes at the pickup counter.  I would have ordered from Amazon but I wanted it in hand before the weekend so Jack could figure it out for me.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -10650,14 +10642,14 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>The lower price and free shipping made the decision easy, and it will be here before his first practice test.</t>
+          <t>Same price as online, no shipping, and it was waiting for me.  In-store pickup is the only reason I still go into a Best Buy.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Margaret</t>
+          <t>Tracy</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -10666,48 +10658,48 @@
         </is>
       </c>
       <c r="C206" s="1" t="n">
-        <v>40217</v>
+        <v>40219</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>black pumps</t>
+          <t>groceries delivered</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Nordstrom, Old Orchard</t>
+          <t>Peapod</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Cole Haan pumps at Nordstrom</t>
+          <t>Peapod - groceries</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>I needed a pair of black pumps for a dinner Tom and I are attending next week, and the pair I have are shabby. Rather than go to Hawthorn, I drove down to Nordstrom at Old Orchard on my day off, since their shoe department is so much larger. The salesman measured my foot, which no one has done in years, and brought out five pairs in my size, including a Cole Haan with the Nike Air sole that I had not considered. They were $138, more than I had planned, but I tried on several and kept coming back to them. I also looked at the Carson's shoe sale on the way home, but nothing there was as comfortable.</t>
+          <t>With the storm I worked from home Wednesday and the kids were off school.  I had placed a Peapod order Tuesday night for Wednesday morning delivery, the usual week's groceries, about $140 plus the $7.95 delivery fee.  Wednesday morning I recieved an email that my delivery was moved to Thursday afternoon because of the roads.  Fine, except we were out of milk and bread and I ordered Tuesday specifically because I knew the storm was coming.  My husband ended up digging the car out and going to Sunset Foods anyway.  The order did show up Thursday and everything was there.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Not satisfied</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>Real service, a good selection and a shoe I can actually walk in. I paid more than I intended, but I will wear them for years.</t>
+          <t>I paid for delivery so I wouldn't have to go out in the snow, and then we went out in the snow.  I get that the roads were bad, but a 24 hour delay with no option to cancel is not great.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Margaret</t>
+          <t>Tracy</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -10716,31 +10708,31 @@
         </is>
       </c>
       <c r="C207" s="1" t="n">
-        <v>40213</v>
+        <v>40212</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>cardigan</t>
+          <t>printer toner, book club book</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Talbots</t>
+          <t>amazon.com</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Talbots, a cardigan and a shell</t>
+          <t>toner cartridge and The Help, amazon</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Talbots at Hawthorn had their red-line clearance going, an additional 40% off the already marked-down winter things. I went in looking for a cardigan to wear to work and found a navy one in my size that had been $89 and came to $32. The saleswoman brought me a matching shell without my asking, which I also bought. There were only two other customers in the store, so I had the fitting room to myself. I did have to dig through the racks, as the clearance was not sorted by size.</t>
+          <t>The printer at home ran out of toner and I needed the book for book club on the 18th (The Help).  Both from Amazon, both at lunch.  Toner was $58 which is still less than Office Depot, and the book was $9.50 in hardcover.  Free shipping over $25.  I have the login saved so it's three clicks.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -10750,14 +10742,14 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>A classic cardigan at about a third of the original price, with pleasant and attentive service. I will get years out of it.</t>
+          <t>Two errands I didn't have to run.  Amazon is faster than driving to the store and cheaper for anything with a part number.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Margaret</t>
+          <t>Tracy</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -10766,11 +10758,11 @@
         </is>
       </c>
       <c r="C208" s="1" t="n">
-        <v>40210</v>
+        <v>40213</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>care package for Katie</t>
+          <t>snow boots for Sophie</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -10780,34 +10772,34 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>amazon.com</t>
+          <t>LL Bean</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>amazon.com - snacks, a book and a phone charger, shipped to Katie's dorm</t>
+          <t>kids snow boots, llbean.com (backordered)</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Katie has midterms coming up at the U of I and I like to send a little something to her dorm.  I put together an order on Amazon with a box of Clif bars, microwave popcorn, the Jodi Picoult paperback she mentioned and a replacement charger for her phone, which she has lost for the second time.  I kept the order over $25 so the shipping was free, though that meant the slower shipping, so it will not arrive until the end of the week.  I considered packing a box myself and taking it to the post office, but by the time I bought the items and paid the postage, this was simpler.</t>
+          <t>Sophie's boots leak.  Went to llbean.com at lunch because their kids' boots are the only ones that have ever actually kept her feet dry.  Her size was backordered until March 5 in the color she wanted and until mid March in the other color.  I ordered the first one anyway because the alternative is Target boots that fall apart in a month.  Free shipping, $39.  So she'll have new boots in time for the last snow of the year, probably.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Not satisfied</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>It was convenient and the free shipping helped, but I would have liked it to arrive sooner. I also could not tuck in a note the way I can when I pack the box myself.</t>
+          <t>I'm paying now for boots I won't see for a month.  I understand it's February but they should have stock in February, that is when people buy boots.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Margaret</t>
+          <t>Tracy</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -10816,48 +10808,48 @@
         </is>
       </c>
       <c r="C209" s="1" t="n">
-        <v>40220</v>
+        <v>40218</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>dress shirts for my husband</t>
+          <t>teacher Valentine gifts</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Carson's</t>
+          <t>starbucks.com, amazon.com</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>3 dress shirts at Carson's, Hawthorn</t>
+          <t>Did not purchase</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Carson's sent an email about their Presidents' Day sale with a printable coupon for an extra 20% off, and I saw that the Van Heusen dress shirts Tom wears were marked down to $19.99 from $45. I checked the sizes online, then went to the store at Hawthorn rather than order, because I know how those shirts can run and I wanted to see the colors. I bought three, a white, a blue and a stripe, for about $48 after the coupon. The line at the register was the longest I have seen in months, with all the Valentine's shoppers.</t>
+          <t>Both kids' teachers get something for Valentine's Day, it's expected at their school.  Looked at Starbucks gift cards online and at Amazon gift cards during lunch, then realized it's easier to pick up the Starbucks cards at Jewel when I'm there anyway and skip the shipping.  Spent 10 minutes on it and bought nothing.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>Three good shirts for roughly the price of one, and Tom will not have to go to the store himself, which he would never do.</t>
+          <t>Nothing wrong with the sites, I just caught myself about to pay shipping on a gift card.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Margaret</t>
+          <t>Tracy</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -10866,31 +10858,31 @@
         </is>
       </c>
       <c r="C210" s="1" t="n">
-        <v>40214</v>
+        <v>40221</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Dutch oven</t>
+          <t>valentines for the kids' classes</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Williams-Sonoma</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Le Creuset Dutch oven at Williams-Sonoma, Deer Park</t>
+          <t>Walgreens - 2 boxes of valentines, 2 Starbucks cards, milk</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>I have wanted a Le Creuset Dutch oven for years and finally decided to buy one with some of my Christmas money. I compared prices on the Williams-Sonoma site, Sur La Table and Amazon, and they were essentially identical, which I gather is how that company operates. Williams-Sonoma had the 5 1/2 quart in the cherry red on sale for $199 instead of $265, and the website showed it in stock at Deer Park Town Center. I drove over Friday afternoon rather than pay to ship something that heavy. The clerk carried it out to the car for me. I made a pot roast in it that night.</t>
+          <t>Friday after work, the Walgreens on Deerfield Rd before I got on the Tollway.  Two boxes of valentines (Sophie picked Disney princesses, Jack took whatever had Star Wars on it), two $15 Starbucks cards for the teachers since I never made it to Jewel, and a gallon of milk because we were out again.  No line.  $44.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -10900,14 +10892,14 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>Checking the website first meant I knew the price and that they had it before I drove over. The sale price made it feel justified, and the pot roast was wonderful.</t>
+          <t>Three errands in one 10 minute stop on the way home.  Walgreens exists for exactly this.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Margaret</t>
+          <t>Tracy</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -10916,11 +10908,11 @@
         </is>
       </c>
       <c r="C211" s="1" t="n">
-        <v>40219</v>
+        <v>40211</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>flowers for my mother</t>
+          <t>winter coat for Jack</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -10930,17 +10922,17 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>proflowers</t>
+          <t>Lands End</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>tulips from proflowers for my mother</t>
+          <t>Squall parka, landsend.com</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>My mother is 78 and lives alone in Rockford, and I always send her flowers for Valentine's Day since my father passed. I used ProFlowers, as I have for the last few years. I chose the pink tulips with the glass vase, $39.99, and paid a little extra to have them delivered on Friday the 12th so they would not come on the weekend, when the rates are higher. The site remembered her address and my card. It took perhaps five minutes, which was welcome on a day when the roads were a mess from the storm.</t>
+          <t>Jack's zipper broke on his coat for the second time and he's 10, he needs something that survives recess.  Ordered the Lands' End Squall parka at lunch.  I've bought their coats for both kids for years, they hold up and the sizing is predictable.  It was marked down to $49.50 from $79 and I had a free shipping code from an email.  Done in 5 minutes.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -10950,14 +10942,14 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>Simple, dependable, and the flowers have always arrived looking fresh. She called in tears last year, so I know it means a great deal to her.</t>
+          <t>Known quantity, good price, no thinking required.  That's what I need in February.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Margaret</t>
+          <t>Vicki</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -10966,11 +10958,11 @@
         </is>
       </c>
       <c r="C212" s="1" t="n">
-        <v>40210</v>
+        <v>40213</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>groceries</t>
+          <t>basketball shoes for my daughter</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -10980,17 +10972,17 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Jewel</t>
+          <t>Dick's Sporting Goods</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Jewel, groceries for the week</t>
+          <t>Nike basketball shoes at Dick's, $54.99</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Monday is my grocery day, so I went to the Jewel on Milwaukee Avenue after my morning walk. I had gone through the Sunday ad and made my list around what was on sale, which this week was chicken breasts, strawberries and the Tropicana orange juice that Michael goes through by the gallon. I also used three of the coupons I had clipped. The store was quiet at that hour and I was in and out in about forty minutes.</t>
+          <t>My daughter plays on the 7th grade team at school (she's 13) and her shoes were coming apart at the toe. Took her to Dick's in Vernon Hills after practice. They have a whole wall of basketball shoes and she went straight for the $110 Kobe ones, which I said no to. Found a pair of Nikes on the sale rack for 54.99 that she liked fine once she tried them on. The kid working the shoe department actually knew what he was talking about and brought out a half size up, which was the right call. Also grabbed a new water bottle since hers is somewhere in the school gym.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -11000,14 +10992,14 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>I stayed on my list, saved about $18 with the sale items and coupons, and did not have to wait at the register.</t>
+          <t>She got shoes she likes, I paid half of what she wanted me to pay, and the salesperson was helpful. In and out in 30 minutes.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Margaret</t>
+          <t>Vicki</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -11016,31 +11008,31 @@
         </is>
       </c>
       <c r="C213" s="1" t="n">
-        <v>40219</v>
+        <v>40220</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>guest room bedding</t>
+          <t>car emergency kit</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>overstock.com, Bed Bath &amp; Beyond</t>
+          <t>target.com, Amazon</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>quilt set from overstock.com</t>
+          <t>roadside emergency kit at Target, $29.99</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Katie is bringing her roommate home for spring break and the guest room comforter has seen better days.  Being snowed in, I compared quilts on the Bed Bath &amp; Beyond website and on Overstock.  Overstock had a cotton quilt set in a blue and white pattern for $64.99 with $2.95 shipping, where the comparable set at Bed Bath &amp; Beyond was $99 before my 20% coupon.  I read through the reviews, which were mostly favorable aside from a few about the colors being lighter than pictured, and ordered the Overstock set.</t>
+          <t>After the storm I decided my son is not driving around without jumper cables and a blanket in the trunk. Looked on Amazon and target.com Wednesday night. Amazon had a kit for 24.99 but shipping made it the same as Target's. Target.com said the Mundelein store had it in stock so I picked it up on the way home from work Thursday. Threw in an ice scraper and a jug of washer fluid while I was there.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -11050,14 +11042,14 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>A good price, nearly free shipping and the reviews gave me confidence. I will definately know when it arrives, but I expect to be pleased.</t>
+          <t>Checking the website first saved me a wasted trip. $29.99 for cables, flares, a flashlight and a poncho is fine with me if it means I worry a little less.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Margaret</t>
+          <t>Vicki</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -11066,26 +11058,31 @@
         </is>
       </c>
       <c r="C214" s="1" t="n">
-        <v>40215</v>
+        <v>40211</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Kindle or nook</t>
+          <t>groceries</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>amazon.com, barnesandnoble.com</t>
+          <t>Jewel</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Jewel - milk, cereal, chicken, lunch stuff, frozen pizzas</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Tom's sister has a Kindle and raves about it, so I spent some time Saturday morning reading about the Kindle on Amazon and the new nook on the Barnes &amp; Noble site. They are both $259, which seems like a great deal of money for something to read a book on. The reviews for the nook mentioned it being slow to turn pages. I did not order one. I will keep it in mind for Tom's birthday in April, when perhaps the prices will have come down.</t>
+          <t>Tuesday is my grocery day. I had my list and the Jewel ad and went after work. With a 16 year old in the house we go through milk and cereal like crazy, so I got 3 gallons and whatever cereal was on the 10 for $10. Boneless chicken breasts were 1.99 a pound so I got two family packs for the freezer.  Line was long at 5:30 and only two lanes open, which is typical for that store.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -11095,14 +11092,14 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>I learned what I wanted to know. There is no hurry, and I would rather wait and see whether the price drops.</t>
+          <t>Got everything on the list and the chicken was a good price. I would have said extremely but the checkout took 15 minutes.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Margaret</t>
+          <t>Vicki</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -11111,48 +11108,48 @@
         </is>
       </c>
       <c r="C215" s="1" t="n">
-        <v>40218</v>
+        <v>40215</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>spring tops</t>
+          <t>jeans and a hoodie for the kids</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>chicos.com</t>
+          <t>Hollister, American Eagle at Hawthorn Mall</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>nothing yet</t>
+          <t>2 pair of jeans and a hoodie at American Eagle</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>With the snow coming down all day and school already called off for tomorrow, I spent an hour on the Chico's website with a glass of wine. They had sent an email about their new spring arrivals and a 20% off coupon for Passport members. I put two tops and a pair of their Travelers pants in my cart, nearly $160 with the discount, and then closed the browser. I have enough clothes, and I would rather see the colors in person at the store in Deer Park. Michael and Tom were watching the hockey game and did not notice I was shopping, which is probably for the best.</t>
+          <t>Saturday at Hawthorn with both kids, which is not my favorite way to spend a Saturday. My daughter wanted Hollister. We went in, it is dark and the music is so loud you can't think, and a plain hoodie was $49.50. I told her we would look at American Eagle first. AE had jeans buy one get one 50% off so my son got two pair (he's outgrown everything again, 16 and still growing) and my daughter found a hoodie on the clearance rack for $19.99. She was a little sulky about not getting the Hollister one but got over it by the food court. Total was about $95 for the three things.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>A pleasant way to pass a snowy evening, and I did not spend any money. The coupon is good through the end of the month.</t>
+          <t>Half the price of Hollister for basically the same stuff. My son could care less what brand it is as long as it fits, so he was easy.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Margaret</t>
+          <t>Vicki</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -11161,11 +11158,11 @@
         </is>
       </c>
       <c r="C216" s="1" t="n">
-        <v>40216</v>
+        <v>40210</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>statistics textbook</t>
+          <t>SAT prep book</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -11175,17 +11172,17 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>half.com, Chegg, amazon.com</t>
+          <t>Amazon, borders.com</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>used textbook from half.com</t>
+          <t>The Official SAT Study Guide from Amazon</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Katie called in a bit of a panic because she needs a statistics textbook for a class she added late, and the campus bookstore wants $148 for it. I had her read me the ISBN and I looked it up on half.com, Chegg and Amazon. Chegg would rent it for $52 for the semester; half.com had a used copy in "good" condition for $41 plus $3.99 shipping. I bought the used one, since she can sell it back in May. It will ship directly to her dorm.</t>
+          <t>My son is taking the SAT in May so I told him we were getting a prep book now, not in April. I looked at the Kaplan and Princeton Review ones and the College Board book that has the actual old tests in it. The reviews on Amazon said to use the College Board one for the practice tests so that is what I went with. It was $13.59 on Amazon and $21.99 at Borders, and with a couple of other things I was over the $25 for free shipping. Ordered it from the kitchen table in about ten minutes.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -11195,14 +11192,14 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>Less than a third of the bookstore price, and it took ten minutes on a Sunday morning. Katie was relieved.</t>
+          <t>Eight dollars cheaper than the store, no driving, and it should be here by Thursday. Now whether he opens it is a different story.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Margaret</t>
+          <t>Vicki</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -11211,31 +11208,31 @@
         </is>
       </c>
       <c r="C217" s="1" t="n">
-        <v>40220</v>
+        <v>40221</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Valentine's cards and candy</t>
+          <t>snow boots for my daughter</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Hallmark, Fannie May</t>
+          <t>Lands End, Zappos</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>cards at Hallmark; Pixies, Mint Meltaways and Trinidads at Fannie May</t>
+          <t>Lands End snow boots</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Valentine's errands. I stopped at the Hallmark in the Libertyville shopping center for cards for Tom, Michael, Katie and my mother, and then went next door to Fannie May. Tom gets a box of Pixies every year and Michael gets the Mint Meltaways, and Katie's box of Trinidads will go in the mail tomorrow. The Hallmark cards were $4 and $5 apiece, which always surprises me, but I like to take my time choosing them. The young woman at Fannie May wrapped Katie's box in tissue for shipping without my asking.</t>
+          <t>Her boots from last year don't fit, so my daughter has been wearing gym shoes in the snow all week. I looked at Zappos first since shipping is free both ways but the Sorels were $90. Lands End had their snow boots marked down to 34.99 and I had a free shipping code from an email, so I ordered a size 7. She wanted the pink ones. If they don't fit I can return them at Sears, which is easier than mailing them back.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -11245,14 +11242,14 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>Both stores had exactly what I came for, I was done in half an hour and the people at Fannie May are always lovely.</t>
+          <t>$35 with free shipping for boots that will probably only fit her one winter anyway. Can't complain.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Margaret</t>
+          <t>Vicki</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -11261,48 +11258,48 @@
         </is>
       </c>
       <c r="C218" s="1" t="n">
-        <v>40212</v>
+        <v>40216</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Valentine's gift for Tom</t>
+          <t>Super Bowl food</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Orvis, LL Bean, Brookstone</t>
+          <t>Costco</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Did not purchase</t>
+          <t>Costco - wings, chips, salsa, pop, water, paper plates</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Tom is impossible to shop for. I looked through the Orvis and L.L. Bean sites for a nice flannel shirt or a fleece vest, and then at Brookstone for one of those gadgets he would never buy himself. Everything was either $90 for a shirt or something he does not need. I had a cup of tea and gave up for the night. He will probably end up with a card and dinner at Tavern in Libertyville, which, to be fair, is what he would choose anyway.</t>
+          <t>We had my brother's family and a couple of my son's friends coming over for the Super Bowl. Went to Costco Sunday morning right when they opened at 10 to beat the crowd. Got the big bag of frozen wings, two things of tortilla chips, the salsa, a case of pop, a case of water and paper plates. Also a rotisserie chicken for Monday because they are $4.99 and I was not going to want to cook. Was out of there by 10:40 and the lines were already getting long behind me.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Not satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Over an hour on three websites and nothing to show for it. The prices on the clothing were more than I want to spend on a Valentine's gift.</t>
+          <t>Everything in one trip, the wings fed 6 teenagers, and I think I spent about $85 which is less than it would of been at Jewel.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Margaret</t>
+          <t>Vicki</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -11311,11 +11308,11 @@
         </is>
       </c>
       <c r="C219" s="1" t="n">
-        <v>40211</v>
+        <v>40218</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>winter coat for my son</t>
+          <t>used car for my son</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -11325,29 +11322,34 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>nordstrom.com, macys.com, landsend.com</t>
+          <t>cars.com, autotrader, craigslist</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Michael has outgrown his winter coat, again, and refuses to wear the one Tom offered him. I spent part of the evening looking at the North Face jackets on Nordstrom's site and at Macy's, and then at the Lands' End squall parka, which is less expensive and would probably last longer. The North Face is what he wants, of course, at $199. I did not order anything. I want him to try one on, and I suspect Nordstrom will mark the winter coats down further by the end of the month.</t>
+          <t>Snow day, everything was cancelled, so my son and I sat down at the computer and looked at used cars. He got his license in January and has been driving my car, which is getting old fast. We are thinking a 2002-2004 Civic or Corolla, under $6,000, and nothing with a sunroof or anything he can show off with. Looked at cars.com and autotrader and craigslist. Anything decent under 6,000 has 130,000 miles on it or is in the city. The ones on craigslist I dont trust. We bookmarked a couple from dealers in Waukegan and Libertyville but I am not calling anybody until the roads are clear.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Not satisfied</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>I did not buy anything, but I now know the prices and what the choices are, so a trip to the store will be quicker.</t>
+          <t>Not satisfied because there was nothing in our price range that I would actually put my kid in. We may have to go up to $7,000 or wait until spring.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Jillian</t>
+          <t>Alicia</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -11356,11 +11358,11 @@
         </is>
       </c>
       <c r="C220" s="1" t="n">
-        <v>40221</v>
+        <v>40217</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>breast pump</t>
+          <t>birthday present for my nephew</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -11370,17 +11372,17 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>amazon.com, babiesrus.com, buybuybaby.com</t>
+          <t>amazon.com</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Amazon - Medela Pump In Style</t>
+          <t>Amazon - Lego set</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Everyone says get the Medela Pump In Style so I compared prices.  Babies R Us $279, buybuybaby.com $279, Amazon $249 with free shipping and no tax.  Thirty dollars is thirty dollars.  Ordered it from Amazon.  I'm due in 8 weeks and this was the last big thing on the list that wasn't on the registry.</t>
+          <t>My nephew turns 6 next week.  My sister said he's into Legos so I searched Amazon at lunch, found a Lego City set in the $20 range with 4.5 stars, and had it shipped directly to their house in Naperville with gift wrap.  Done in less than 10 minutes.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -11390,14 +11392,14 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Same pump everyone recommends for $30 less.  One more thing checked off, 8 weeks to go!</t>
+          <t>Shipped straight to him, gift wrapped, and I didn't have to find time to go to a store or the post office.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Jillian</t>
+          <t>Alicia</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -11406,43 +11408,48 @@
         </is>
       </c>
       <c r="C221" s="1" t="n">
-        <v>40214</v>
+        <v>40215</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>car seat</t>
+          <t>Costco run</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>amazon.com, babycenter.com, consumer reports</t>
+          <t>Costco</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Costco - paper towels, chicken, granola bars, printer paper, a sweater</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Spent most of my evening on car seats.  Started on Amazon, then the babycenter message boards, then Consumer Reports which I had to pay for.  Every seat has someone saying it's the best and someone saying it's the worst.  Infant seat vs. convertible, which ones fit in a Civic, which bases fit.  I closed the laptop with more tabs open than when I started and no decision.</t>
+          <t>Dave and I went to Costco in Mettawa Saturday morning while my mom had our son.  Standard stuff - paper towels, toilet paper, chicken breasts, the big box of granola bars for lunches, printer paper for my home office.  I also picked up a sweater for $19.99 from the table because it looked fine and why not.  $240 total which is about normal for us.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Not satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>I thought I'd have an answer tonight and I'm more confused than when I started.  This is the one thing I'm actually scared of getting wrong.</t>
+          <t>Fast because we went early, and no kid asking for samples every ten feet.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Jillian</t>
+          <t>Alicia</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -11455,39 +11462,44 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>crib</t>
+          <t>groceries</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>babiesrus.com, buybuybaby.com, amazon.com</t>
+          <t>Peapod</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Peapod - groceries</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Started seriously looking at cribs tonight!  I had a list of about 8 from the baby book and from my friend Jen, and I went through all of them on babiesrus.com, buybuybaby.com and Amazon reading reviews.  Some of the reviews are scary (drop side recalls) so I'm only looking at fixed side ones now.  Narrowed it down to 2, both convertible, one is $299 and one is $379.  Mike wants to see them in person before we decide so we're going to the store this weekend.</t>
+          <t>Placed our Peapod order Sunday night for Monday evening delivery.  I keep a standing list in my account so it takes about 15 minutes to go through it and add whatever is new.  Delivery fee was $6.95 which is less than the gas and the hour I'd spend at Jewel with a 4 year old.  Driver was in our window and nothing was substituted this time.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Didn't buy yet but I feel so much better having it down to two.  Eight was too many.</t>
+          <t>Everything came as ordered, on time, and I never left the house.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Jillian</t>
+          <t>Alicia</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -11496,11 +11508,11 @@
         </is>
       </c>
       <c r="C223" s="1" t="n">
-        <v>40218</v>
+        <v>40211</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>crib mattress</t>
+          <t>pants and shirts for my son</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -11510,34 +11522,34 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>amazon.com, babiesrus.com</t>
+          <t>kohls.com</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Amazon - crib mattress</t>
+          <t>kohls.com - 3 pairs pants, 2 shirts</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Snowed in today so I researched crib mattresses.  I didn't know this was a whole thing - organic vs. not, foam vs. coil, how firm.  Read reviews for an hour on Amazon and Babies R Us.  Ended up with a Sealy for $89 on Amazon, 4+ stars and people said it fit the crib we picked.  Free shipping.  The organic ones were $250 and I just couldn't.</t>
+          <t>Did this at lunch at my desk.  My son has hit a growth spurt and all his pants are high waters.  Kohls.com had Jumping Beans pants on sale for $8 and I had a 15% off email code plus I got $10 in Kohl's Cash out of it.  Free shipping with my Kohl's charge.  Took ten minutes.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>I think it's a good mattress but part of me wonders if I should have spent more.  It's where she'll sleep every night.</t>
+          <t>Cheap, fast, and I didn't have to drag him to a store to try things on - Kohls returns are easy if they don't fit.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Jillian</t>
+          <t>Alicia</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -11546,48 +11558,43 @@
         </is>
       </c>
       <c r="C224" s="1" t="n">
-        <v>40211</v>
+        <v>40218</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>glider for the nursery</t>
+          <t>snow boots for my son</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>craigslist</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>Dutailier glider and ottoman - craigslist, $75</t>
+          <t>zappos.com, landsend.com</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>I had been eyeing the gliders at Babies R Us ($250 and up!) and my sister told me to check craigslist first.  There was a Dutailier glider with the ottoman in Lake Forest for $75, from a family whose youngest is 3 now.  Mike drove over with his truck after work and picked it up.  It's in perfect shape, a little dusty.  Same one is $300 new.</t>
+          <t>Snow day, school closed, worked from home.  My son's boots are leaking so I looked at Zappos and Lands End between conference calls.  Lands End had the ones I liked for $34 but I wasn't sure what size he is in boots now so I'm having Dave measure his foot tonight and I'll order tomorrow.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Saved over $200 on something I'll use every night for the next two years.  I keep going in the nursery to sit in it.</t>
+          <t>Found what I want and Lands End has free returns, just need the size.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Jillian</t>
+          <t>Alicia</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -11596,31 +11603,31 @@
         </is>
       </c>
       <c r="C225" s="1" t="n">
-        <v>40212</v>
+        <v>40216</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>maternity jeans</t>
+          <t>Super Bowl pizza</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Motherhood Maternity, Gurnee Mills</t>
+          <t>Lou Malnati's website</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Motherhood Maternity - jeans, 1 top</t>
+          <t>2 deep dish pizzas and a salad</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>I finally can't button anything so I went to Motherhood Maternity at Gurnee Mills.  The saleswoman was really helpful about sizing but also really pushy about the clearance tops and the belly pillow thing, I said no about four times.  Got the full panel jeans ($49) and one long sleeve top.  The jeans are so comfortable I don't know why I waited.</t>
+          <t>Ordered pizza online from Lou Malnati's for the game instead of calling because the line is always busy on Super Bowl Sunday.  The site said 90 minutes and it took closer to two hours, but it got here before kickoff.  Dave thought we should have ordered by 2 o'clock, he was probably right.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -11630,14 +11637,14 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>Love the jeans.  Did not love being followed around the store.</t>
+          <t>Food was good as always.  Would have liked it to come when they said it would.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Jillian</t>
+          <t>Alicia</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -11646,11 +11653,11 @@
         </is>
       </c>
       <c r="C226" s="1" t="n">
-        <v>40217</v>
+        <v>40219</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>maternity tops</t>
+          <t>Valentines dinner for Dave</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -11660,17 +11667,17 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>oldnavy.com</t>
+          <t>Groupon</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>oldnavy.com - 4 maternity tops, leggings</t>
+          <t>Groupon for a restaurant in Libertyville</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Old Navy maternity is so much cheaper than Motherhood and the reviews on the site say they run true to size.  Got 4 long sleeve tops on sale for $12-15 each and a pair of maternity leggings.  Ordered enough to get free shipping over $50.  I read every review on each top first, Mike thinks I'm crazy.</t>
+          <t>I got a Groupon email for a restaurant in Libertyville we've been meaning to try - $50 of food for $25.  Bought it at my desk in about 30 seconds and emailed my mom to see if she can take our son that weekend.  That's the Valentine's plan.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -11680,14 +11687,14 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Four tops for what one cost at Motherhood.  Hopefully they fit, but returns go to the store so it's not a big deal.</t>
+          <t>Half price dinner and it made deciding what to do for Valentines easy.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Jillian</t>
+          <t>Alicia</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -11696,48 +11703,48 @@
         </is>
       </c>
       <c r="C227" s="1" t="n">
-        <v>40220</v>
+        <v>40212</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>nursery paint</t>
+          <t>valentines for preschool</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Home Depot</t>
+          <t>amazon.com, orientaltrading.com</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Home Depot - 2 gallons of paint, roller, tape (then 2 more gallons)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>We picked a pale yellow for the nursery from the Behr chips and went to Home Depot in Gurnee to get it mixed.  Waited 25 minutes at the paint counter because only one person was working it.  Got home, Mike rolled the first wall and it was way more lemon than the chip, almost neon.  Went back the next morning and the guy said thats just how yellow dries and wouldn't remix it without charging us again.  We ended up paying for two more gallons of a lighter shade.  $75 for paint we can't use.</t>
+          <t>His preschool needs 18 valentines by the 12th.  I looked at Oriental Trading and Amazon for the little card packs with pencils or tattoos.  Oriental Trading was cheap but shipping was almost as much as the order and I wasn't sure it would get here in time.  Decided I'll just grab a box at Target this week.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Not at all satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Long wait, wrong color, and they wouldn't make it right.  Really upset about this one.</t>
+          <t>Didn't buy anything but figured out it's not worth ordering online for something I can get at Target in five minutes.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Jillian</t>
+          <t>Alicia</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -11746,11 +11753,11 @@
         </is>
       </c>
       <c r="C228" s="1" t="n">
-        <v>40215</v>
+        <v>40213</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>registry</t>
+          <t>valentines, wine, cat litter</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -11760,17 +11767,17 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Babies R Us</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Babies R Us - onesies and a bottle brush</t>
+          <t>Target - Cars valentines, candy hearts, 2 bottles of wine, cat litter, shampoo</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Registry day!!  Mike and I went to Babies R Us in Vernon Hills and they gave us the scanner gun and we walked every aisle.  He got really into scanning things.  We looked at the two cribs in person and liked the cheaper one better, so it's on the registry.  We also scanned the car seat the Consumer Reports article liked, so maybe that's decided too.  Bought a pack of white onesies and a bottle brush because I couldn't leave with nothing.</t>
+          <t>Stopped at the Target in Vernon Hills on the way home from work.  Got the Cars valentines my son wanted, a bag of the little candy hearts to go with them, cat litter, shampoo, and a couple bottles of wine for the weekend.  Used the self checkout.  Twenty minutes door to door.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -11780,14 +11787,14 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Two hours and I feel like we actually have a plan now.  And it was fun, which I wasn't expecting.</t>
+          <t>Everything on my list in one quick stop on the way home.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Dawn</t>
+          <t>Alicia</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -11800,22 +11807,27 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>groceries</t>
+          <t>winter coat for me</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Shopped offline and didn't purchase</t>
+          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Jewel</t>
+          <t>kohls.com, Kohl's store</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Kohl's store - coat</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Tried to do a quick grocery run at Jewel with Jack (20 months) in the cart. Made it through produce and the dairy aisle before he lost it completely, screaming, throwing his shoes. I left the half full cart by the deli and carried him out. Will go back tonight when my husband is home.</t>
+          <t>Saw on kohls.com that their winter coats were an extra 30% off clearance so I went to the Kohl's in Vernon Hills after work to try them on and use my Kohl's Cash before it expired.  Found a coat for $38 but the line was 20 minutes long with two registers open and then the cashier couldn't get my Kohl's Cash to scan and had to call someone over.  Forty-five minutes in the store for one coat.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -11825,14 +11837,14 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>Didn't get a single thing and now I have to go back.  Not Jewel's fault.</t>
+          <t>The coat was a good price but the checkout was ridiculous.  Should have just ordered it online.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Bridget</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -11841,11 +11853,11 @@
         </is>
       </c>
       <c r="C230" s="1" t="n">
-        <v>40220</v>
+        <v>40210</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>crib mattress</t>
+          <t>diapers and wipes</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -11855,17 +11867,17 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>amazon.com, babiesrus.com, consumer reports</t>
+          <t>diapers.com</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Amazon - Sealy Soybean crib mattress</t>
+          <t>diapers.com - 2 boxes of Pampers, wipes</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>We're moving Owen to a toddler bed next month and the baby will get the crib, but the old mattress has a cracked cover so I wanted a new one.  I read the Consumer Reports ratings through the library website and then compared the top three on Amazon and babiesrus.com.  I wanted one without a lot of chemicals, and the Sealy Soybean one had good reviews and was $119 on Amazon with free shipping versus $139 at Babies R Us.  I read through about thirty reviews to make sure nobody had problems with it fitting a standard crib before I ordered.</t>
+          <t>We were down to about 6 diapers for the baby so I ordered from diapers.com last night after the kids were finally asleep.  I had a $10 off code from the little card that came in my last box and they always get here in a day or two which is faster than me getting both kids in the car to go to Target honestly.  Got 2 boxes of Pampers size 2 and a big box of wipes.  Free shipping over $49 so I was over that anyway.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -11875,14 +11887,14 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>Took my time, read the reviews, and saved $20.  It should be here next week.</t>
+          <t>Cheaper than Target with the code and it shows up on my porch.  Thats all I need right now!!</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Bridget</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -11891,31 +11903,31 @@
         </is>
       </c>
       <c r="C231" s="1" t="n">
-        <v>40211</v>
+        <v>40221</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>maternity clothes for work</t>
+          <t>exersaucer</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>motherhood.com, Motherhood Maternity store at Hawthorn</t>
+          <t>craigslist</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2 pair of pants and a cardigan at Motherhood Maternity</t>
+          <t>nothing yet</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>I'm 22 weeks with our second and my work pants have officially stopped buttoning.  I looked at the Motherhood website first to see what they had in the career line and what the prices were, and made a list of a few things, but I didn't want to order pants online without trying them on since I'm between sizes and the return shipping isn't free.  Went to the store at Hawthorn Mall on my lunch break and tried on probably eight pairs before settling on two in black and gray, plus a cardigan that was on the clearance rack for $19.99.  The salesgirl was helpful and didn't hover.</t>
+          <t>The baby is almost ready to sit up and I want an exersaucer but they are $80 new.  Looked on craigslist and there were a bunch in Grayslake and Gurnee for $20-$30.  I emailed two people, one already sold it and the other one hasnt answered yet.  I'm not in a hurry so we'll see.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -11925,14 +11937,14 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>Got what I needed and the pants fit well.  I still think $40 for a pair of pants I'll wear for four months is a lot, but I did my homework and that was the best price I found.</t>
+          <t>Craigslist is hit or miss but there were alot of them so I'm sure I'll get one.  Just annoying when people dont write back.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Kelsey</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -11941,31 +11953,31 @@
         </is>
       </c>
       <c r="C232" s="1" t="n">
-        <v>40217</v>
+        <v>40211</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>a play kitchen for Lily</t>
+          <t>formula</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>craigslist</t>
+          <t>Amazon Subscribe &amp; Save</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Little Tikes kitchen from a lady in Grayslake, $25</t>
+          <t>Amazon, 4 cans of Similac</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>I've been wanting to get Lily one of those Little Tikes kitchens since Christmas but they're like $80-100 new at Target and Toys R Us and she'd probably be done with it in a year, so I've been checking craigslist every couple of days and Monday morning a lady in Grayslake had one listed for $25 with the little pots and pans and everything. I emailed her right away and she said someone else had asked about it too but I could have it if I came that afternoon, so I threw Lily in the car and drove over with cash, she met me in her garage and the thing was a little dirty but nothing a wipe down with Clorox wipes couldn't fix. Lily has been playing with it nonstop since we got home and keeps making me "coffee" lol.</t>
+          <t>Set up subscribe and save on Amazon for the Similac since we go through so much of it.  Its 15% off and it just shows up every month so I dont have to think about it.  I did the math at the kitchen table while the baby napped and it comes out to about $3 less a can than Jewel.  My husband thinks I'm crazy for spending that long on it but $3 a can adds up when you buy 8 a month.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -11975,14 +11987,14 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>$25 instead of $90 for basically the same thing, and the lady was really nice about it.  I love craigslist for this kind of stuff.</t>
+          <t>One less thing to remember and we're saving like $25 a month on it.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Kelsey</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -11991,11 +12003,11 @@
         </is>
       </c>
       <c r="C233" s="1" t="n">
-        <v>40214</v>
+        <v>40212</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>clothes for my daughter</t>
+          <t>groceries</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -12005,17 +12017,17 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Carter's at Gurnee Mills</t>
+          <t>Jewel</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2 outfits and pajamas at Carter's</t>
+          <t>Jewel - groceries</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>My mom came up for the day so we took Lily to Gurnee Mills because I had a Carter's coupon from the mail, 20% off your purchase, and she's growing out of all her 24 month stuff so fast its crazy. The store was having a buy 1 get 1 50% off thing on the spring stuff but it was all still pretty pricey for what it is so I just got two outfits and a set of pajamas, my mom paid for one of the outfits which was nice of her.  Then we walked around and got pretzels and Lily fell asleep in the stroller so we actually got to look in Bath and Body Works in peace haha.</t>
+          <t>Jewel with both kids which is always an adventure.  I had my list and a stack of coupons from the Sunday paper and the ones I printed off the Jewel website, and alot of the stuff I needed was on the buy one get one list this week so I stocked up on cereal and pasta.  The baby started screaming in the dairy aisle so I skipped the last few things and just got in line.  Saved $31 in coupons which the cashier announced to the whole line, ha.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -12025,14 +12037,14 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>Cute clothes and the coupon helped but I still felt like I spent more than I meant to, Carter's is not cheap even on sale.</t>
+          <t>Good savings but I forgot the eggs and the dog food because of the meltdown so I'll have to go back.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Kelsey</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -12041,11 +12053,11 @@
         </is>
       </c>
       <c r="C234" s="1" t="n">
-        <v>40211</v>
+        <v>40215</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>diapers, wipes, snacks for Lily</t>
+          <t>kids clothes at the consignment sale</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -12055,17 +12067,17 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Moms club consignment sale (Libertyville)</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Target - diapers, wipes, goldfish, a sippy cup</t>
+          <t>big bag of kids clothes, snow pants, 2 toys</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>We were down to like 4 diapers so I loaded Lily in the car and ran up to the Target in Round Lake Beach after her nap, she loves riding in the cart there because of the big red balls out front and the popcorn smell so it's not a big deal to take her. Got the Target brand diapers because they're a couple dollars cheaper than Pampers and honestly they work just fine for us, plus a box of wipes and goldfish and she picked out a new sippy cup with Elmo on it which was not on my list but it was $3 so whatever.  In and out in maybe half an hour.</t>
+          <t>The moms club consignment sale was this morning in the church gym in Libertyville.  I got there 15 minutes before it opened and there was already a line of strollers.  Found snow pants for my 2 year old for $4 (!!), a whole stack of 6-12 month stuff for the baby, some shirts for my daughter and 2 little people toys.  All of it was $42.  Some of the stuff still had tags on it.  I was there an hour and a half and my husband had the kids so it was practically a vacation.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -12075,14 +12087,14 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>Got everything I came for, no meltdowns, and the diapers were on sale which I didn't even know until I got to the register.</t>
+          <t>$42 for what would have been $200 new, and I didnt have to do it with the kids.  Best shopping I've done in months.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Kelsey</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12091,31 +12103,26 @@
         </is>
       </c>
       <c r="C235" s="1" t="n">
-        <v>40215</v>
+        <v>40218</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>groceries and stuff for the super bowl</t>
+          <t>photo book for my mom</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Jewel</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>Jewel, groceries, chips, pop, a veggie tray</t>
+          <t>Shutterfly</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Saturday morning grocery run to the Jewel on Rollins, we're having my husband's brother and his girlfriend over for the game tomorrow so I needed chips and pop and a veggie tray plus the normal stuff like milk and bananas and Lily's yogurt. I had my Preferred card and a couple of coupons I printed off the Jewel website but one of them wouldn't scan and the cashier just kind of shrugged and I didn't feel like arguing over 75 cents with a toddler yelling for a cookie. The chips were 2 for $5 which was good.  Spent $94 which is about normal for us for the week.</t>
+          <t>Snow day, husband worked from home, kids napped at the same time for once so I started a photo book on Shutterfly for my moms birthday.  Got about halfway through uploading pictures before the baby woke up.  Its $29.99 for the one I want which is more than I want to pay so I'm going to wait for one of their 40% off emails, they send them every couple weeks.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -12125,14 +12132,14 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>Got what we needed and it was close to home but the coupon thing was kind of annoying and Jewel is never the cheapest.</t>
+          <t>Didnt finish it but I know they will send a code soon and I have time, her birthday isnt until March.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Kelsey</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12145,39 +12152,44 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>potty training stuff</t>
+          <t>prints for Valentines cards</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>target.com, amazon.com, babycenter boards</t>
+          <t>Walgreens photo</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Walgreens, 4x6 prints</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>We were snowed in Tuesday and Wednesday so I had alot of time on the computer during naps and I started looking at potty chairs since Lily is starting to show some interest. Looked at target.com and Amazon and read about a million reviews, some people swear by the little stand alone potty and some say just get the seat that goes on the regular toilet, and then I got sucked into the babycenter message boards for like an hour reading about potty training which was probably a mistake. Didn't buy anything, I think I want to see them in person at Target first and also my sister in law said she might still have theirs in the basement.</t>
+          <t>Uploaded pictures of the kids to the Walgreens site and ordered 20 prints to stick in Valentines cards for the grandparents and aunts.  They were ready in an hour and I picked them up on the way to the pediatrician.  They had a code for 10 cents a print so it was $2 and change.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>Didn't buy anything but I feel like I know what I'm looking for now, and I might get one for free from my sister in law anyway.</t>
+          <t>Two dollars, ready in an hour, and I was going right past there anyway.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Carly</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12186,11 +12198,11 @@
         </is>
       </c>
       <c r="C237" s="1" t="n">
-        <v>40215</v>
+        <v>40214</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>double stroller</t>
+          <t>snow pants for my 2 year old</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -12200,17 +12212,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>walmart.com, target.com, craigslist</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>nothing yet, still looking</t>
+          <t>target.com, oldnavy.com, landsend.com</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>I've been wanting a double stroller since Ava was born but we've been making do with the single plus the Baby Bjorn. Looked at walmart.com and target.com Saturday night after the kids were down, the Graco DuoGlider is about $130 at Walmart which is the cheapest new one I found, but that's still alot for us right now with my husband's hours cut.  Checked craigslist too and there were a few used ones for $50-60 but they looked pretty beat up in the pictures. Going to keep looking and maybe ask for one for Ava's birthday from the grandparents.</t>
+          <t>My daughter has outgrown her snowpants and it is February so I figured they would be on clearance by now.  Looked at target.com, old navy and lands end.  Lands end were nice but $35 and old navy was sold out of her size.  Target had some for $15 but the reviews said they run small.  Didnt buy, going to check the consignment sale this weekend first.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -12220,14 +12227,14 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>Didn't buy but I know what the going price is now. $130 isn't terrible, I just want to make sure we really need it first.</t>
+          <t>I didnt find a deal but I'm not paying full price for something she will wear for 6 more weeks.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Carly</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -12236,11 +12243,11 @@
         </is>
       </c>
       <c r="C238" s="1" t="n">
-        <v>40212</v>
+        <v>40216</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>spring/summer clothes for the kids</t>
+          <t>Super Bowl snacks</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -12250,17 +12257,17 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Once Upon a Child</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Once Upon a Child - 6 shirts, 3 pair shorts, sandals, a jacket</t>
+          <t>Target - chips, dip, pop, diapers</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Took a bag of the stuff Mason outgrew to Once Upon a Child in Vernon Hills to sell and they gave me $22 in store credit which I put right back into clothes for both kids! Found a ton of like-new spring stuff for Mason (3) and Ava (1 1/2), most of it Gap and Gymboree and Children's Place for $2-4 a piece.  Also got Ava a pair of pink sandals that still had the tags on for $4. Total was $38 after my credit so I basically got a whole season of clothes for $16 out of pocket. Love that place!!</t>
+          <t>Ran to Target in the morning for chips and pop and stuff for my husbands friends who were coming over for the game.  Also grabbed 2 boxes of diapers since they had the $5 gift card deal when you buy 2.  Target was crowded but I only had the baby so it was fine.  Ended up spending $60 which was more than I wanted but half of it was diapers.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -12270,14 +12277,14 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Name brand clothes for the price of garage sale stuff and I got rid of a bag of stuff I didn't need.  Win win!</t>
+          <t>Got the snacks and the diaper deal paid for itself with the gift card.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Carly</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -12286,11 +12293,11 @@
         </is>
       </c>
       <c r="C239" s="1" t="n">
-        <v>40218</v>
+        <v>40217</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>valentines for Mason's preschool class</t>
+          <t>Valentines craft stuff for playgroup</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -12300,17 +12307,17 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Dollar Tree</t>
+          <t>Michaels</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Dollar Tree - Cars valentines, heart stickers, pencils, a bag of conversation hearts</t>
+          <t>Michaels, foam hearts, stickers, doilies, glue sticks</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Mason has his Valentine's party at preschool on Friday (if we're not snowed out!) so we ran to the Dollar Tree in Mundelein before the snow started to get his valentines.  He picked out the Cars ones and I got heart stickers and a pack of pencils to put with them instead of candy since a couple kids in his class have allergies. Also grabbed conversation hearts for me and a couple of cheap heart balloons for Ava because she was being so good.  $8 total for everything, you can't beat the Dollar Tree for this kind of stuff.</t>
+          <t>I'm hosting playgroup on Wednesday and said I'd do a Valentines craft for the kids.  Went to Michaels in Gurnee with my 40% off coupon and got foam hearts, stickers, doilies and glue sticks.  Everything Valentines was already 50% off so I used the coupon on the glue sticks.  Spent $9 total for 6 kids.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -12320,14 +12327,14 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>Eight bucks for 15 valentines plus extras.  Mason was so excited to pick them out himself.</t>
+          <t>Nine dollars and the kids will be busy for twenty minutes.  Worth it.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Carly</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -12340,7 +12347,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>diapers and wipes</t>
+          <t>clothes for the kids</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -12350,17 +12357,17 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>diapers.com</t>
+          <t>oldnavy.com</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>diapers.com - 2 boxes of Pampers, wipes</t>
+          <t>oldnavy.com - jeans, 4 long sleeve tees, a hoodie, socks</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>We were down to about 6 diapers for the baby so I ordered from diapers.com last night after the kids were finally asleep.  I had a $10 off code from the little card that came in my last box and they always get here in a day or two which is faster than me getting both kids in the car to go to Target honestly.  Got 2 boxes of Pampers size 2 and a big box of wipes.  Free shipping over $49 so I was over that anyway.</t>
+          <t>Old Navy was having their overstock sale online and I needed jeans for Mason (3) because he's blown out the knees on all of his, and Ava (1 1/2) needs basically everything since the hand me downs from Mason are getting pretty worn. Filled my cart and I was at $43 and free shipping is $50 so I added socks and a hoodie for Ava to get over the line, which I'd rather do than pay $7 for shipping on a $43 order.  Also had a 15% off code from one of those email things.  The jeans were $10 each.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -12370,14 +12377,14 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>Cheaper than Target with the code and it shows up on my porch.  Thats all I need right now!!</t>
+          <t>Good prices, free shipping, and I didn't have to drag two kids through a store.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Carly</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -12386,48 +12393,48 @@
         </is>
       </c>
       <c r="C241" s="1" t="n">
-        <v>40221</v>
+        <v>40220</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>exersaucer</t>
+          <t>crib mattress</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>craigslist</t>
+          <t>amazon.com, babiesrus.com, consumer reports</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>nothing yet</t>
+          <t>Amazon - Sealy Soybean crib mattress</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>The baby is almost ready to sit up and I want an exersaucer but they are $80 new.  Looked on craigslist and there were a bunch in Grayslake and Gurnee for $20-$30.  I emailed two people, one already sold it and the other one hasnt answered yet.  I'm not in a hurry so we'll see.</t>
+          <t>We're moving Ava to a toddler bed next month and the baby will get the crib, but the old mattress has a cracked cover so I wanted a new one.  I read the Consumer Reports ratings through the library website and then compared the top three on Amazon and babiesrus.com.  I wanted one without a lot of chemicals, and the Sealy Soybean one had good reviews and was $119 on Amazon with free shipping versus $139 at Babies R Us.  I read through about thirty reviews to make sure nobody had problems with it fitting a standard crib before I ordered.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Craigslist is hit or miss but there were alot of them so I'm sure I'll get one.  Just annoying when people dont write back.</t>
+          <t>Took my time, read the reviews, and saved $20.  It should be here next week.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Carly</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -12436,48 +12443,48 @@
         </is>
       </c>
       <c r="C242" s="1" t="n">
-        <v>40211</v>
+        <v>40215</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>formula</t>
+          <t>double stroller</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Amazon Subscribe &amp; Save</t>
+          <t>walmart.com, target.com, craigslist</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Amazon, 4 cans of Similac</t>
+          <t>nothing yet, still looking</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Set up subscribe and save on Amazon for the Similac since we go through so much of it.  Its 15% off and it just shows up every month so I dont have to think about it.  I did the math at the kitchen table while the baby napped and it comes out to about $3 less a can than Jewel.  My husband thinks I'm crazy for spending that long on it but $3 a can adds up when you buy 8 a month.</t>
+          <t>I've been wanting a double stroller since Ava was born but we've been making do with the single plus the Baby Bjorn. Looked at walmart.com and target.com Saturday night after the kids were down, the Graco DuoGlider is about $130 at Walmart which is the cheapest new one I found, but that's still alot for us right now with my husband's hours cut.  Checked craigslist too and there were a few used ones for $50-60 but they looked pretty beat up in the pictures. Going to keep looking and maybe ask for one for Ava's birthday from the grandparents.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>One less thing to remember and we're saving like $25 a month on it.</t>
+          <t>Didn't buy but I know what the going price is now. $130 isn't terrible, I just want to make sure we really need it first.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Carly</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -12486,7 +12493,7 @@
         </is>
       </c>
       <c r="C243" s="1" t="n">
-        <v>40212</v>
+        <v>40221</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -12495,7 +12502,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped offline and didn't purchase</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -12503,31 +12510,26 @@
           <t>Jewel</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>Jewel - groceries</t>
-        </is>
-      </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Jewel with both kids which is always an adventure.  I had my list and a stack of coupons from the Sunday paper and the ones I printed off the Jewel website, and alot of the stuff I needed was on the buy one get one list this week so I stocked up on cereal and pasta.  The baby started screaming in the dairy aisle so I skipped the last few things and just got in line.  Saved $31 in coupons which the cashier announced to the whole line, ha.</t>
+          <t>Tried to do a quick grocery run at Jewel with Ava (20 months) in the cart. Made it through produce and the dairy aisle before she lost it completely, screaming, throwing her shoes. I left the half full cart by the deli and carried her out. Will go back tonight when my husband is home.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Not satisfied</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>Good savings but I forgot the eggs and the dog food because of the meltdown so I'll have to go back.</t>
+          <t>Didn't get a single thing and now I have to go back.  Not Jewel's fault.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Carly</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -12536,48 +12538,48 @@
         </is>
       </c>
       <c r="C244" s="1" t="n">
-        <v>40215</v>
+        <v>40211</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>kids clothes at the consignment sale</t>
+          <t>maternity clothes for work</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Moms club consignment sale (Libertyville)</t>
+          <t>motherhood.com, Motherhood Maternity store at Hawthorn</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>big bag of kids clothes, snow pants, 2 toys</t>
+          <t>2 pair of pants and a cardigan at Motherhood Maternity</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>The moms club consignment sale was this morning in the church gym in Libertyville.  I got there 15 minutes before it opened and there was already a line of strollers.  Found snow pants for my 2 year old for $4 (!!), a whole stack of 6-12 month stuff for the baby, some shirts for my daughter and 2 little people toys.  All of it was $42.  Some of the stuff still had tags on it.  I was there an hour and a half and my husband had the kids so it was practically a vacation.</t>
+          <t>I'm 22 weeks with our third and my work pants have officially stopped buttoning.  I looked at the Motherhood website first to see what they had in the career line and what the prices were, and made a list of a few things, but I didn't want to order pants online without trying them on since I'm between sizes and the return shipping isn't free.  Went to the store at Hawthorn Mall on my lunch break and tried on probably eight pairs before settling on two in black and gray, plus a cardigan that was on the clearance rack for $19.99.  The salesgirl was helpful and didn't hover.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>$42 for what would have been $200 new, and I didnt have to do it with the kids.  Best shopping I've done in months.</t>
+          <t>Got what I needed and the pants fit well.  I still think $40 for a pair of pants I'll wear for four months is a lot, but I did my homework and that was the best price I found.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Carly</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -12586,43 +12588,48 @@
         </is>
       </c>
       <c r="C245" s="1" t="n">
-        <v>40218</v>
+        <v>40212</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>photo book for my mom</t>
+          <t>spring/summer clothes for the kids</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Shutterfly</t>
+          <t>Once Upon a Child</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Once Upon a Child - 6 shirts, 3 pair shorts, sandals, a jacket</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Snow day, husband worked from home, kids napped at the same time for once so I started a photo book on Shutterfly for my moms birthday.  Got about halfway through uploading pictures before the baby woke up.  Its $29.99 for the one I want which is more than I want to pay so I'm going to wait for one of their 40% off emails, they send them every couple weeks.</t>
+          <t>Took a bag of the stuff Mason outgrew to Once Upon a Child in Vernon Hills to sell and they gave me $22 in store credit which I put right back into clothes for both kids! Found a ton of like-new spring stuff for Mason (3) and Ava (1 1/2), most of it Gap and Gymboree and Children's Place for $2-4 a piece.  Also got Ava a pair of pink sandals that still had the tags on for $4. Total was $38 after my credit so I basically got a whole season of clothes for $16 out of pocket. Love that place!!</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>Didnt finish it but I know they will send a code soon and I have time, her birthday isnt until March.</t>
+          <t>Name brand clothes for the price of garage sale stuff and I got rid of a bag of stuff I didn't need.  Win win!</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Carly</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -12631,31 +12638,31 @@
         </is>
       </c>
       <c r="C246" s="1" t="n">
-        <v>40220</v>
+        <v>40218</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>prints for Valentines cards</t>
+          <t>valentines for Mason's preschool class</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Walgreens photo</t>
+          <t>Dollar Tree</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Walgreens, 4x6 prints</t>
+          <t>Dollar Tree - Cars valentines, heart stickers, pencils, a bag of conversation hearts</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Uploaded pictures of the kids to the Walgreens site and ordered 20 prints to stick in Valentines cards for the grandparents and aunts.  They were ready in an hour and I picked them up on the way to the pediatrician.  They had a code for 10 cents a print so it was $2 and change.</t>
+          <t>Mason has his Valentine's party at preschool on Friday (if we're not snowed out!) so we ran to the Dollar Tree in Mundelein before the snow started to get his valentines.  He picked out the Cars ones and I got heart stickers and a pack of pencils to put with them instead of candy since a couple kids in his class have allergies. Also grabbed conversation hearts for me and a couple of cheap heart balloons for Ava because she was being so good.  $8 total for everything, you can't beat the Dollar Tree for this kind of stuff.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -12665,14 +12672,14 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>Two dollars, ready in an hour, and I was going right past there anyway.</t>
+          <t>Eight bucks for 15 valentines plus extras.  Mason was so excited to pick them out himself.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Jillian</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -12681,43 +12688,48 @@
         </is>
       </c>
       <c r="C247" s="1" t="n">
-        <v>40214</v>
+        <v>40221</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>snow pants for my 2 year old</t>
+          <t>breast pump</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>target.com, oldnavy.com, landsend.com</t>
+          <t>amazon.com, babiesrus.com, buybuybaby.com</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Amazon - Medela Pump In Style</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>My daughter has outgrown her snowpants and it is February so I figured they would be on clearance by now.  Looked at target.com, old navy and lands end.  Lands end were nice but $35 and old navy was sold out of her size.  Target had some for $15 but the reviews said they run small.  Didnt buy, going to check the consignment sale this weekend first.</t>
+          <t>Everyone says get the Medela Pump In Style so I compared prices.  Babies R Us $279, buybuybaby.com $279, Amazon $249 with free shipping and no tax.  Thirty dollars is thirty dollars.  Ordered it from Amazon.  I'm due in 8 weeks and this was the last big thing on the list that wasn't on the registry.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>I didnt find a deal but I'm not paying full price for something she will wear for 6 more weeks.</t>
+          <t>Same pump everyone recommends for $30 less.  One more thing checked off, 8 weeks to go!</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Jillian</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -12726,48 +12738,43 @@
         </is>
       </c>
       <c r="C248" s="1" t="n">
-        <v>40216</v>
+        <v>40214</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Super Bowl snacks</t>
+          <t>car seat</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>Target - chips, dip, pop, diapers</t>
+          <t>amazon.com, babycenter.com, consumer reports</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Ran to Target in the morning for chips and pop and stuff for my husbands friends who were coming over for the game.  Also grabbed 2 boxes of diapers since they had the $5 gift card deal when you buy 2.  Target was crowded but I only had the baby so it was fine.  Ended up spending $60 which was more than I wanted but half of it was diapers.</t>
+          <t>Spent most of my evening on car seats.  Started on Amazon, then the babycenter message boards, then Consumer Reports which I had to pay for.  Every seat has someone saying it's the best and someone saying it's the worst.  Infant seat vs. convertible, which ones fit in a Civic, which bases fit.  I closed the laptop with more tabs open than when I started and no decision.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Not satisfied</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Got the snacks and the diaper deal paid for itself with the gift card.</t>
+          <t>I thought I'd have an answer tonight and I'm more confused than when I started.  This is the one thing I'm actually scared of getting wrong.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Jillian</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -12776,48 +12783,43 @@
         </is>
       </c>
       <c r="C249" s="1" t="n">
-        <v>40217</v>
+        <v>40210</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Valentines craft stuff for playgroup</t>
+          <t>crib</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Michaels</t>
-        </is>
-      </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>Michaels, foam hearts, stickers, doilies, glue sticks</t>
+          <t>babiesrus.com, buybuybaby.com, amazon.com</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>I'm hosting playgroup on Wednesday and said I'd do a Valentines craft for the kids.  Went to Michaels in Gurnee with my 40% off coupon and got foam hearts, stickers, doilies and glue sticks.  Everything Valentines was already 50% off so I used the coupon on the glue sticks.  Spent $9 total for 6 kids.</t>
+          <t>Started seriously looking at cribs tonight!  I had a list of about 8 from the baby book and from my friend Jen, and I went through all of them on babiesrus.com, buybuybaby.com and Amazon reading reviews.  Some of the reviews are scary (drop side recalls) so I'm only looking at fixed side ones now.  Narrowed it down to 2, both convertible, one is $299 and one is $379.  Mike wants to see them in person before we decide so we're going to the store this weekend.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>Nine dollars and the kids will be busy for twenty minutes.  Worth it.</t>
+          <t>Didn't buy yet but I feel so much better having it down to two.  Eight was too many.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Alicia</t>
+          <t>Jillian</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -12826,11 +12828,11 @@
         </is>
       </c>
       <c r="C250" s="1" t="n">
-        <v>40217</v>
+        <v>40218</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>birthday present for my nephew</t>
+          <t>crib mattress</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -12840,34 +12842,34 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>amazon.com</t>
+          <t>amazon.com, babiesrus.com</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Amazon - Lego set</t>
+          <t>Amazon - crib mattress</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>My nephew turns 6 next week.  My sister said he's into Legos so I searched Amazon at lunch, found a Lego City set in the $20 range with 4.5 stars, and had it shipped directly to their house in Naperville with gift wrap.  Done in less than 10 minutes.</t>
+          <t>Snowed in today so I researched crib mattresses.  I didn't know this was a whole thing - organic vs. not, foam vs. coil, how firm.  Read reviews for an hour on Amazon and Babies R Us.  Ended up with a Sealy for $89 on Amazon, 4+ stars and people said it fit the crib we picked.  Free shipping.  The organic ones were $250 and I just couldn't.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Shipped straight to him, gift wrapped, and I didn't have to find time to go to a store or the post office.</t>
+          <t>I think it's a good mattress but part of me wonders if I should have spent more.  It's where she'll sleep every night.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Alicia</t>
+          <t>Jillian</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -12876,31 +12878,31 @@
         </is>
       </c>
       <c r="C251" s="1" t="n">
-        <v>40215</v>
+        <v>40211</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Costco run</t>
+          <t>glider for the nursery</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Costco</t>
+          <t>craigslist</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Costco - paper towels, chicken, granola bars, printer paper, a sweater</t>
+          <t>Dutailier glider and ottoman - craigslist, $75</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Dave and I went to Costco in Mettawa Saturday morning while my mom had our son.  Standard stuff - paper towels, toilet paper, chicken breasts, the big box of granola bars for lunches, printer paper for my home office.  I also picked up a sweater for $19.99 from the table because it looked fine and why not.  $240 total which is about normal for us.</t>
+          <t>I had been eyeing the gliders at Babies R Us ($250 and up!) and my sister told me to check craigslist first.  There was a Dutailier glider with the ottoman in Lake Forest for $75, from a family whose youngest is 3 now.  Mike drove over with his truck after work and picked it up.  It's in perfect shape, a little dusty.  Same one is $300 new.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -12910,14 +12912,14 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Fast because we went early, and no kid asking for samples every ten feet.</t>
+          <t>Saved over $200 on something I'll use every night for the next two years.  I keep going in the nursery to sit in it.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Alicia</t>
+          <t>Jillian</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -12926,48 +12928,48 @@
         </is>
       </c>
       <c r="C252" s="1" t="n">
-        <v>40210</v>
+        <v>40212</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>groceries</t>
+          <t>maternity jeans</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Peapod</t>
+          <t>Motherhood Maternity, Gurnee Mills</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Peapod - groceries</t>
+          <t>Motherhood Maternity - jeans, 1 top</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Placed our Peapod order Sunday night for Monday evening delivery.  I keep a standing list in my account so it takes about 15 minutes to go through it and add whatever is new.  Delivery fee was $6.95 which is less than the gas and the hour I'd spend at Jewel with a 4 year old.  Driver was in our window and nothing was substituted this time.</t>
+          <t>I finally can't button anything so I went to Motherhood Maternity at Gurnee Mills.  The saleswoman was really helpful about sizing but also really pushy about the clearance tops and the belly pillow thing, I said no about four times.  Got the full panel jeans ($49) and one long sleeve top.  The jeans are so comfortable I don't know why I waited.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>Everything came as ordered, on time, and I never left the house.</t>
+          <t>Love the jeans.  Did not love being followed around the store.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Alicia</t>
+          <t>Jillian</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -12976,11 +12978,11 @@
         </is>
       </c>
       <c r="C253" s="1" t="n">
-        <v>40211</v>
+        <v>40217</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>pants and shirts for my son</t>
+          <t>maternity tops</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -12990,17 +12992,17 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>kohls.com</t>
+          <t>oldnavy.com</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>kohls.com - 3 pairs pants, 2 shirts</t>
+          <t>oldnavy.com - 4 maternity tops, leggings</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Did this at lunch at my desk.  My son has hit a growth spurt and all his pants are high waters.  Kohls.com had Jumping Beans pants on sale for $8 and I had a 15% off email code plus I got $10 in Kohl's Cash out of it.  Free shipping with my Kohl's charge.  Took ten minutes.</t>
+          <t>Old Navy maternity is so much cheaper than Motherhood and the reviews on the site say they run true to size.  Got 4 long sleeve tops on sale for $12-15 each and a pair of maternity leggings.  Ordered enough to get free shipping over $50.  I read every review on each top first, Mike thinks I'm crazy.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -13010,14 +13012,14 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Cheap, fast, and I didn't have to drag him to a store to try things on - Kohls returns are easy if they don't fit.</t>
+          <t>Four tops for what one cost at Motherhood.  Hopefully they fit, but returns go to the store so it's not a big deal.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Alicia</t>
+          <t>Jillian</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -13026,43 +13028,48 @@
         </is>
       </c>
       <c r="C254" s="1" t="n">
-        <v>40218</v>
+        <v>40220</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>snow boots for my son</t>
+          <t>nursery paint</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>zappos.com, landsend.com</t>
+          <t>Home Depot</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Home Depot - 2 gallons of paint, roller, tape (then 2 more gallons)</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Snow day, school closed, worked from home.  My son's boots are leaking so I looked at Zappos and Lands End between conference calls.  Lands End had the ones I liked for $34 but I wasn't sure what size he is in boots now so I'm having Dave measure his foot tonight and I'll order tomorrow.</t>
+          <t>We picked a pale yellow for the nursery from the Behr chips and went to Home Depot in Gurnee to get it mixed.  Waited 25 minutes at the paint counter because only one person was working it.  Got home, Mike rolled the first wall and it was way more lemon than the chip, almost neon.  Went back the next morning and the guy said thats just how yellow dries and wouldn't remix it without charging us again.  We ended up paying for two more gallons of a lighter shade.  $75 for paint we can't use.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Not at all satisfied</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Found what I want and Lands End has free returns, just need the size.</t>
+          <t>Long wait, wrong color, and they wouldn't make it right.  Really upset about this one.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Alicia</t>
+          <t>Jillian</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -13071,48 +13078,48 @@
         </is>
       </c>
       <c r="C255" s="1" t="n">
-        <v>40216</v>
+        <v>40215</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Super Bowl pizza</t>
+          <t>registry</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Lou Malnati's website</t>
+          <t>Babies R Us</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2 deep dish pizzas and a salad</t>
+          <t>Babies R Us - onesies and a bottle brush</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Ordered pizza online from Lou Malnati's for the game instead of calling because the line is always busy on Super Bowl Sunday.  The site said 90 minutes and it took closer to two hours, but it got here before kickoff.  Dave thought we should have ordered by 2 o'clock, he was probably right.</t>
+          <t>Registry day!!  Mike and I went to Babies R Us in Vernon Hills and they gave us the scanner gun and we walked every aisle.  He got really into scanning things.  We looked at the two cribs in person and liked the cheaper one better, so it's on the registry.  We also scanned the car seat the Consumer Reports article liked, so maybe that's decided too.  Bought a pack of white onesies and a bottle brush because I couldn't leave with nothing.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Food was good as always.  Would have liked it to come when they said it would.</t>
+          <t>Two hours and I feel like we actually have a plan now.  And it was fun, which I wasn't expecting.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Alicia</t>
+          <t>Kelsey</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -13121,31 +13128,31 @@
         </is>
       </c>
       <c r="C256" s="1" t="n">
-        <v>40219</v>
+        <v>40217</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Valentines dinner for Dave</t>
+          <t>a play kitchen for Lily</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Groupon</t>
+          <t>craigslist</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Groupon for a restaurant in Libertyville</t>
+          <t>Little Tikes kitchen from a lady in Grayslake, $25</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>I got a Groupon email for a restaurant in Libertyville we've been meaning to try - $50 of food for $25.  Bought it at my desk in about 30 seconds and emailed my mom to see if she can take our son that weekend.  That's the Valentine's plan.</t>
+          <t>I've been wanting to get Lily one of those Little Tikes kitchens since Christmas but they're like $80-100 new at Target and Toys R Us and she'd probably be done with it in a year, so I've been checking craigslist every couple of days and Monday morning a lady in Grayslake had one listed for $25 with the little pots and pans and everything. I emailed her right away and she said someone else had asked about it too but I could have it if I came that afternoon, so I threw Lily in the car and drove over with cash, she met me in her garage and the thing was a little dirty but nothing a wipe down with Clorox wipes couldn't fix. Lily has been playing with it nonstop since we got home and keeps making me "coffee" lol.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -13155,14 +13162,14 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>Half price dinner and it made deciding what to do for Valentines easy.</t>
+          <t>$25 instead of $90 for basically the same thing, and the lady was really nice about it.  I love craigslist for this kind of stuff.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Alicia</t>
+          <t>Kelsey</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -13171,31 +13178,31 @@
         </is>
       </c>
       <c r="C257" s="1" t="n">
-        <v>40212</v>
+        <v>40214</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>valentines for preschool</t>
+          <t>clothes for my daughter</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>amazon.com, orientaltrading.com</t>
+          <t>Carter's at Gurnee Mills</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2 outfits and pajamas at Carter's</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>His preschool needs 18 valentines by the 12th.  I looked at Oriental Trading and Amazon for the little card packs with pencils or tattoos.  Oriental Trading was cheap but shipping was almost as much as the order and I wasn't sure it would get here in time.  Decided I'll just grab a box at Target this week.</t>
+          <t>My mom came up for the day so we took Lily to Gurnee Mills because I had a Carter's coupon from the mail, 20% off your purchase, and she's growing out of all her 24 month stuff so fast its crazy. The store was having a buy 1 get 1 50% off thing on the spring stuff but it was all still pretty pricey for what it is so I just got two outfits and a set of pajamas, my mom paid for one of the outfits which was nice of her.  Then we walked around and got pretzels and Lily fell asleep in the stroller so we actually got to look in Bath and Body Works in peace haha.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -13205,14 +13212,14 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>Didn't buy anything but figured out it's not worth ordering online for something I can get at Target in five minutes.</t>
+          <t>Cute clothes and the coupon helped but I still felt like I spent more than I meant to, Carter's is not cheap even on sale.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Alicia</t>
+          <t>Kelsey</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -13221,11 +13228,11 @@
         </is>
       </c>
       <c r="C258" s="1" t="n">
-        <v>40213</v>
+        <v>40211</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>valentines, wine, cat litter</t>
+          <t>diapers, wipes, snacks for Lily</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -13240,12 +13247,12 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Target - Cars valentines, candy hearts, 2 bottles of wine, cat litter, shampoo</t>
+          <t>Target - diapers, wipes, goldfish, a sippy cup</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Stopped at the Target in Vernon Hills on the way home from work.  Got the Cars valentines my son wanted, a bag of the little candy hearts to go with them, cat litter, shampoo, and a couple bottles of wine for the weekend.  Used the self checkout.  Twenty minutes door to door.</t>
+          <t>We were down to like 4 diapers so I loaded Lily in the car and ran up to the Target in Round Lake Beach after her nap, she loves riding in the cart there because of the big red balls out front and the popcorn smell so it's not a big deal to take her. Got the Target brand diapers because they're a couple dollars cheaper than Pampers and honestly they work just fine for us, plus a box of wipes and goldfish and she picked out a new sippy cup with Elmo on it which was not on my list but it was $3 so whatever.  In and out in maybe half an hour.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -13255,14 +13262,14 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>Everything on my list in one quick stop on the way home.</t>
+          <t>Got everything I came for, no meltdowns, and the diapers were on sale which I didn't even know until I got to the register.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Alicia</t>
+          <t>Kelsey</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -13271,48 +13278,48 @@
         </is>
       </c>
       <c r="C259" s="1" t="n">
-        <v>40221</v>
+        <v>40215</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>winter coat for me</t>
+          <t>groceries and stuff for the super bowl</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>kohls.com, Kohl's store</t>
+          <t>Jewel</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Kohl's store - coat</t>
+          <t>Jewel, groceries, chips, pop, a veggie tray</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Saw on kohls.com that their winter coats were an extra 30% off clearance so I went to the Kohl's in Vernon Hills after work to try them on and use my Kohl's Cash before it expired.  Found a coat for $38 but the line was 20 minutes long with two registers open and then the cashier couldn't get my Kohl's Cash to scan and had to call someone over.  Forty-five minutes in the store for one coat.</t>
+          <t>Saturday morning grocery run to the Jewel on Rollins, we're having my husband's brother and his girlfriend over for the game tomorrow so I needed chips and pop and a veggie tray plus the normal stuff like milk and bananas and Lily's yogurt. I had my Preferred card and a couple of coupons I printed off the Jewel website but one of them wouldn't scan and the cashier just kind of shrugged and I didn't feel like arguing over 75 cents with a toddler yelling for a cookie. The chips were 2 for $5 which was good.  Spent $94 which is about normal for us for the week.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>Not satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>The coat was a good price but the checkout was ridiculous.  Should have just ordered it online.</t>
+          <t>Got what we needed and it was close to home but the coupon thing was kind of annoying and Jewel is never the cheapest.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>Kelsey</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -13321,48 +13328,43 @@
         </is>
       </c>
       <c r="C260" s="1" t="n">
-        <v>40210</v>
+        <v>40220</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>clothes for the boys</t>
+          <t>potty training stuff</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>oldnavy.com</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>oldnavy.com - jeans, 4 long sleeve tees, a hoodie, socks</t>
+          <t>target.com, amazon.com, babycenter boards</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Old Navy was having their overstock sale online and I needed jeans for Tyler (4) because he's blown out the knees on all of his, and Nate (2) needs basically everything since the hand me downs from Tyler are getting pretty worn. Filled my cart and I was at $43 and free shipping is $50 so I added socks and a hoodie for Nate to get over the line, which I'd rather do than pay $7 for shipping on a $43 order.  Also had a 15% off code from one of those email things.  The jeans were $10 each.</t>
+          <t>We were snowed in Tuesday and Wednesday so I had alot of time on the computer during naps and I started looking at potty chairs since Lily is starting to show some interest. Looked at target.com and Amazon and read about a million reviews, some people swear by the little stand alone potty and some say just get the seat that goes on the regular toilet, and then I got sucked into the babycenter message boards for like an hour reading about potty training which was probably a mistake. Didn't buy anything, I think I want to see them in person at Target first and also my sister in law said she might still have theirs in the basement.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>Good prices, free shipping, and I didn't have to drag two boys through a store.</t>
+          <t>Didn't buy anything but I feel like I know what I'm looking for now, and I might get one for free from my sister in law anyway.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>Kelsey</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -13375,7 +13377,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>baby food, puffs, sleep sacks</t>
+          <t>spring clothes for Lily</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -13385,17 +13387,17 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>amazon.com, diapers.com</t>
+          <t>gymboree.com</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Amazon - Earth's Best jars, Gerber puffs, 2 Halo sleep sacks</t>
+          <t>gymboree.com - 2 dresses, leggings, a cardigan, hair clips</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Snow day.  Daycare was closed and so was my office, so I was home with Ella and did some ordering while she napped.  Stocked up on baby food and puffs through Amazon (Subscribe &amp; Save again) and ordered two more Halo sleep sacks in the next size since the two we have are always in the wash.  Checked diapers.com first but their price on the sleep sacks was higher and I already had an Amazon order going, so I just added everything to that.  Free shipping, done.</t>
+          <t>Recieved the Gymboree email that their spring line was 30% off plus I had Gymbucks from December that were about to expire, so I sat down after Lily went to bed and ordered her spring stuff. I had to get the total over $75 to use all my Gymbucks so I added the hair clips at the end. The site was slow and kicked me out of my cart once but the second time it went through. Ended up with 2 dresses, 2 pairs of leggings and a cardigan for about $60 after everything, which for Gymboree is really good.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -13405,7 +13407,7 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>Got it all in one order while stuck at home.  Can't complain about that.</t>
+          <t>Used my Gymbucks before they expired and got her set for spring. The matching outfits are so cute I can hardly stand it.</t>
         </is>
       </c>
     </row>
@@ -13421,41 +13423,41 @@
         </is>
       </c>
       <c r="C262" s="1" t="n">
-        <v>40216</v>
+        <v>40219</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>convertible car seat</t>
+          <t>baby food, puffs, sleep sacks</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>babiesrus.com, amazon.com</t>
+          <t>amazon.com, diapers.com</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Did not purchase</t>
+          <t>Amazon - Earth's Best jars, Gerber puffs, 2 Halo sleep sacks</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Ella is almost out of the infant seat so I spent part of Sunday morning (while my husband watched the pre-game) researching convertible seats.  Narrowed it down to the Britax Marathon or the Graco MyRide based on reviews and the Consumer Reports ratings.  Babies R Us has a 20% coupon that expires next week but it excludes Britax, of course.  Going to wait and see if Amazon drops the price, it's been bouncing around.</t>
+          <t>Snow day.  Daycare was closed and so was my office, so I was home with Ella and did some ordering while she napped.  Stocked up on baby food and puffs through Amazon (Subscribe &amp; Save again) and ordered two more Halo sleep sacks in the next size since the two we have are always in the wash.  Checked diapers.com first but their price on the sleep sacks was higher and I already had an Amazon order going, so I just added everything to that.  Free shipping, done.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Productive research, no decision yet.  I'd rather take a week and get the right seat than rush it.</t>
+          <t>Got it all in one order while stuck at home.  Can't complain about that.</t>
         </is>
       </c>
     </row>
@@ -13471,41 +13473,41 @@
         </is>
       </c>
       <c r="C263" s="1" t="n">
-        <v>40210</v>
+        <v>40216</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>diapers and wipes</t>
+          <t>convertible car seat</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>amazon.com</t>
+          <t>babiesrus.com, amazon.com</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Amazon - Pampers size 3 (2 boxes), wipes</t>
+          <t>Did not purchase</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Set up Subscribe &amp; Save on Amazon for diapers and wipes.  I work full time and the last thing I want to do on a weeknight is run to the store for diapers.  15% off plus free shipping, and I compared the per-diaper price against Costco and Target and it was within a few cents.  Took about 10 minutes at lunch.</t>
+          <t>Ella is almost out of the infant seat so I spent part of Sunday morning (while my husband watched the pre-game) researching convertible seats.  Narrowed it down to the Britax Marathon or the Graco MyRide based on reviews and the Consumer Reports ratings.  Babies R Us has a 20% coupon that expires next week but it excludes Britax, of course.  Going to wait and see if Amazon drops the price, it's been bouncing around.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>Cheaper than the store once you factor in my time, and it just shows up on the porch every month.</t>
+          <t>Productive research, no decision yet.  I'd rather take a week and get the right seat than rush it.</t>
         </is>
       </c>
     </row>
@@ -13521,48 +13523,48 @@
         </is>
       </c>
       <c r="C264" s="1" t="n">
-        <v>40213</v>
+        <v>40210</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>formula</t>
+          <t>diapers and wipes</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>amazon.com</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Walgreens, 1 can of Similac</t>
+          <t>Amazon - Pampers size 3 (2 boxes), wipes</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Realized at 9:45 at night that we had maybe one bottle's worth of formula left for the morning daycare bottle.  Walgreens on Milwaukee Ave is the only thing open that late so I drove over in my pajamas.  They had the Similac Advance but only the small can and it was $15.99, which is at least $3 more than Target.  Paid it because I had no choice.  Note to self, keep a backup can in the pantry.</t>
+          <t>Set up Subscribe &amp; Save on Amazon for diapers and wipes.  I work full time and the last thing I want to do on a weeknight is run to the store for diapers.  15% off plus free shipping, and I compared the per-diaper price against Costco and Target and it was within a few cents.  Took about 10 minutes at lunch.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>Not satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>Overpriced and I only ended up there because I didn't plan ahead.  Convenient, but $16 for a small can is ridiculous.</t>
+          <t>Cheaper than the store once you factor in my time, and it just shows up on the porch every month.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Crystal</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -13571,41 +13573,41 @@
         </is>
       </c>
       <c r="C265" s="1" t="n">
-        <v>40214</v>
+        <v>40213</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>spring clothes for my 3 year old</t>
+          <t>formula</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>gymboree.com</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>gymboree.com - 2 dresses, leggings, a cardigan, hair clips</t>
+          <t>Walgreens, 1 can of Similac</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Recieved the Gymboree email that their spring line was 30% off plus I had Gymbucks from December that were about to expire, so I sat down after Chloe went to bed and ordered her spring stuff. I had to get the total over $75 to use all my Gymbucks so I added the hair clips at the end. The site was slow and kicked me out of my cart once but the second time it went through. Ended up with 2 dresses, 2 pairs of leggings and a cardigan for about $60 after everything, which for Gymboree is really good.</t>
+          <t>Realized at 9:45 at night that we had maybe one bottle's worth of formula left for the morning daycare bottle.  Walgreens on Milwaukee Ave is the only thing open that late so I drove over in my pajamas.  They had the Similac Advance but only the small can and it was $15.99, which is at least $3 more than Target.  Paid it because I had no choice.  Note to self, keep a backup can in the pantry.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Not satisfied</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>Used my Gymbucks before they expired and got her set for spring. The matching outfits are so cute I can hardly stand it.</t>
+          <t>Overpriced and I only ended up there because I didn't plan ahead.  Convenient, but $16 for a small can is ridiculous.</t>
         </is>
       </c>
     </row>
@@ -13771,43 +13773,48 @@
         </is>
       </c>
       <c r="C269" s="1" t="n">
-        <v>40212</v>
+        <v>40217</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>valentines for the grandkids' classes</t>
+          <t>groceries</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>shutterfly, vistaprint</t>
+          <t>Aldi</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Aldi, groceries</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>My daughter wanted me to look at the photo valentines on Shutterfly where you put the child's picture on the card.  They were cute but it came out to about $20 per child with shipping, and the 3 year old's preschool only has 12 kids.  I told her the boxed ones from Target are $2.99 and the kids like the Spiderman ones anyway.</t>
+          <t>Did my shopping at Aldi on Grand Ave. $42 for the week. Brought my own bags and a quarter for the cart.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>I'm glad I looked before I bought. The cards were nice but not worth it for a preschool class.</t>
+          <t>Cheapest place around. I can stay in my budget.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Joyce</t>
+          <t>Arlene</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -13816,31 +13823,26 @@
         </is>
       </c>
       <c r="C270" s="1" t="n">
-        <v>40211</v>
+        <v>40212</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>a fleece jacket</t>
+          <t>valentines for the grandkids' classes</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Lands End</t>
-        </is>
-      </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>landsend.com, fleece jacket</t>
+          <t>shutterfly, vistaprint</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>I've been wearing the same fleece to walk the dog for about six years so I ordered a new one from Lands' End. They had the full zip one on overstock for $29.50, down from $49.50. I know my size with them so there's no guessing. Shipping was $6.95 which I always forget about untill checkout.</t>
+          <t>My daughter wanted me to look at the photo valentines on Shutterfly where you put the child's picture on the card.  They were cute but it came out to about $20 per child with shipping, and the 3 year old's preschool only has 12 kids.  I told her the boxed ones from Target are $2.99 and the kids like the Spiderman ones anyway.</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -13850,14 +13852,14 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>Good price on the jacket and I know it will fit, but shipping ate up some of the savings.</t>
+          <t>I'm glad I looked before I bought. The cards were nice but not worth it for a preschool class.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Joyce</t>
+          <t>Harriet</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -13870,27 +13872,27 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>baby clothes for my new granddaughter</t>
+          <t>a winter coat</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>amazon.com</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>amazon: 3 Carter's sleepers, a hooded towel</t>
+          <t>Nordstrom, a wool coat</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Our first grandbaby, Addison, was born in January in Scottsdale and I can't just drop by with things like my mother did. I ordered three Carter's sleepers in 3-6 months and a hooded towel on Amazon and shipped them straight to my son's house. Free shipping with the super saver option, and I could add a gift note. My daughter in law sent me a picture of her in one of the sleepers two days later.</t>
+          <t>My good wool coat is eleven years old and the lining has finally given out, so I went to Nordstrom at Old Orchard on Monday morning when it is quiet. A lovely saleswoman in the coat department brought me four coats to try and was honest about which one suited me. I chose a charcoal coat by Cinzia Rocca, which was marked down from the fall. Not inexpensive, but it will last me another ten years.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -13900,14 +13902,14 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>Shipped right to Arizona for free and I got a picture to prove it fit.</t>
+          <t>Attentive, honest service and a coat that will outlast anything cheaper.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Joyce</t>
+          <t>Harriet</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -13916,43 +13918,48 @@
         </is>
       </c>
       <c r="C272" s="1" t="n">
-        <v>40214</v>
+        <v>40213</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>digital picture frame</t>
+          <t>dress shoes</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>amazon, bestbuy.com</t>
+          <t>macys.com</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>macys.com, Naturalizer pumps in 8 narrow</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>I want a digital frame so I can load it with pictures of the baby for my mother, who is 86 and not going to use a computer. Spent an hour reading reviews on Amazon and Best Buy's site. Every frame has someone saying it died in a month, and the specs mean nothing to me, 800x600 vs 1024x768. Gave up for tonight.</t>
+          <t>This was my second attempt to buy the same pair of shoes from Macy's website. The pair that arrived in January was a size 8 medium although I had ordered the narrow, and returning them was an ordeal: I had to print a label, pay $7.95 to send them back, and three weeks later the credit has still not appeared on my statement. I telephoned customer service today and was on hold for twenty-five minutes before a young woman told me to wait another billing cycle. I reordered the narrow width against my better judgment because the store does not carry it.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>Not satisfied</t>
+          <t>Not at all satisfied</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>Too many choices and the reviews contradict each other, I'm no closer to picking one.</t>
+          <t>I have paid twice for shoes I do not have, paid to return their mistake, and been told to wait. I will not order from their website again.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Harriet</t>
+          <t>Joyce</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -13961,48 +13968,48 @@
         </is>
       </c>
       <c r="C273" s="1" t="n">
-        <v>40210</v>
+        <v>40211</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>a winter coat</t>
+          <t>a fleece jacket</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Lands End</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Nordstrom, a wool coat</t>
+          <t>landsend.com, fleece jacket</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>My good wool coat is eleven years old and the lining has finally given out, so I went to Nordstrom at Old Orchard on Monday morning when it is quiet. A lovely saleswoman in the coat department brought me four coats to try and was honest about which one suited me. I chose a charcoal coat by Cinzia Rocca, which was marked down from the fall. Not inexpensive, but it will last me another ten years.</t>
+          <t>I've been wearing the same fleece to walk the dog for about six years so I ordered a new one from Lands' End. They had the full zip one on overstock for $29.50, down from $49.50. I know my size with them so there's no guessing. Shipping was $6.95 which I always forget about untill checkout.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>Attentive, honest service and a coat that will outlast anything cheaper.</t>
+          <t>Good price on the jacket and I know it will fit, but shipping ate up some of the savings.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Harriet</t>
+          <t>Joyce</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -14011,11 +14018,11 @@
         </is>
       </c>
       <c r="C274" s="1" t="n">
-        <v>40213</v>
+        <v>40210</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>dress shoes</t>
+          <t>baby clothes for my new granddaughter</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -14025,34 +14032,34 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>macys.com</t>
+          <t>amazon.com</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>macys.com, Naturalizer pumps in 8 narrow</t>
+          <t>amazon: 3 Carter's sleepers, a hooded towel</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>This was my second attempt to buy the same pair of shoes from Macy's website. The pair that arrived in January was a size 8 medium although I had ordered the narrow, and returning them was an ordeal: I had to print a label, pay $7.95 to send them back, and three weeks later the credit has still not appeared on my statement. I telephoned customer service today and was on hold for twenty-five minutes before a young woman told me to wait another billing cycle. I reordered the narrow width against my better judgment because the store does not carry it.</t>
+          <t>Our first grandbaby, Addison, was born in January in Scottsdale and I can't just drop by with things like my mother did. I ordered three Carter's sleepers in 3-6 months and a hooded towel on Amazon and shipped them straight to my son's house. Free shipping with the super saver option, and I could add a gift note. My daughter in law sent me a picture of her in one of the sleepers two days later.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Not at all satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>I have paid twice for shoes I do not have, paid to return their mistake, and been told to wait. I will not order from their website again.</t>
+          <t>Shipped right to Arizona for free and I got a picture to prove it fit.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Darlene</t>
+          <t>Joyce</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -14061,48 +14068,43 @@
         </is>
       </c>
       <c r="C275" s="1" t="n">
-        <v>40210</v>
+        <v>40214</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>photo book of the grandkids</t>
+          <t>digital picture frame</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Shutterfly</t>
-        </is>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>Shutterfly, 8x8 photo book</t>
+          <t>amazon, bestbuy.com</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>I had about 200 pictures from Christmas with the grandkids on the camera and finally sat down Sunday night and made a photo book on Shutterfly. Took me almost three hours because I kept moving pictures around, but they had a 30% off code from the email plus free shipping on $30 and I ended up at $27 for the 8x8 hardcover. This one is for my mother in the nursing home, she can't work the digital frame my brother got her but she can turn pages. I ordered it Monday morning from work on my break, don't tell my boss!!</t>
+          <t>I want a digital frame so I can load it with pictures of the baby for my mother, who is 86 and not going to use a computer. Spent an hour reading reviews on Amazon and Best Buy's site. Every frame has someone saying it died in a month, and the specs mean nothing to me, 800x600 vs 1024x768. Gave up for tonight.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Not satisfied</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>The website is fun to use and the coupon made it affordable. My mom is going to love it.</t>
+          <t>Too many choices and the reviews contradict each other, I'm no closer to picking one.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Mildred</t>
+          <t>Joyce</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -14115,27 +14117,27 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>groceries</t>
+          <t>photo book of the baby</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Aldi</t>
+          <t>Shutterfly</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Aldi, groceries</t>
+          <t>Shutterfly, 8x8 photo book</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Did my shopping at Aldi on Grand Ave. $42 for the week. Brought my own bags and a quarter for the cart.</t>
+          <t>I had about 200 pictures from our trip out to Scottsdale to meet Addison on the camera and finally sat down Sunday night and made a photo book on Shutterfly. Took me almost three hours because I kept moving pictures around, but they had a 30% off code from the email plus free shipping on $30 and I ended up at $27 for the 8x8 hardcover. This one is for my mother in the nursing home, she can't work a computer but she can turn pages. I ordered it Monday morning from work on my break, don't tell my boss!!</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -14145,14 +14147,14 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>Cheapest place around. I can stay in my budget.</t>
+          <t>The website is fun to use and the coupon made it affordable. My mom is going to love it.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Mallory</t>
+          <t>Anjali</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -14161,11 +14163,11 @@
         </is>
       </c>
       <c r="C277" s="1" t="n">
-        <v>40220</v>
+        <v>40213</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Valentine's gift for my boyfriend</t>
+          <t>Cell phone plan</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -14175,12 +14177,17 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>amazon, thinkgeek, bestbuy.com</t>
+          <t>verizonwireless.com, att.com, t-mobile.com, sprint.com</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Did not purchase</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Still have no idea what to get Chris for Valentine's.  Spent probably an hour at work going back and forth between Amazon and thinkgeek and Best Buy looking at headphones and video games and some ridiculous Star Wars stuff.  Everything is either too much or too dumb.  Didnt buy anything, I will probably just end up at Target Saturday like always.</t>
+          <t>I am still on my parents' Verizon family plan and I want to see if it would be cheaper to get my own.  Made a spreadsheet of the individual plans on all four carriers at 450 minutes with unlimited texting.  Cheapest was T-Mobile at $59.99 before taxes, but then I would need a new phone.  Verizon is $69.99 and I could keep mine.  Either way it is more than the $30 I give my parents now.  Staying put.</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -14190,14 +14197,14 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>Wasted an hour and I'm no closer.  He's impossible to shop for.</t>
+          <t>Spent two hours on it and the answer is that everything costs more than I expected.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Paige</t>
+          <t>Anjali</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -14206,11 +14213,11 @@
         </is>
       </c>
       <c r="C278" s="1" t="n">
-        <v>40215</v>
+        <v>40220</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>groceries and wine</t>
+          <t>Headphones</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -14220,34 +14227,34 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Trader Joe's</t>
+          <t>Best Buy</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Trader Joe's - groceries, 3 bottles of wine, flowers</t>
+          <t>Sony earbuds, $19.99</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Had friends coming over Saturday night to watch movies so I went to Trader Joe's in Lake Zurich in the morning.  Got cheese, crackers, the frozen appetizer things everybody likes, three bottles of the cheap wine and some tulips for the table.  It was crowded (it's always crowded) but the lines move fast.  About $60 total.</t>
+          <t>My earbuds died and I use them every day at the library.  I knew amazon had the same Sony ones for $12 but I didn't want to wait a week, so I went to Best Buy in Vernon Hills after the roads were cleared.  $19.99.  The cheaper Skullcandy ones had bad reviews on the shelf tag.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>Everything for a whole night with friends for $60 and the tulips were $4.  Can't beat it.</t>
+          <t>Paid $8 more than online for not waiting.  Fair enough, but it still bugs me.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Danielle</t>
+          <t>Anjali</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -14256,43 +14263,48 @@
         </is>
       </c>
       <c r="C279" s="1" t="n">
-        <v>40212</v>
+        <v>40210</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Registry</t>
+          <t>Textbook</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>crateandbarrel.com, bedbathandbeyond.com</t>
+          <t>half.com, amazon.com, Chegg, campus bookstore website</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>used statistics textbook from half.com, $38.50</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Mike and I set up the registry at Crate &amp; Barrel in the store a couple weeks ago and I spent some time tonight before my shift adding things online at both Crate &amp; Barrel and Bed Bath &amp; Beyond.  The Bed Bath site is clunky and kept logging me out.  Crate's site was fine.  Added towels, a knife set and a few things Mike picked.</t>
+          <t>The stats textbook for my methods class is $142 new at the campus bookstore.  I checked half.com, amazon used, and Chegg for renting.  Chegg was $48 to rent for the semester, amazon used started at $55, half.com had a copy in good condition for $38.50 including shipping.  I bought the half.com copy since I can resell it in May and probably get most of it back.</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>Got it done.  Not really shopping but it needed to happen.</t>
+          <t>Paid about a quarter of the bookstore price.  The seller had 99% positive feedback.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Danielle</t>
+          <t>Caitlin</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -14305,44 +14317,39 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Save the date supplies</t>
+          <t>bar stools</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Michaels</t>
-        </is>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>cardstock, envelopes, a paper cutter at Michaels</t>
+          <t>overstock.com, potterybarn.com, crateandbarrel.com</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>We are making our own save the dates to save money.  Michaels had a 40% off one item coupon in the Sunday paper and another one I printed from their website.  Used one on the paper cutter ($24.99 down to $15) and the other on a pack of cardstock.  The cashier let me use both since I rang them up as two transactions.  Envelopes were on sale too.</t>
+          <t>I have a breakfast bar in the condo and no stools, 8 months after moving in.  Pottery Barn's are gorgeous and $199 each.  Overstock had similar ones for $89 each but reviews mentioned wobbling.  Crate &amp; Barrel was in between.  I think I want to sit on them before I buy, so I may go to Old Orchard this weekend.</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Saved about $20 with the coupons and got everything in one trip.</t>
+          <t>Good to know the range.  I'm not going to buy furniture without sitting on it.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Danielle</t>
+          <t>Caitlin</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -14351,48 +14358,48 @@
         </is>
       </c>
       <c r="C281" s="1" t="n">
-        <v>40210</v>
+        <v>40215</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Scrubs</t>
+          <t>groceries and wine</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>allheart.com, scrubsandbeyond.com</t>
+          <t>Trader Joe's</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>2 sets of scrubs from allheart.com</t>
+          <t>Trader Joe's - groceries, 3 bottles of wine, flowers</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Needed new scrubs, mine are getting thin.  Scrubs and Beyond was cheaper per set but allheart had the Cherokee brand I like in the hunter green our unit wears.  Ordered two sets.  The coupon code from their email didn't work at checkout and shipping was $8.95, so it ended up more than I thought.</t>
+          <t>Had friends coming over Saturday night to watch movies so I went to Trader Joe's in Lake Zurich in the morning.  Got cheese, crackers, the frozen appetizer things everybody likes, three bottles of the cheap wine and some tulips for the table.  It was crowded (it's always crowded) but the lines move fast.  About $60 total.</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>Not satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>The coupon not working was annoying and the shipping charge is high for two sets of scrubs.</t>
+          <t>Everything for a whole night with friends for $60 and the tulips were $4.  Can't beat it.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Danielle</t>
+          <t>Caitlin</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -14401,41 +14408,41 @@
         </is>
       </c>
       <c r="C282" s="1" t="n">
-        <v>40211</v>
+        <v>40210</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Wedding dress</t>
+          <t>Running shoes</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Shopped offline and didn't purchase</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Fleet Feet</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Did not purchase</t>
+          <t>Brooks Adrenaline at Fleet Feet</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Had an appointment at David's Bridal in Gurnee with my mom and my sister.  They gave us a consultant who was also helping two other brides, so she kept disappearing.  I told her my budget was $600 and she kept bringing dresses that were $800 and up.  I tried on 5, liked one, but she couldn't tell me when it would come in if I ordered it.  We left after an hour and 15 minutes and nobody even asked if we wanted to book another appointment.</t>
+          <t>I have been putting off new running shoes since the fall and my knees are starting to tell me about it.  Drove into the city to Fleet Feet because they actually watch you run and fit you properly.  Ended up with the Brooks Adrenaline again, $99.95.  The guy also looked at my old pair and said I was overdue by about 200 miles.</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>Not at all satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>I expected a lot more help for something this big.  Felt like a number.</t>
+          <t>Worth the drive and the price to be fitted by someone who knows what they're doing.</t>
         </is>
       </c>
     </row>
@@ -14451,11 +14458,11 @@
         </is>
       </c>
       <c r="C283" s="1" t="n">
-        <v>40213</v>
+        <v>40220</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>bar stools</t>
+          <t>Valentine's gift for my boyfriend</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -14465,22 +14472,22 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>overstock.com, potterybarn.com, crateandbarrel.com</t>
+          <t>amazon, thinkgeek, bestbuy.com</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>I have a breakfast bar in the condo and no stools, 8 months after moving in.  Pottery Barn's are gorgeous and $199 each.  Overstock had similar ones for $89 each but reviews mentioned wobbling.  Crate &amp; Barrel was in between.  I think I want to sit on them before I buy, so I may go to Old Orchard this weekend.</t>
+          <t>Still have no idea what to get Chris for Valentine's.  Spent probably an hour at work going back and forth between Amazon and thinkgeek and Best Buy looking at headphones and video games and some ridiculous Star Wars stuff.  Everything is either too much or too dumb.  Didnt buy anything, I will probably just end up at Target Saturday like always.</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Not satisfied</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>Good to know the range.  I'm not going to buy furniture without sitting on it.</t>
+          <t>Wasted an hour and I'm no closer.  He's impossible to shop for.</t>
         </is>
       </c>
     </row>
@@ -14496,31 +14503,31 @@
         </is>
       </c>
       <c r="C284" s="1" t="n">
-        <v>40210</v>
+        <v>40214</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Running shoes</t>
+          <t>Valentine's gift for my mom</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Fleet Feet</t>
+          <t>proflowers, 1-800-Flowers</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Brooks Adrenaline at Fleet Feet</t>
+          <t>tulips and a box of chocolates from proflowers</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>I have been putting off new running shoes since the fall and my knees are starting to tell me about it.  Drove into the city to Fleet Feet because they actually watch you run and fit you properly.  Ended up with the Brooks Adrenaline again, $99.95.  The guy also looked at my old pair and said I was overdue by about 200 miles.</t>
+          <t>My mom is a widow and Valentine's is a hard day for her, so I send her something every year.  ProFlowers had 30 tulips with a vase for $39.99 and I added the chocolates.  1-800-Flowers was about $10 more for a similar bunch.  Scheduled the delivery for Friday the 12th so they get there before the weekend.  Delivery charge was $9.99 which seemed like a lot.</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -14530,14 +14537,14 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>Worth the drive and the price to be fitted by someone who knows what they're doing.</t>
+          <t>Easy to schedule and I know she'll love them.  Just wish the delivery fee was less.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Caitlin</t>
+          <t>Danielle</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -14546,48 +14553,43 @@
         </is>
       </c>
       <c r="C285" s="1" t="n">
-        <v>40214</v>
+        <v>40212</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Valentine's gift for my mom</t>
+          <t>Registry</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped online and didn't purchase</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>proflowers, 1-800-Flowers</t>
-        </is>
-      </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>tulips and a box of chocolates from proflowers</t>
+          <t>crateandbarrel.com, bedbathandbeyond.com</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>My mom is a widow and Valentine's is a hard day for her, so I send her something every year.  ProFlowers had 30 tulips with a vase for $39.99 and I added the chocolates.  1-800-Flowers was about $10 more for a similar bunch.  Scheduled the delivery for Friday the 12th so they get there before the weekend.  Delivery charge was $9.99 which seemed like a lot.</t>
+          <t>Mike and I set up the registry at Crate &amp; Barrel in the store a couple weeks ago and I spent some time tonight before my shift adding things online at both Crate &amp; Barrel and Bed Bath &amp; Beyond.  The Bed Bath site is clunky and kept logging me out.  Crate's site was fine.  Added towels, a knife set and a few things Mike picked.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>Easy to schedule and I know she'll love them.  Just wish the delivery fee was less.</t>
+          <t>Got it done.  Not really shopping but it needed to happen.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Haley</t>
+          <t>Danielle</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -14600,39 +14602,44 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>bachelorette party stuff</t>
+          <t>Save the date supplies</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Shopped online and didn't purchase</t>
+          <t>Shopped offline and purchased offline</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>amazon.com, partycity.com, etsy, bachelorette.com</t>
+          <t>Michaels</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>cardstock, envelopes, a paper cutter at Michaels</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>I am maid of honor for my friend Steph's wedding in May and I am starting to plan the bachelorette.  Spent my lunch hour looking at sashes, tiaras, those straws, etc.  Party City has all the standard stuff but etsy had cuter personalized things that are more expensive.  Didn't buy anything because I need to figure out the budget with the other bridesmaids first.  Also looked at a few hotels in Chicago but that is a whole seperate project.</t>
+          <t>We are making our own save the dates to save money.  Michaels had a 40% off one item coupon in the Sunday paper and another one I printed from their website.  Used one on the paper cutter ($24.99 down to $15) and the other on a pack of cardstock.  The cashier let me use both since I rang them up as two transactions.  Envelopes were on sale too.</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>Found a lot of options but need to know what everyone is willing to spend first.</t>
+          <t>Saved about $20 with the coupons and got everything in one trip.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Haley</t>
+          <t>Danielle</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -14641,48 +14648,48 @@
         </is>
       </c>
       <c r="C287" s="1" t="n">
-        <v>40218</v>
+        <v>40210</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>boots</t>
+          <t>Scrubs</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>dsw.com, zappos</t>
+          <t>allheart.com, scrubsandbeyond.com</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>tall brown boots at DSW in Vernon Hills</t>
+          <t>2 sets of scrubs from allheart.com</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>The snow finally did it, my feet have been soaked every morning walking to the train.  I found a pair of Steve Madden boots on DSW's website for $89.95 and saw the Vernon Hills store had them in my size, so I ran over there after work before the storm got bad.  They had a $10 off coupon at the register for rewards members too.</t>
+          <t>Needed new scrubs, mine are getting thin.  Scrubs and Beyond was cheaper per set but allheart had the Cherokee brand I like in the hunter green our unit wears.  Ordered two sets.  The coupon code from their email didn't work at checkout and shipping was $8.95, so it ended up more than I thought.</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Not satisfied</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>Got them the same day instead of waiting for shipping, and saved $10 on top of it!</t>
+          <t>The coupon not working was annoying and the shipping charge is high for two sets of scrubs.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Haley</t>
+          <t>Danielle</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -14695,37 +14702,37 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Groupon</t>
+          <t>Wedding dress</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped offline and didn't purchase</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Groupon</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>$40 at a sushi place in the city for $20</t>
+          <t>Did not purchase</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>My coworker got me hooked on Groupon.  Today's deal was $40 worth of sushi for $20 at a place near my office so I jumped on it, my roommate Katie and I have been wanting to try it.  Took about 30 seconds to buy.  I now have 3 Groupons sitting in my email I need to actually use.</t>
+          <t>Had an appointment at David's Bridal in Gurnee with my mom and my sister.  They gave us a consultant who was also helping two other brides, so she kept disappearing.  I told her my budget was $600 and she kept bringing dresses that were $800 and up.  I tried on 5, liked one, but she couldn't tell me when it would come in if I ordered it.  We left after an hour and 15 minutes and nobody even asked if we wanted to book another appointment.</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>Extremely satisfied</t>
+          <t>Not at all satisfied</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>Half off sushi!  Can't argue with that.</t>
+          <t>I expected a lot more help for something this big.  Felt like a number.</t>
         </is>
       </c>
     </row>
@@ -14741,11 +14748,11 @@
         </is>
       </c>
       <c r="C289" s="1" t="n">
-        <v>40217</v>
+        <v>40213</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>hotel for the bachelorette</t>
+          <t>bachelorette party stuff</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -14755,27 +14762,22 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>hotels.com, Expedia, priceline, the hotel websites</t>
-        </is>
-      </c>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t>nothing yet</t>
+          <t>amazon.com, partycity.com, etsy, bachelorette.com</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Tried to figure out hotels for the bachelorette weekend downtown.  Looked at hotels.com, Expedia and priceline for the same Saturday in April and every one of them had a different price for the same room at the Hard Rock, from $189 to $249.  Then the hotel's own site had a package that looked better but you couldn't tell what it included.  Gave up after an hour, I will just call them.</t>
+          <t>I am maid of honor for my friend Steph's wedding in May and I am starting to plan the bachelorette.  Spent my lunch hour looking at sashes, tiaras, those straws, etc.  Party City has all the standard stuff but etsy had cuter personalized things that are more expensive.  Didn't buy anything because I need to figure out the budget with the other bridesmaids first.  Also looked at a few hotels in Chicago but that is a whole seperate project.</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>Not satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>Confusing and a waste of a lunch hour.  You shouldn't have to check 4 sites to know what a room costs.</t>
+          <t>Found a lot of options but need to know what everyone is willing to spend first.</t>
         </is>
       </c>
     </row>
@@ -14791,48 +14793,48 @@
         </is>
       </c>
       <c r="C290" s="1" t="n">
-        <v>40210</v>
+        <v>40218</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Metra monthly pass</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Shopped offline and purchased offline</t>
+          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Vernon Hills Metra station</t>
+          <t>dsw.com, zappos</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>February monthly pass</t>
+          <t>tall brown boots at DSW in Vernon Hills</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>First of the month = monthly pass time.  I always buy it at the ticket window at the station because I never remember to order it online in time.  $135 and change for the month, and there was a line of about 8 people doing the exact same thing.</t>
+          <t>The snow finally did it, my feet have been soaked every morning walking to the train.  I found a pair of Steve Madden boots on DSW's website for $89.95 and saw the Vernon Hills store had them in my size, so I ran over there after work before the storm got bad.  They had a $10 off coupon at the register for rewards members too.</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Extremely satisfied</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>It is what it is.  At least the line moved fast.</t>
+          <t>Got them the same day instead of waiting for shipping, and saved $10 on top of it!</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Simone</t>
+          <t>Haley</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -14841,31 +14843,31 @@
         </is>
       </c>
       <c r="C291" s="1" t="n">
-        <v>40213</v>
+        <v>40211</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>running shoes</t>
+          <t>Groupon</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
+          <t>Shopped online and purchased online</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>zappos, runningwarehouse.com, Fleet Feet</t>
+          <t>Groupon</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Fleet Feet, Asics Gel-Kayano</t>
+          <t>$40 at a sushi place in the city for $20</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>I have been putting off new running shoes since my knee started bothering me.  Looked at the Asics I always get on Zappos and runningwarehouse to see what the going price was, about $120 everywhere.  Decided to just go to Fleet Feet in Deerfield after work since they actually watch you run and I wanted to make sure it wasn't the shoes.  The guy there said my old pair was way past due (which I knew) and I ended up with the same model, one size up.  Same price as online so I didn't feel bad about it.</t>
+          <t>My coworker got me hooked on Groupon.  Today's deal was $40 worth of sushi for $20 at a place near my office so I jumped on it, my roommate Katie and I have been wanting to try it.  Took about 30 seconds to buy.  I now have 3 Groupons sitting in my email I need to actually use.</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -14875,14 +14877,14 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>Paid the same as online and got someone to actually look at my feet.  Knee feels better already, or maybe that's in my head.</t>
+          <t>Half off sushi!  Can't argue with that.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Anjali</t>
+          <t>Haley</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -14891,11 +14893,11 @@
         </is>
       </c>
       <c r="C292" s="1" t="n">
-        <v>40213</v>
+        <v>40217</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Cell phone plan</t>
+          <t>hotel for the bachelorette</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -14905,17 +14907,17 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>verizonwireless.com, att.com, t-mobile.com, sprint.com</t>
+          <t>hotels.com, Expedia, priceline, the hotel websites</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Did not purchase</t>
+          <t>nothing yet</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>I am still on my parents' Verizon family plan and I want to see if it would be cheaper to get my own.  Made a spreadsheet of the individual plans on all four carriers at 450 minutes with unlimited texting.  Cheapest was T-Mobile at $59.99 before taxes, but then I would need a new phone.  Verizon is $69.99 and I could keep mine.  Either way it is more than the $30 I give my parents now.  Staying put.</t>
+          <t>Tried to figure out hotels for the bachelorette weekend downtown.  Looked at hotels.com, Expedia and priceline for the same Saturday in April and every one of them had a different price for the same room at the Hard Rock, from $189 to $249.  Then the hotel's own site had a package that looked better but you couldn't tell what it included.  Gave up after an hour, I will just call them.</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -14925,14 +14927,14 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>Spent two hours on it and the answer is that everything costs more than I expected.</t>
+          <t>Confusing and a waste of a lunch hour.  You shouldn't have to check 4 sites to know what a room costs.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Anjali</t>
+          <t>Haley</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -14941,11 +14943,11 @@
         </is>
       </c>
       <c r="C293" s="1" t="n">
-        <v>40220</v>
+        <v>40210</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Headphones</t>
+          <t>Metra monthly pass</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -14955,17 +14957,17 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Best Buy</t>
+          <t>Vernon Hills Metra station</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Sony earbuds, $19.99</t>
+          <t>February monthly pass</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>My earbuds died and I use them every day at the library.  I knew amazon had the same Sony ones for $12 but I didn't want to wait a week, so I went to Best Buy in Vernon Hills after the roads were cleared.  $19.99.  The cheaper Skullcandy ones had bad reviews on the shelf tag.</t>
+          <t>First of the month = monthly pass time.  I always buy it at the ticket window at the station because I never remember to order it online in time.  $135 and change for the month, and there was a line of about 8 people doing the exact same thing.</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -14975,14 +14977,14 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>Paid $8 more than online for not waiting.  Fair enough, but it still bugs me.</t>
+          <t>It is what it is.  At least the line moved fast.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Anjali</t>
+          <t>Haley</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -14991,31 +14993,31 @@
         </is>
       </c>
       <c r="C294" s="1" t="n">
-        <v>40210</v>
+        <v>40213</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Textbook</t>
+          <t>running shoes</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Shopped online and purchased online</t>
+          <t>Shopped online and purchased offline (at store, over phone, by mail)</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>half.com, amazon.com, Chegg, campus bookstore website</t>
+          <t>zappos, runningwarehouse.com, Fleet Feet</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>used statistics textbook from half.com, $38.50</t>
+          <t>Fleet Feet, Asics Gel-Kayano</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>The stats textbook for my methods class is $142 new at the campus bookstore.  I checked half.com, amazon used, and Chegg for renting.  Chegg was $48 to rent for the semester, amazon used started at $55, half.com had a copy in good condition for $38.50 including shipping.  I bought the half.com copy since I can resell it in May and probably get most of it back.</t>
+          <t>I have been putting off new running shoes since my knee started bothering me.  Looked at the Asics I always get on Zappos and runningwarehouse to see what the going price was, about $120 everywhere.  Decided to just go to Fleet Feet in Deerfield after work since they actually watch you run and I wanted to make sure it wasn't the shoes.  The guy there said my old pair was way past due (which I knew) and I ended up with the same model, one size up.  Same price as online so I didn't feel bad about it.</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -15025,7 +15027,7 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>Paid about a quarter of the bookstore price.  The seller had 99% positive feedback.</t>
+          <t>Paid the same as online and got someone to actually look at my feet.  Knee feels better already, or maybe that's in my head.</t>
         </is>
       </c>
     </row>
